--- a/public/sc/network/downloads/scholars-and-directions.xlsx
+++ b/public/sc/network/downloads/scholars-and-directions.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人物目录" sheetId="1" r:id="R400882360c914b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方向明细" sheetId="2" r:id="R9e78cb74424c4229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人物目录" sheetId="1" r:id="R33bfb18bcc444683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方向明细" sheetId="2" r:id="R116d22254ac34ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物理论文" sheetId="3" r:id="R004c553933704554"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -98,8 +99,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScholarCatalog" displayName="ScholarCatalog" ref="A5:F35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:F35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScholarCatalog" displayName="ScholarCatalog" ref="A5:F43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:F43"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="学校/机构"/>
@@ -113,8 +114,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ResearchDirections" displayName="ResearchDirections" ref="A5:G132" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G132"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ResearchDirections" displayName="ResearchDirections" ref="A5:G162" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G162"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="研究主类"/>
@@ -123,6 +124,24 @@
     <x:tableColumn id="5" name="待回答的问题"/>
     <x:tableColumn id="6" name="证据依据"/>
     <x:tableColumn id="7" name="来源网址"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PhysicsPapers" displayName="PhysicsPapers" ref="A5:I201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:I201"/>
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="人物"/>
+    <x:tableColumn id="2" name="发表日期与精度"/>
+    <x:tableColumn id="3" name="论文题名"/>
+    <x:tableColumn id="4" name="期刊"/>
+    <x:tableColumn id="5" name="DOI"/>
+    <x:tableColumn id="6" name="作者位置"/>
+    <x:tableColumn id="7" name="归属证据"/>
+    <x:tableColumn id="8" name="元数据状态"/>
+    <x:tableColumn id="9" name="来源网址"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -344,7 +363,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>首批学者目录</x:v>
+        <x:v>学者目录</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -354,7 +373,7 @@
     </x:row>
     <x:row r="3" ht="19.5" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>2026-10-22核验；30位首批人选。旧附件时效单独标记，名单不代表招生资格。</x:v>
+        <x:v>2026-10-23更新；38位人物，含物理专题9位。各来源时效见正文。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -592,7 +611,7 @@
     </x:row>
     <x:row r="16" ht="37.5" customHeight="1">
       <x:c r="A16" s="10" t="str">
-        <x:v>周珍宇</x:v>
+        <x:v>舒富文</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
         <x:v>南昌大学</x:v>
@@ -601,98 +620,98 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D16" s="10" t="str">
-        <x:v>功能性MOF孔环境设计；乙炔/乙烯及多组分分离；电化学传感器设计；多孔材料电催化</x:v>
+        <x:v>黑洞信息、全息纠缠与量子引力；修正引力与引力波检验；量子信息方法与引力诱导纠缠</x:v>
       </x:c>
       <x:c r="E16" s="10" t="str">
-        <x:v>官网确认2013.09-2016.06在华南理工获硕士学位；尚未据此指定导师。</x:v>
+        <x:v>任职状态按采集日官网核验；历史论文保留其原始年代，未将现单位回填。</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="37.5" customHeight="1">
       <x:c r="A17" s="10" t="str">
-        <x:v>崔志明</x:v>
+        <x:v>王俊波</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>华南理工大学</x:v>
+        <x:v>南昌大学</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D17" s="10" t="str">
-        <x:v>固态及复合电解质；锂、石墨与硅基负极；固态软包电池；氢氧电催化与膜电极</x:v>
+        <x:v>金属表面反应路径与自由基转移；二维Kagome与共价/金属有机结构构筑；实空间表征与多尺度手性传递</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
-        <x:v>官方课题组由崔志明、宋慧宇共同带领；不将团队所有成果归为单人独立工作。</x:v>
+        <x:v>任职状态按采集日官网核验；历史论文保留其原始年代，未将现单位回填。</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zmcui/</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="37.5" customHeight="1">
       <x:c r="A18" s="10" t="str">
-        <x:v>江焕峰</x:v>
+        <x:v>王启胜</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>华南理工大学</x:v>
+        <x:v>南昌大学</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D18" s="10" t="str">
-        <x:v>绿色有机合成与过渡金属催化；精细化学品与药物中间体；CO2作为羰基源的羧基化</x:v>
+        <x:v>低维拓扑与范德华材料输运；铅盐半导体热载流子与红外探测；非易失光存储与可重构感存算；光热电定位、成像与信息编码</x:v>
       </x:c>
       <x:c r="E18" s="10" t="str">
-        <x:v>当前教师目录链接的简介明确截至2008年，不能当成2026完整画像；另有2025中国化学会报告线索。</x:v>
+        <x:v>任职状态按采集日官网核验；历史论文保留其原始年代，未将现单位回填。</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/092809/</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5" customHeight="1">
       <x:c r="A19" s="10" t="str">
-        <x:v>李雪辉</x:v>
+        <x:v>于天宝</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>华南理工大学</x:v>
+        <x:v>南昌大学</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D19" s="10" t="str">
-        <x:v>生物质催化转化；绿色催化技术；催化脱硫脱氮；催化塑料降解</x:v>
+        <x:v>拓扑光子/声光子晶体与波导；准连续谱束缚态与光物质耦合；衍射光网络与光电协同计算；结构光场与光学计量成像</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>官网链接到绿色催化与能源课题组；上述是团队声明，个人主持分工待论文与项目核实。</x:v>
+        <x:v>任职状态按采集日官网核验；历史论文保留其原始年代，未将现单位回填。</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="37.5" customHeight="1">
       <x:c r="A20" s="10" t="str">
-        <x:v>李映伟</x:v>
+        <x:v>周珍宇</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>华南理工大学</x:v>
+        <x:v>南昌大学</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D20" s="10" t="str">
-        <x:v>MOF基多相催化；能源相关小分子活化；生物质资源催化转化；光/电催化交叉</x:v>
+        <x:v>功能性MOF孔环境设计；乙炔/乙烯及多组分分离；电化学传感器设计；多孔材料电催化</x:v>
       </x:c>
       <x:c r="E20" s="10" t="str">
-        <x:v>采用2024-03-27官方简介；最新课题与招生情况另核。</x:v>
+        <x:v>官网确认2013.09-2016.06在华南理工获硕士学位；尚未据此指定导师。</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
+        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="37.5" customHeight="1">
       <x:c r="A21" s="10" t="str">
-        <x:v>龙金星</x:v>
+        <x:v>崔志明</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -701,18 +720,18 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D21" s="10" t="str">
-        <x:v>离子液体参与的生物质解聚；生物质组分定向解聚；环境友好催化剂结构调控；绿色催化过程及理论基础</x:v>
+        <x:v>固态及复合电解质；锂、石墨与硅基负极；固态软包电池；氢氧电催化与膜电极</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
-        <x:v>姓名是龙金星 Jinxing Long；不要与李映伟、沈葵论文中的 Jilan Long 混为同一人。</x:v>
+        <x:v>官方课题组由崔志明、宋慧宇共同带领；不将团队所有成果归为单人独立工作。</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/zmcui/</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="37.5" customHeight="1">
       <x:c r="A22" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>江焕峰</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -721,18 +740,18 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
-        <x:v>MOF及衍生多孔纳米催化材料；分级孔与沸石结构；单原子和合金限域；CO2还原与水电解；加氢、氧化与生物质转化</x:v>
+        <x:v>绿色有机合成与过渡金属催化；精细化学品与药物中间体；CO2作为羰基源的羧基化</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>官方附件所在页为2021年，论文清单主要截至2020年前后；细分路线属于该资料时段。</x:v>
+        <x:v>当前教师目录链接的简介明确截至2008年，不能当成2026完整画像；另有2025中国化学会报告线索。</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="37.5" customHeight="1">
       <x:c r="A23" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李雪辉</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -741,18 +760,18 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D23" s="10" t="str">
-        <x:v>二维膜的精密构筑；限域分子与离子传质；新型膜与气体分离；盐湖提锂与退役电池回收；战略关键金属纯化</x:v>
+        <x:v>生物质催化转化；绿色催化技术；催化脱硫脱氮；催化塑料降解</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
-        <x:v>采用2024-08-30官方简介。</x:v>
+        <x:v>官网链接到绿色催化与能源课题组；上述是团队声明，个人主持分工待论文与项目核实。</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="37.5" customHeight="1">
       <x:c r="A24" s="10" t="str">
-        <x:v>伍婉卿</x:v>
+        <x:v>李映伟</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -761,18 +780,18 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D24" s="10" t="str">
-        <x:v>催化有机合成方法学；不饱和键化合物高效转化；功能分子及杂环构建；烯烃氧化胺化</x:v>
+        <x:v>MOF基多相催化；能源相关小分子活化；生物质资源催化转化；光/电催化交叉</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
-        <x:v>采用2024-03-21公开简介。</x:v>
+        <x:v>采用2024-03-27官方简介；最新课题与招生情况另核。</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="51" customHeight="1">
       <x:c r="A25" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -781,18 +800,18 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D25" s="10" t="str">
-        <x:v>轻烃与烷烃异构体分离；超纯气体与Ar/O2分离；CO2捕获；VOCs净化与低温脱硝；碳基储能材料</x:v>
+        <x:v>光子带隙、波导与单向态；等离激元共振与增强光谱；非线性频率转换与白光激光；光镊与金属颗粒操控；微纳光学计算与成像方法</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
-        <x:v>采用2024年官方简历，含2024-2027项目；项目结束时间不代表已完成。</x:v>
+        <x:v>官网代表作清单全部收录49篇，另补2篇学校近期报道，合计51篇。来源有界清单，非论文全集。任职/职称按采集日网页表述；不以现单位回填早期论文单位。</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="37.5" customHeight="1">
       <x:c r="A26" s="10" t="str">
-        <x:v>祝诗发</x:v>
+        <x:v>龙金星</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
         <x:v>华南理工大学</x:v>
@@ -801,199 +820,359 @@
         <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D26" s="10" t="str">
-        <x:v>炔烃化学与乙炔转化；过渡金属催化新转化；可见光催化；不对称合成与天然产物全合成</x:v>
+        <x:v>离子液体参与的生物质解聚；生物质组分定向解聚；环境友好催化剂结构调控；绿色催化过程及理论基础</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
-        <x:v>方向为课题组公开声明；具体个人贡献须逐篇核实。</x:v>
+        <x:v>姓名是龙金星 Jinxing Long；不要与李映伟、沈葵论文中的 Jilan Long 混为同一人。</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="51" customHeight="1">
       <x:c r="A27" s="10" t="str">
-        <x:v>樊栓狮</x:v>
+        <x:v>梅军</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D27" s="10" t="str">
-        <x:v>天然气水合物原理与应用；天然气及LNG储运；储能与节能空调；可再生能源与新能源利用</x:v>
+        <x:v>低频吸声与声学有效介质；声子晶体狄拉克锥与拓扑态；超格栅逆向设计与声路复用；水声与弹性波超分辨聚焦</x:v>
       </x:c>
       <x:c r="E27" s="10" t="str">
-        <x:v>采用2024年目录附件，具体课题阶段仍需逐项追踪。</x:v>
+        <x:v>官网未提供逐篇列表，本轮按出版社署名/单位证据收录14篇（2012—2026），非完整发表集合。任职/职称按采集日网页表述；不以现单位回填早期论文单位。</x:v>
       </x:c>
       <x:c r="F27" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13954a233585/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="37.5" customHeight="1">
       <x:c r="A28" s="10" t="str">
-        <x:v>林东恩</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D28" s="10" t="str">
-        <x:v>嘌呤与抗病毒药物骨架；可见光介导绿色氧化偶联；环氧树脂、固化剂与光固化树脂；日化与陶瓷化学品配方</x:v>
+        <x:v>MOF及衍生多孔纳米催化材料；分级孔与沸石结构；单原子和合金限域；CO2还原与水电解；加氢、氧化与生物质转化</x:v>
       </x:c>
       <x:c r="E28" s="10" t="str">
-        <x:v>采用2024年个人简介；配方研究和药物合成分别记录。</x:v>
+        <x:v>官方附件所在页为2021年，论文清单主要截至2020年前后；细分路线属于该资料时段。</x:v>
       </x:c>
       <x:c r="F28" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5" customHeight="1">
       <x:c r="A29" s="10" t="str">
-        <x:v>欧阳新平</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
-        <x:v>木质素基精细化学品；木质素解聚与单酚分离；工业配方与材料应用</x:v>
+        <x:v>二维膜的精密构筑；限域分子与离子传质；新型膜与气体分离；盐湖提锂与退役电池回收；战略关键金属纯化</x:v>
       </x:c>
       <x:c r="E29" s="10" t="str">
-        <x:v>附件论文主要在2009-2011年前后；需刷新近五年方向及现职信息。</x:v>
+        <x:v>采用2024-08-30官方简介。</x:v>
       </x:c>
       <x:c r="F29" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="37.5" customHeight="1">
       <x:c r="A30" s="10" t="str">
-        <x:v>王立世</x:v>
+        <x:v>吴宏滨</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D30" s="10" t="str">
-        <x:v>纳米材料电分析应用；电分析理论与新方法；分析仪器研制</x:v>
+        <x:v>有机太阳电池界面与能量损失；有机发光与短波红外器件；器件物理与光生电荷动力学</x:v>
       </x:c>
       <x:c r="E30" s="10" t="str">
-        <x:v>官方目录仍列名，但所链接简介含2009年前后论文；近期方向、任职和招生均需刷新。</x:v>
+        <x:v>官网代表作清单全部收录10篇。来源有界清单，非论文全集。任职/职称按采集日网页表述；不以现单位回填早期论文单位。</x:v>
       </x:c>
       <x:c r="F30" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="51" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="37.5" customHeight="1">
       <x:c r="A31" s="10" t="str">
-        <x:v>奚红霞</x:v>
+        <x:v>伍婉卿</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D31" s="10" t="str">
-        <x:v>环境能源功能材料结构调控；结构建模与构效关系；传质与分离工程</x:v>
+        <x:v>催化有机合成方法学；不饱和键化合物高效转化；功能分子及杂环构建；烯烃氧化胺化</x:v>
       </x:c>
       <x:c r="E31" s="10" t="str">
-        <x:v>页面标注2015年，附件含2017年论文；存在时间信息不一致，作为历史方向入口。 附件硕士与博士起止年均写1993-1996，履历时间存在冲突，留待原始履历核实。</x:v>
+        <x:v>采用2024-03-21公开简介。</x:v>
       </x:c>
       <x:c r="F31" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="37.5" customHeight="1">
       <x:c r="A32" s="10" t="str">
-        <x:v>肖静</x:v>
+        <x:v>夏启斌</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D32" s="10" t="str">
-        <x:v>清洁燃料脱硫脱氮；CO2等气体吸附分离；吸附分离过程设计；水体有机微污染与环境催化</x:v>
+        <x:v>轻烃与烷烃异构体分离；超纯气体与Ar/O2分离；CO2捕获；VOCs净化与低温脱硝；碳基储能材料</x:v>
       </x:c>
       <x:c r="E32" s="10" t="str">
-        <x:v>官方附件内容偏早期，具体近期课题需补查。</x:v>
+        <x:v>采用2024年官方简历，含2024-2027项目；项目结束时间不代表已完成。</x:v>
       </x:c>
       <x:c r="F32" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="51" customHeight="1">
       <x:c r="A33" s="10" t="str">
-        <x:v>杨思宇</x:v>
+        <x:v>张煜然</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D33" s="10" t="str">
-        <x:v>风光煤多能耦合化工转化；AI辅助多物理场建模；微纳尺度传质传热建模；绿电-氢能-工业耦合网络</x:v>
+        <x:v>量子计量与多参数估计；量子模拟、热化与信息传播；非厄米拓扑与开放量子系统；量子资源与拓扑纠缠</x:v>
       </x:c>
       <x:c r="E33" s="10" t="str">
-        <x:v>页面创建于2022年，但正文已列2025.09研究员履历；两种日期分别保留。</x:v>
+        <x:v>官网代表作清单全部收录20篇。来源有界清单，非论文全集。代表作截至2022，未覆盖2023加入华工后的完整产出。任职/职称按采集日网页表述；不以现单位回填早期论文单位。</x:v>
       </x:c>
       <x:c r="F33" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="37.5" customHeight="1">
       <x:c r="A34" s="10" t="str">
-        <x:v>张正国</x:v>
+        <x:v>祝诗发</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
         <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>扩展比较</x:v>
+        <x:v>第一圈延伸</x:v>
       </x:c>
       <x:c r="D34" s="10" t="str">
-        <x:v>传热表界面与高效换热器；复合相变储热材料；电子器件与动力电池热管理；太阳能、建筑与热泵节能</x:v>
+        <x:v>炔烃化学与乙炔转化；过渡金属催化新转化；可见光催化；不对称合成与天然产物全合成</x:v>
       </x:c>
       <x:c r="E34" s="10" t="str">
-        <x:v>采用2024年官方简介。</x:v>
+        <x:v>方向为课题组公开声明；具体个人贡献须逐篇核实。</x:v>
       </x:c>
       <x:c r="F34" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="37.5" customHeight="1">
       <x:c r="A35" s="10" t="str">
-        <x:v>邢华斌</x:v>
+        <x:v>樊栓狮</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>浙江大学</x:v>
+        <x:v>华南理工大学</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
         <x:v>扩展比较</x:v>
       </x:c>
       <x:c r="D35" s="10" t="str">
+        <x:v>天然气水合物原理与应用；天然气及LNG储运；储能与节能空调；可再生能源与新能源利用</x:v>
+      </x:c>
+      <x:c r="E35" s="10" t="str">
+        <x:v>采用2024年目录附件，具体课题阶段仍需逐项追踪。</x:v>
+      </x:c>
+      <x:c r="F35" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="37.5" customHeight="1">
+      <x:c r="A36" s="10" t="str">
+        <x:v>林东恩</x:v>
+      </x:c>
+      <x:c r="B36" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D36" s="10" t="str">
+        <x:v>嘌呤与抗病毒药物骨架；可见光介导绿色氧化偶联；环氧树脂、固化剂与光固化树脂；日化与陶瓷化学品配方</x:v>
+      </x:c>
+      <x:c r="E36" s="10" t="str">
+        <x:v>采用2024年个人简介；配方研究和药物合成分别记录。</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="37.5" customHeight="1">
+      <x:c r="A37" s="10" t="str">
+        <x:v>欧阳新平</x:v>
+      </x:c>
+      <x:c r="B37" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="str">
+        <x:v>木质素基精细化学品；木质素解聚与单酚分离；工业配方与材料应用</x:v>
+      </x:c>
+      <x:c r="E37" s="10" t="str">
+        <x:v>附件论文主要在2009-2011年前后；需刷新近五年方向及现职信息。</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="37.5" customHeight="1">
+      <x:c r="A38" s="10" t="str">
+        <x:v>王立世</x:v>
+      </x:c>
+      <x:c r="B38" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="str">
+        <x:v>纳米材料电分析应用；电分析理论与新方法；分析仪器研制</x:v>
+      </x:c>
+      <x:c r="E38" s="10" t="str">
+        <x:v>官方目录仍列名，但所链接简介含2009年前后论文；近期方向、任职和招生均需刷新。</x:v>
+      </x:c>
+      <x:c r="F38" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="51" customHeight="1">
+      <x:c r="A39" s="10" t="str">
+        <x:v>奚红霞</x:v>
+      </x:c>
+      <x:c r="B39" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="str">
+        <x:v>环境能源功能材料结构调控；结构建模与构效关系；传质与分离工程</x:v>
+      </x:c>
+      <x:c r="E39" s="10" t="str">
+        <x:v>页面标注2015年，附件含2017年论文；存在时间信息不一致，作为历史方向入口。 附件硕士与博士起止年均写1993-1996，履历时间存在冲突，留待原始履历核实。</x:v>
+      </x:c>
+      <x:c r="F39" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="37.5" customHeight="1">
+      <x:c r="A40" s="10" t="str">
+        <x:v>肖静</x:v>
+      </x:c>
+      <x:c r="B40" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="str">
+        <x:v>清洁燃料脱硫脱氮；CO2等气体吸附分离；吸附分离过程设计；水体有机微污染与环境催化</x:v>
+      </x:c>
+      <x:c r="E40" s="10" t="str">
+        <x:v>官方附件内容偏早期，具体近期课题需补查。</x:v>
+      </x:c>
+      <x:c r="F40" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="37.5" customHeight="1">
+      <x:c r="A41" s="10" t="str">
+        <x:v>杨思宇</x:v>
+      </x:c>
+      <x:c r="B41" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="str">
+        <x:v>风光煤多能耦合化工转化；AI辅助多物理场建模；微纳尺度传质传热建模；绿电-氢能-工业耦合网络</x:v>
+      </x:c>
+      <x:c r="E41" s="10" t="str">
+        <x:v>页面创建于2022年，但正文已列2025.09研究员履历；两种日期分别保留。</x:v>
+      </x:c>
+      <x:c r="F41" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="37.5" customHeight="1">
+      <x:c r="A42" s="10" t="str">
+        <x:v>张正国</x:v>
+      </x:c>
+      <x:c r="B42" s="10" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D42" s="10" t="str">
+        <x:v>传热表界面与高效换热器；复合相变储热材料；电子器件与动力电池热管理；太阳能、建筑与热泵节能</x:v>
+      </x:c>
+      <x:c r="E42" s="10" t="str">
+        <x:v>采用2024年官方简介。</x:v>
+      </x:c>
+      <x:c r="F42" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="37.5" customHeight="1">
+      <x:c r="A43" s="10" t="str">
+        <x:v>邢华斌</x:v>
+      </x:c>
+      <x:c r="B43" s="10" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>扩展比较</x:v>
+      </x:c>
+      <x:c r="D43" s="10" t="str">
         <x:v>高纯分离工程；电子化学材料与纯化；吸附分离材料设计；丙烯/丙烷精准筛分</x:v>
       </x:c>
-      <x:c r="E35" s="10" t="str">
+      <x:c r="E43" s="10" t="str">
         <x:v>官方方向已定位；近五年活跃性待论文核实。</x:v>
       </x:c>
-      <x:c r="F35" s="10" t="str">
+      <x:c r="F43" s="10" t="str">
         <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R402295d148c54248"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf06fb482854049ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1036,7 +1215,7 @@
     </x:row>
     <x:row r="3" ht="19.5" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>127条方向；问题用于后续阅读，尚未声称所有方法均由本人使用。</x:v>
+        <x:v>157条方向；问题与方法用于后续阅读核验。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -2183,1825 +2362,8543 @@
     </x:row>
     <x:row r="54" ht="37.5" customHeight="1">
       <x:c r="A54" s="10" t="str">
-        <x:v>周珍宇</x:v>
+        <x:v>舒富文</x:v>
       </x:c>
       <x:c r="B54" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>功能性MOF孔环境设计</x:v>
+        <x:v>黑洞信息、全息纠缠与量子引力</x:v>
       </x:c>
       <x:c r="D54" s="10" t="str">
-        <x:v>MOF；孔内电场；穿插结构</x:v>
+        <x:v>黑洞；纠缠岛；Page曲线</x:v>
       </x:c>
       <x:c r="E54" s="10" t="str">
-        <x:v>孔几何和电场如何共同决定分子识别？</x:v>
+        <x:v>纠缠岛处方在不同黑洞背景下何时成立，能否在幺正性和熵不等式上相容？</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
-        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="37.5" customHeight="1">
       <x:c r="A55" s="10" t="str">
-        <x:v>周珍宇</x:v>
+        <x:v>舒富文</x:v>
       </x:c>
       <x:c r="B55" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>乙炔/乙烯及多组分分离</x:v>
+        <x:v>修正引力与引力波检验</x:v>
       </x:c>
       <x:c r="D55" s="10" t="str">
-        <x:v>C2H2/C2H4；三元气体</x:v>
+        <x:v>Einstein-Gauss-Bonnet引力；引力波；原初黑洞</x:v>
       </x:c>
       <x:c r="E55" s="10" t="str">
-        <x:v>材料筛分是否能在混合气与循环条件下成立？</x:v>
+        <x:v>理论稳定性条件怎样进入可观测约束？引力波检验依赖哪些波形、系统参数和近似？</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
         <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="37.5" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="33" customHeight="1">
       <x:c r="A56" s="10" t="str">
-        <x:v>周珍宇</x:v>
+        <x:v>舒富文</x:v>
       </x:c>
       <x:c r="B56" s="10" t="str">
-        <x:v>分析化学与传感</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>电化学传感器设计</x:v>
+        <x:v>量子信息方法与引力诱导纠缠</x:v>
       </x:c>
       <x:c r="D56" s="10" t="str">
-        <x:v>MOF基传感材料</x:v>
+        <x:v>MERA张量网络；bit threads；微观质量体</x:v>
       </x:c>
       <x:c r="E56" s="10" t="str">
-        <x:v>选择性识别和电子传递之间怎样衔接？</x:v>
+        <x:v>纠缠量、背景曲率与维度假设分别怎样改变预测？</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="37.5" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="33" customHeight="1">
       <x:c r="A57" s="10" t="str">
-        <x:v>周珍宇</x:v>
+        <x:v>王俊波</x:v>
       </x:c>
       <x:c r="B57" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>低维凝聚态与表界面物理</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>多孔材料电催化</x:v>
+        <x:v>金属表面反应路径与自由基转移</x:v>
       </x:c>
       <x:c r="D57" s="10" t="str">
-        <x:v>MOF基电催化材料</x:v>
+        <x:v>Ag(111)；Cu(111)；Au(111)；有机前驱体</x:v>
       </x:c>
       <x:c r="E57" s="10" t="str">
-        <x:v>具体反应和工作活性相需要哪些原文证据？</x:v>
+        <x:v>如何把基底屏蔽、分子构型与自由基转移对反应选择性的作用分开？</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="37.5" customHeight="1">
       <x:c r="A58" s="10" t="str">
-        <x:v>崔志明</x:v>
+        <x:v>王俊波</x:v>
       </x:c>
       <x:c r="B58" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>低维凝聚态与表界面物理</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>固态及复合电解质</x:v>
+        <x:v>二维Kagome与共价/金属有机结构构筑</x:v>
       </x:c>
       <x:c r="D58" s="10" t="str">
-        <x:v>氧化物；聚合物复合物；凝胶；硫化物界面</x:v>
+        <x:v>Kagome晶格；金属有机网络</x:v>
       </x:c>
       <x:c r="E58" s="10" t="str">
-        <x:v>离子传输、机械性能和界面稳定如何兼顾？</x:v>
+        <x:v>几何晶格形成、稳定与可转移性是否同时成立？结构不能直接等同于电子拓扑性质。</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="37.5" customHeight="1">
       <x:c r="A59" s="10" t="str">
-        <x:v>崔志明</x:v>
+        <x:v>王俊波</x:v>
       </x:c>
       <x:c r="B59" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>低维凝聚态与表界面物理</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>锂、石墨与硅基负极</x:v>
+        <x:v>实空间表征与多尺度手性传递</x:v>
       </x:c>
       <x:c r="D59" s="10" t="str">
-        <x:v>锂金属；高载石墨；硅基负极</x:v>
+        <x:v>STM；XPS；DFT；氢键与卤键</x:v>
       </x:c>
       <x:c r="E59" s="10" t="str">
-        <x:v>在真实负载和有限锂条件下循环是否稳定？</x:v>
+        <x:v>哪些中间体被直接观察，哪些来自计算；分子尺度结构如何传到介观尺度？</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="33" customHeight="1">
       <x:c r="A60" s="10" t="str">
-        <x:v>崔志明</x:v>
+        <x:v>王启胜</x:v>
       </x:c>
       <x:c r="B60" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>低维凝聚态与表界面物理</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>固态软包电池</x:v>
+        <x:v>低维拓扑与范德华材料输运</x:v>
       </x:c>
       <x:c r="D60" s="10" t="str">
-        <x:v>软包电池；电解质-电极组合</x:v>
+        <x:v>SnTe/PbSnTe；WTe2；二维碲</x:v>
       </x:c>
       <x:c r="E60" s="10" t="str">
-        <x:v>材料指标怎样转化为器件能量密度与寿命？</x:v>
+        <x:v>如何区分表面/体态输运、晶体各向异性与界面效应？</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/092809/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm
+https://www.x-mol.com/groups/wang_qisheng/publications</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="37.5" customHeight="1">
       <x:c r="A61" s="10" t="str">
-        <x:v>崔志明</x:v>
+        <x:v>王启胜</x:v>
       </x:c>
       <x:c r="B61" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>半导体材料与光电器件</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>氢氧电催化与膜电极</x:v>
+        <x:v>铅盐半导体热载流子与红外探测</x:v>
       </x:c>
       <x:c r="D61" s="10" t="str">
-        <x:v>金属间化合物；介孔碳载体；三相界面</x:v>
+        <x:v>PbS；PbSe；声子瓶颈</x:v>
       </x:c>
       <x:c r="E61" s="10" t="str">
-        <x:v>活性、传荷传质和规模制备怎样协同？</x:v>
+        <x:v>增益、响应时间、噪声与工作温度如何权衡，热扩散长度是否有独立实验支撑？</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/092809/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm
+https://www.x-mol.com/groups/wang_qisheng/publications</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="37.5" customHeight="1">
       <x:c r="A62" s="10" t="str">
-        <x:v>江焕峰</x:v>
+        <x:v>王启胜</x:v>
       </x:c>
       <x:c r="B62" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>绿色有机合成与过渡金属催化</x:v>
+        <x:v>非易失光存储与可重构感存算</x:v>
       </x:c>
       <x:c r="D62" s="10" t="str">
-        <x:v>碳碳键构建；环境友好介质</x:v>
+        <x:v>MoS2/PbS；Si/CuO；离子插层</x:v>
       </x:c>
       <x:c r="E62" s="10" t="str">
-        <x:v>反应创新如何减少步骤、氧化剂和分离负担？</x:v>
+        <x:v>器件存储态、能耗与循环稳定性如何连接具体计算任务？</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>历史官方资料</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
+        <x:v>https://teacher.ncu.edu.cn/publish/092809/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm
+https://www.x-mol.com/groups/wang_qisheng/publications</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="37.5" customHeight="1">
       <x:c r="A63" s="10" t="str">
-        <x:v>江焕峰</x:v>
+        <x:v>王启胜</x:v>
       </x:c>
       <x:c r="B63" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>半导体材料与光电器件</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>精细化学品与药物中间体</x:v>
+        <x:v>光热电定位、成像与信息编码</x:v>
       </x:c>
       <x:c r="D63" s="10" t="str">
-        <x:v>天然资源；药物中间体</x:v>
+        <x:v>位置敏感探测器；光学定位；图像编码</x:v>
       </x:c>
       <x:c r="E63" s="10" t="str">
-        <x:v>方法学是否支持可放大且可分离的制备路线？</x:v>
+        <x:v>位置/图像精度与光谱、入射功率、温漂、算法训练集之间有什么依赖？</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>历史官方资料</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/092809/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm
+https://www.x-mol.com/groups/wang_qisheng/publications</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="37.5" customHeight="1">
       <x:c r="A64" s="10" t="str">
-        <x:v>江焕峰</x:v>
+        <x:v>于天宝</x:v>
       </x:c>
       <x:c r="B64" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>CO2作为羰基源的羧基化</x:v>
+        <x:v>拓扑光子/声光子晶体与波导</x:v>
       </x:c>
       <x:c r="D64" s="10" t="str">
-        <x:v>CO2；羧基化反应</x:v>
+        <x:v>光子晶体；角态；声光子晶体</x:v>
       </x:c>
       <x:c r="E64" s="10" t="str">
-        <x:v>CO2活化与新键形成如何耦合？</x:v>
+        <x:v>拓扑不变量、边界条件与实际缺陷容忍度之间如何对应？</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>官方学术报告线索</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>https://www.chemsoc.org.cn/a6519.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="37.5" customHeight="1">
       <x:c r="A65" s="10" t="str">
-        <x:v>李雪辉</x:v>
+        <x:v>于天宝</x:v>
       </x:c>
       <x:c r="B65" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>生物质催化转化</x:v>
+        <x:v>准连续谱束缚态与光物质耦合</x:v>
       </x:c>
       <x:c r="D65" s="10" t="str">
-        <x:v>生物质；绿色催化体系</x:v>
+        <x:v>准BIC；激子；磁光效应</x:v>
       </x:c>
       <x:c r="E65" s="10" t="str">
-        <x:v>原料组分与催化体系怎样决定产物路线？</x:v>
+        <x:v>高Q共振、模式重叠与损耗如何共同决定强耦合和磁光增强？</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="37.5" customHeight="1">
       <x:c r="A66" s="10" t="str">
-        <x:v>李雪辉</x:v>
+        <x:v>于天宝</x:v>
       </x:c>
       <x:c r="B66" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>绿色催化技术</x:v>
+        <x:v>衍射光网络与光电协同计算</x:v>
       </x:c>
       <x:c r="D66" s="10" t="str">
-        <x:v>新型催化材料与过程</x:v>
+        <x:v>超表面；衍射网络；光电GAN</x:v>
       </x:c>
       <x:c r="E66" s="10" t="str">
-        <x:v>绿色性是否有物料、能量与溶剂使用证据？</x:v>
+        <x:v>性能优势在什么光学尺寸、训练代价、探测噪声及基线比较条件下成立？</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="37.5" customHeight="1">
       <x:c r="A67" s="10" t="str">
-        <x:v>李雪辉</x:v>
+        <x:v>于天宝</x:v>
       </x:c>
       <x:c r="B67" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>催化脱硫脱氮</x:v>
+        <x:v>结构光场与光学计量成像</x:v>
       </x:c>
       <x:c r="D67" s="10" t="str">
-        <x:v>含硫/含氮化合物</x:v>
+        <x:v>光学斯格明子；相干性；非视距成像</x:v>
       </x:c>
       <x:c r="E67" s="10" t="str">
-        <x:v>选择性脱除是否伴随催化剂失活或副产物？</x:v>
+        <x:v>光场拓扑与相干性可以怎样转化为可校准的位移或成像信息？</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="33" customHeight="1">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://spms.ncu.edu.cn/szdw/zzjs/wlx.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="37.5" customHeight="1">
       <x:c r="A68" s="10" t="str">
-        <x:v>李雪辉</x:v>
+        <x:v>周珍宇</x:v>
       </x:c>
       <x:c r="B68" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
+        <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>催化塑料降解</x:v>
+        <x:v>功能性MOF孔环境设计</x:v>
       </x:c>
       <x:c r="D68" s="10" t="str">
-        <x:v>废塑料；催化解聚</x:v>
+        <x:v>MOF；孔内电场；穿插结构</x:v>
       </x:c>
       <x:c r="E68" s="10" t="str">
-        <x:v>混合原料和添加剂如何影响产物与回收价值？</x:v>
+        <x:v>孔几何和电场如何共同决定分子识别？</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="33" customHeight="1">
+        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="37.5" customHeight="1">
       <x:c r="A69" s="10" t="str">
-        <x:v>李映伟</x:v>
+        <x:v>周珍宇</x:v>
       </x:c>
       <x:c r="B69" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>MOF基多相催化</x:v>
+        <x:v>乙炔/乙烯及多组分分离</x:v>
       </x:c>
       <x:c r="D69" s="10" t="str">
-        <x:v>MOF；孔内催化位点</x:v>
+        <x:v>C2H2/C2H4；三元气体</x:v>
       </x:c>
       <x:c r="E69" s="10" t="str">
-        <x:v>孔结构和催化中心如何共同决定反应路径？</x:v>
+        <x:v>材料筛分是否能在混合气与循环条件下成立？</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="33" customHeight="1">
+        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="37.5" customHeight="1">
       <x:c r="A70" s="10" t="str">
-        <x:v>李映伟</x:v>
+        <x:v>周珍宇</x:v>
       </x:c>
       <x:c r="B70" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>分析化学与传感</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>能源相关小分子活化</x:v>
+        <x:v>电化学传感器设计</x:v>
       </x:c>
       <x:c r="D70" s="10" t="str">
-        <x:v>能源相关小分子</x:v>
+        <x:v>MOF基传感材料</x:v>
       </x:c>
       <x:c r="E70" s="10" t="str">
-        <x:v>具体底物、目标产物和限速步骤是什么？</x:v>
+        <x:v>选择性识别和电子传递之间怎样衔接？</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="33" customHeight="1">
+        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="37.5" customHeight="1">
       <x:c r="A71" s="10" t="str">
-        <x:v>李映伟</x:v>
+        <x:v>周珍宇</x:v>
       </x:c>
       <x:c r="B71" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>生物质资源催化转化</x:v>
+        <x:v>多孔材料电催化</x:v>
       </x:c>
       <x:c r="D71" s="10" t="str">
-        <x:v>生物质及衍生平台分子</x:v>
+        <x:v>MOF基电催化材料</x:v>
       </x:c>
       <x:c r="E71" s="10" t="str">
-        <x:v>位点设计能否改善复杂底物的选择性？</x:v>
+        <x:v>具体反应和工作活性相需要哪些原文证据？</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
+        <x:v>https://chem.ncu.edu.cn/article.jsp?urltype=news.NewsContentUrl&amp;wbnewsid=11071&amp;wbtreeid=1411</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="33" customHeight="1">
       <x:c r="A72" s="10" t="str">
-        <x:v>李映伟</x:v>
+        <x:v>崔志明</x:v>
       </x:c>
       <x:c r="B72" s="10" t="str">
         <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>光/电催化交叉</x:v>
+        <x:v>固态及复合电解质</x:v>
       </x:c>
       <x:c r="D72" s="10" t="str">
-        <x:v>多孔材料；光电催化体系</x:v>
+        <x:v>氧化物；聚合物复合物；凝胶；硫化物界面</x:v>
       </x:c>
       <x:c r="E72" s="10" t="str">
-        <x:v>如何区别光吸收、电荷输运与化学活性贡献？</x:v>
+        <x:v>离子传输、机械性能和界面稳定如何兼顾？</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="33" customHeight="1">
       <x:c r="A73" s="10" t="str">
-        <x:v>龙金星</x:v>
+        <x:v>崔志明</x:v>
       </x:c>
       <x:c r="B73" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>离子液体参与的生物质解聚</x:v>
+        <x:v>锂、石墨与硅基负极</x:v>
       </x:c>
       <x:c r="D73" s="10" t="str">
-        <x:v>离子液体；生物质</x:v>
+        <x:v>锂金属；高载石墨；硅基负极</x:v>
       </x:c>
       <x:c r="E73" s="10" t="str">
-        <x:v>溶剂、酸碱性与催化位点作用如何拆分？</x:v>
+        <x:v>在真实负载和有限锂条件下循环是否稳定？</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="33" customHeight="1">
       <x:c r="A74" s="10" t="str">
-        <x:v>龙金星</x:v>
+        <x:v>崔志明</x:v>
       </x:c>
       <x:c r="B74" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
-        <x:v>生物质组分定向解聚</x:v>
+        <x:v>固态软包电池</x:v>
       </x:c>
       <x:c r="D74" s="10" t="str">
-        <x:v>生物质组分；定向产物</x:v>
+        <x:v>软包电池；电解质-电极组合</x:v>
       </x:c>
       <x:c r="E74" s="10" t="str">
-        <x:v>怎样抑制二次缩合并保留目标结构？</x:v>
+        <x:v>材料指标怎样转化为器件能量密度与寿命？</x:v>
       </x:c>
       <x:c r="F74" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G74" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="33" customHeight="1">
       <x:c r="A75" s="10" t="str">
-        <x:v>龙金星</x:v>
+        <x:v>崔志明</x:v>
       </x:c>
       <x:c r="B75" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
-        <x:v>环境友好催化剂结构调控</x:v>
+        <x:v>氢氧电催化与膜电极</x:v>
       </x:c>
       <x:c r="D75" s="10" t="str">
-        <x:v>催化新材料；精细结构</x:v>
+        <x:v>金属间化合物；介孔碳载体；三相界面</x:v>
       </x:c>
       <x:c r="E75" s="10" t="str">
-        <x:v>结构变化与性能提升是否有独立机理证据？</x:v>
+        <x:v>活性、传荷传质和规模制备怎样协同？</x:v>
       </x:c>
       <x:c r="F75" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G75" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/zmcui/yjnr/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="37.5" customHeight="1">
       <x:c r="A76" s="10" t="str">
-        <x:v>龙金星</x:v>
+        <x:v>江焕峰</x:v>
       </x:c>
       <x:c r="B76" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
-        <x:v>绿色催化过程及理论基础</x:v>
+        <x:v>绿色有机合成与过渡金属催化</x:v>
       </x:c>
       <x:c r="D76" s="10" t="str">
-        <x:v>催化过程；资源化流程</x:v>
+        <x:v>碳碳键构建；环境友好介质</x:v>
       </x:c>
       <x:c r="E76" s="10" t="str">
-        <x:v>催化结果如何纳入溶剂回收与全流程评价？</x:v>
+        <x:v>反应创新如何减少步骤、氧化剂和分离负担？</x:v>
       </x:c>
       <x:c r="F76" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>历史官方资料</x:v>
       </x:c>
       <x:c r="G76" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="37.5" customHeight="1">
       <x:c r="A77" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>江焕峰</x:v>
       </x:c>
       <x:c r="B77" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
-        <x:v>MOF及衍生多孔纳米催化材料</x:v>
+        <x:v>精细化学品与药物中间体</x:v>
       </x:c>
       <x:c r="D77" s="10" t="str">
-        <x:v>MOF；衍生碳；金属纳米颗粒</x:v>
+        <x:v>天然资源；药物中间体</x:v>
       </x:c>
       <x:c r="E77" s="10" t="str">
-        <x:v>前驱体结构在衍生后保留了哪些功能？</x:v>
+        <x:v>方法学是否支持可放大且可分离的制备路线？</x:v>
       </x:c>
       <x:c r="F77" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>历史官方资料</x:v>
       </x:c>
       <x:c r="G77" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/00/19/9f0b7a784d30b6c3eafe49f226f7/eca85a16-5508-4799-b106-110719adfdda.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="33" customHeight="1">
       <x:c r="A78" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>江焕峰</x:v>
       </x:c>
       <x:c r="B78" s="10" t="str">
         <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>分级孔与沸石结构</x:v>
+        <x:v>CO2作为羰基源的羧基化</x:v>
       </x:c>
       <x:c r="D78" s="10" t="str">
-        <x:v>有序大/微孔；分子筛；沸石</x:v>
+        <x:v>CO2；羧基化反应</x:v>
       </x:c>
       <x:c r="E78" s="10" t="str">
-        <x:v>传质改善与活性位变化如何分开验证？</x:v>
+        <x:v>CO2活化与新键形成如何耦合？</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官方学术报告线索</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>https://www.chemsoc.org.cn/a6519.html</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="33" customHeight="1">
       <x:c r="A79" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>李雪辉</x:v>
       </x:c>
       <x:c r="B79" s="10" t="str">
         <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>单原子和合金限域</x:v>
+        <x:v>生物质催化转化</x:v>
       </x:c>
       <x:c r="D79" s="10" t="str">
-        <x:v>单原子；超细合金颗粒；孔内封装</x:v>
+        <x:v>生物质；绿色催化体系</x:v>
       </x:c>
       <x:c r="E79" s="10" t="str">
-        <x:v>局部配位和空间限域如何控制稳定性？</x:v>
+        <x:v>原料组分与催化体系怎样决定产物路线？</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>官网代表成果线索</x:v>
+        <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G79" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="33" customHeight="1">
       <x:c r="A80" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>李雪辉</x:v>
       </x:c>
       <x:c r="B80" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>CO2还原与水电解</x:v>
+        <x:v>绿色催化技术</x:v>
       </x:c>
       <x:c r="D80" s="10" t="str">
-        <x:v>CO2电还原；HER/OER</x:v>
+        <x:v>新型催化材料与过程</x:v>
       </x:c>
       <x:c r="E80" s="10" t="str">
-        <x:v>材料结构设计能否兼顾活性、选择性与耐久？</x:v>
+        <x:v>绿色性是否有物料、能量与溶剂使用证据？</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="33" customHeight="1">
       <x:c r="A81" s="10" t="str">
-        <x:v>沈葵</x:v>
+        <x:v>李雪辉</x:v>
       </x:c>
       <x:c r="B81" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>环境治理与资源循环</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>加氢、氧化与生物质转化</x:v>
+        <x:v>催化脱硫脱氮</x:v>
       </x:c>
       <x:c r="D81" s="10" t="str">
-        <x:v>多相催化体系</x:v>
+        <x:v>含硫/含氮化合物</x:v>
       </x:c>
       <x:c r="E81" s="10" t="str">
-        <x:v>不同反应共享哪些可迁移的材料设计规律？</x:v>
+        <x:v>选择性脱除是否伴随催化剂失活或副产物？</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="33" customHeight="1">
       <x:c r="A82" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李雪辉</x:v>
       </x:c>
       <x:c r="B82" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>环境治理与资源循环</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>二维膜的精密构筑</x:v>
+        <x:v>催化塑料降解</x:v>
       </x:c>
       <x:c r="D82" s="10" t="str">
-        <x:v>MXene；二维材料膜</x:v>
+        <x:v>废塑料；催化解聚</x:v>
       </x:c>
       <x:c r="E82" s="10" t="str">
-        <x:v>层间距、缺陷和堆叠方式如何决定实际通量与选择性？</x:v>
+        <x:v>混合原料和添加剂如何影响产物与回收价值？</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/cgce/main.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="33" customHeight="1">
       <x:c r="A83" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李映伟</x:v>
       </x:c>
       <x:c r="B83" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>限域分子与离子传质</x:v>
+        <x:v>MOF基多相催化</x:v>
       </x:c>
       <x:c r="D83" s="10" t="str">
-        <x:v>分子；离子；限域孔道</x:v>
+        <x:v>MOF；孔内催化位点</x:v>
       </x:c>
       <x:c r="E83" s="10" t="str">
-        <x:v>尺寸、水合与电荷作用在何种条件下占主导？</x:v>
+        <x:v>孔结构和催化中心如何共同决定反应路径？</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="33" customHeight="1">
       <x:c r="A84" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李映伟</x:v>
       </x:c>
       <x:c r="B84" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>新型膜与气体分离</x:v>
+        <x:v>能源相关小分子活化</x:v>
       </x:c>
       <x:c r="D84" s="10" t="str">
-        <x:v>MOF/COF膜；混合基质膜；纳滤膜</x:v>
+        <x:v>能源相关小分子</x:v>
       </x:c>
       <x:c r="E84" s="10" t="str">
-        <x:v>材料性能如何保持到支撑膜与实际组件？</x:v>
+        <x:v>具体底物、目标产物和限速步骤是什么？</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="33" customHeight="1">
       <x:c r="A85" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李映伟</x:v>
       </x:c>
       <x:c r="B85" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>盐湖提锂与退役电池回收</x:v>
+        <x:v>生物质资源催化转化</x:v>
       </x:c>
       <x:c r="D85" s="10" t="str">
-        <x:v>锂离子；盐湖；退役动力电池</x:v>
+        <x:v>生物质及衍生平台分子</x:v>
       </x:c>
       <x:c r="E85" s="10" t="str">
-        <x:v>复杂离子共存下选择性、通量与回收率如何权衡？</x:v>
+        <x:v>位点设计能否改善复杂底物的选择性？</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="33" customHeight="1">
       <x:c r="A86" s="10" t="str">
-        <x:v>魏嫣莹</x:v>
+        <x:v>李映伟</x:v>
       </x:c>
       <x:c r="B86" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>战略关键金属纯化</x:v>
+        <x:v>光/电催化交叉</x:v>
       </x:c>
       <x:c r="D86" s="10" t="str">
-        <x:v>关键金属；分离与高值利用</x:v>
+        <x:v>多孔材料；光电催化体系</x:v>
       </x:c>
       <x:c r="E86" s="10" t="str">
-        <x:v>高纯要求与循环利用流程怎样衔接？</x:v>
+        <x:v>如何区别光吸收、电荷输运与化学活性贡献？</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540091/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="37.5" customHeight="1">
       <x:c r="A87" s="10" t="str">
-        <x:v>伍婉卿</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B87" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>催化有机合成方法学</x:v>
+        <x:v>光子带隙、波导与单向态</x:v>
       </x:c>
       <x:c r="D87" s="10" t="str">
-        <x:v>过渡金属催化；成键反应</x:v>
+        <x:v>各向异性晶体；磁光晶体；硅光子器件</x:v>
       </x:c>
       <x:c r="E87" s="10" t="str">
-        <x:v>催化模式带来的新选择性如何证明？</x:v>
+        <x:v>带隙与缺陷损耗怎样连接器件功能？单向透射是否满足非互易隔离的定义？</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="37.5" customHeight="1">
       <x:c r="A88" s="10" t="str">
-        <x:v>伍婉卿</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B88" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>不饱和键化合物高效转化</x:v>
+        <x:v>等离激元共振与增强光谱</x:v>
       </x:c>
       <x:c r="D88" s="10" t="str">
-        <x:v>烯烃；炔烃</x:v>
+        <x:v>金属纳米结构；纳米间隙；SERS/TERS</x:v>
       </x:c>
       <x:c r="E88" s="10" t="str">
-        <x:v>底物官能化怎样兼顾区域选择性与兼容性？</x:v>
+        <x:v>场增强、辐射增强、散射与非辐射损耗分别贡献多少？</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="37.5" customHeight="1">
       <x:c r="A89" s="10" t="str">
-        <x:v>伍婉卿</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B89" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>功能分子及杂环构建</x:v>
+        <x:v>非线性频率转换与白光激光</x:v>
       </x:c>
       <x:c r="D89" s="10" t="str">
-        <x:v>含氮杂环；功能分子</x:v>
+        <x:v>准相位匹配；啁啾非线性晶体；超宽谱光源</x:v>
       </x:c>
       <x:c r="E89" s="10" t="str">
-        <x:v>产物价值来自骨架新颖性还是可验证的应用？</x:v>
+        <x:v>带宽、平坦度、脉冲能量与相干性如何同时测量及比较？</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="37.5" customHeight="1">
       <x:c r="A90" s="10" t="str">
-        <x:v>伍婉卿</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B90" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>烯烃氧化胺化</x:v>
+        <x:v>光镊与金属颗粒操控</x:v>
       </x:c>
       <x:c r="D90" s="10" t="str">
-        <x:v>非活化烯烃；脂肪伯胺；钯催化</x:v>
+        <x:v>金纳米棒；Janus颗粒；矢量光束</x:v>
       </x:c>
       <x:c r="E90" s="10" t="str">
-        <x:v>如何控制氧化条件下的竞争反应？</x:v>
+        <x:v>捕获力、光热作用和流体环境怎样影响颗粒运动？</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
         <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="33" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="37.5" customHeight="1">
       <x:c r="A91" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>李志远</x:v>
       </x:c>
       <x:c r="B91" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>微纳光学、拓扑光子与光计算</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>轻烃与烷烃异构体分离</x:v>
+        <x:v>微纳光学计算与成像方法</x:v>
       </x:c>
       <x:c r="D91" s="10" t="str">
-        <x:v>C2/C3/C4；C6异构体；MOF</x:v>
+        <x:v>平面波传递矩阵；离散偶极子；非线性耦合模</x:v>
       </x:c>
       <x:c r="E91" s="10" t="str">
-        <x:v>逆选择性、孔筛分和吸附热差异如何比较？</x:v>
+        <x:v>数值收敛、边界条件和实验标定如何建立可靠对应？</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>官网项目线索</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="33" customHeight="1">
       <x:c r="A92" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>龙金星</x:v>
       </x:c>
       <x:c r="B92" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>超纯气体与Ar/O2分离</x:v>
+        <x:v>离子液体参与的生物质解聚</x:v>
       </x:c>
       <x:c r="D92" s="10" t="str">
-        <x:v>铝基MOF；氩/氧</x:v>
+        <x:v>离子液体；生物质</x:v>
       </x:c>
       <x:c r="E92" s="10" t="str">
-        <x:v>小尺寸差异下怎样形成有用的选择性和工作容量？</x:v>
+        <x:v>溶剂、酸碱性与催化位点作用如何拆分？</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>官网项目线索</x:v>
+        <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="33" customHeight="1">
       <x:c r="A93" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>龙金星</x:v>
       </x:c>
       <x:c r="B93" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>CO2捕获</x:v>
+        <x:v>生物质组分定向解聚</x:v>
       </x:c>
       <x:c r="D93" s="10" t="str">
-        <x:v>复合多孔材料；含水气体</x:v>
+        <x:v>生物质组分；定向产物</x:v>
       </x:c>
       <x:c r="E93" s="10" t="str">
-        <x:v>湿度竞争与再生温度如何影响实际效果？</x:v>
+        <x:v>怎样抑制二次缩合并保留目标结构？</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="33" customHeight="1">
       <x:c r="A94" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>龙金星</x:v>
       </x:c>
       <x:c r="B94" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C94" s="10" t="str">
-        <x:v>VOCs净化与低温脱硝</x:v>
+        <x:v>环境友好催化剂结构调控</x:v>
       </x:c>
       <x:c r="D94" s="10" t="str">
-        <x:v>VOCs吸附剂；氧化催化剂；脱硝材料</x:v>
+        <x:v>催化新材料；精细结构</x:v>
       </x:c>
       <x:c r="E94" s="10" t="str">
-        <x:v>吸附容量、催化矿化与抗失活如何共同优化？</x:v>
+        <x:v>结构变化与性能提升是否有独立机理证据？</x:v>
       </x:c>
       <x:c r="F94" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G94" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="33" customHeight="1">
       <x:c r="A95" s="10" t="str">
-        <x:v>夏启斌</x:v>
+        <x:v>龙金星</x:v>
       </x:c>
       <x:c r="B95" s="10" t="str">
-        <x:v>电化学能源与电合成</x:v>
+        <x:v>化工过程、传热与系统</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
-        <x:v>碳基储能材料</x:v>
+        <x:v>绿色催化过程及理论基础</x:v>
       </x:c>
       <x:c r="D95" s="10" t="str">
-        <x:v>多孔碳</x:v>
+        <x:v>催化过程；资源化流程</x:v>
       </x:c>
       <x:c r="E95" s="10" t="str">
-        <x:v>储能性能由孔结构还是表面化学主导？</x:v>
+        <x:v>催化结果如何纳入溶剂回收与全流程评价？</x:v>
       </x:c>
       <x:c r="F95" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G95" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2017/0707/c2421a170720/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="33" customHeight="1">
       <x:c r="A96" s="10" t="str">
-        <x:v>祝诗发</x:v>
+        <x:v>梅军</x:v>
       </x:c>
       <x:c r="B96" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>声学、弹性波与超材料</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>炔烃化学与乙炔转化</x:v>
+        <x:v>低频吸声与声学有效介质</x:v>
       </x:c>
       <x:c r="D96" s="10" t="str">
-        <x:v>炔烃；乙炔</x:v>
+        <x:v>局域共振；声学超材料</x:v>
       </x:c>
       <x:c r="E96" s="10" t="str">
-        <x:v>乙炔作为合成原料与待去除杂质时，研究问题有何不同？</x:v>
+        <x:v>亚波长厚度、吸声带宽和入射角鲁棒性怎样权衡？</x:v>
       </x:c>
       <x:c r="F96" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G96" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13954a233585/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="33" customHeight="1">
       <x:c r="A97" s="10" t="str">
-        <x:v>祝诗发</x:v>
+        <x:v>梅军</x:v>
       </x:c>
       <x:c r="B97" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>声学、弹性波与超材料</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>过渡金属催化新转化</x:v>
+        <x:v>声子晶体狄拉克锥与拓扑态</x:v>
       </x:c>
       <x:c r="D97" s="10" t="str">
-        <x:v>过渡金属催化体系</x:v>
+        <x:v>声子晶体；拓扑通道</x:v>
       </x:c>
       <x:c r="E97" s="10" t="str">
-        <x:v>金属中心如何改变炔烃活化和成键选择性？</x:v>
+        <x:v>对称性、边界与频带如何影响通道传播和缺陷散射？</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13954a233585/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="33" customHeight="1">
       <x:c r="A98" s="10" t="str">
-        <x:v>祝诗发</x:v>
+        <x:v>梅军</x:v>
       </x:c>
       <x:c r="B98" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>声学、弹性波与超材料</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>可见光催化</x:v>
+        <x:v>超格栅逆向设计与声路复用</x:v>
       </x:c>
       <x:c r="D98" s="10" t="str">
-        <x:v>光催化有机转化</x:v>
+        <x:v>水声超格栅；深度学习；非互易环行器</x:v>
       </x:c>
       <x:c r="E98" s="10" t="str">
-        <x:v>如何区分能量转移、电子转移和热背景？</x:v>
+        <x:v>设计目标、无源/有源条件和制造容差如何限制效率？</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zhu/research/list.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13954a233585/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="33" customHeight="1">
       <x:c r="A99" s="10" t="str">
-        <x:v>祝诗发</x:v>
+        <x:v>梅军</x:v>
       </x:c>
       <x:c r="B99" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>声学、弹性波与超材料</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>不对称合成与天然产物全合成</x:v>
+        <x:v>水声与弹性波超分辨聚焦</x:v>
       </x:c>
       <x:c r="D99" s="10" t="str">
-        <x:v>手性分子；天然产物</x:v>
+        <x:v>声学超透镜；弯曲波</x:v>
       </x:c>
       <x:c r="E99" s="10" t="str">
-        <x:v>方法在复杂分子构建中是否保持选择性和步骤效率？</x:v>
+        <x:v>焦斑、旁瓣、数值孔径和工作带宽是否在相同能量基准上比较？</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/zhu/research/list.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13954a233585/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="33" customHeight="1">
       <x:c r="A100" s="10" t="str">
-        <x:v>樊栓狮</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B100" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>天然气水合物原理与应用</x:v>
+        <x:v>MOF及衍生多孔纳米催化材料</x:v>
       </x:c>
       <x:c r="D100" s="10" t="str">
-        <x:v>天然气水合物；相平衡</x:v>
+        <x:v>MOF；衍生碳；金属纳米颗粒</x:v>
       </x:c>
       <x:c r="E100" s="10" t="str">
-        <x:v>热力学平衡、成核与传热传质怎样共同控制形成过程？</x:v>
+        <x:v>前驱体结构在衍生后保留了哪些功能？</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="33" customHeight="1">
       <x:c r="A101" s="10" t="str">
-        <x:v>樊栓狮</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B101" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>天然气及LNG储运</x:v>
+        <x:v>分级孔与沸石结构</x:v>
       </x:c>
       <x:c r="D101" s="10" t="str">
-        <x:v>天然气；LNG；流动安全</x:v>
+        <x:v>有序大/微孔；分子筛；沸石</x:v>
       </x:c>
       <x:c r="E101" s="10" t="str">
-        <x:v>气体储运的热力学条件与安全窗口怎样建立？</x:v>
+        <x:v>传质改善与活性位变化如何分开验证？</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="33" customHeight="1">
       <x:c r="A102" s="10" t="str">
-        <x:v>樊栓狮</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B102" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>储能与节能空调</x:v>
+        <x:v>单原子和合金限域</x:v>
       </x:c>
       <x:c r="D102" s="10" t="str">
-        <x:v>储能材料；冷量储存</x:v>
+        <x:v>单原子；超细合金颗粒；孔内封装</x:v>
       </x:c>
       <x:c r="E102" s="10" t="str">
-        <x:v>材料循环性能如何影响设备层面节能？</x:v>
+        <x:v>局部配位和空间限域如何控制稳定性？</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="33" customHeight="1">
       <x:c r="A103" s="10" t="str">
-        <x:v>樊栓狮</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B103" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>可再生能源与新能源利用</x:v>
+        <x:v>CO2还原与水电解</x:v>
       </x:c>
       <x:c r="D103" s="10" t="str">
-        <x:v>能源利用系统</x:v>
+        <x:v>CO2电还原；HER/OER</x:v>
       </x:c>
       <x:c r="E103" s="10" t="str">
-        <x:v>不同能源环节如何匹配供需并减少损耗？</x:v>
+        <x:v>材料结构设计能否兼顾活性、选择性与耐久？</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="33" customHeight="1">
       <x:c r="A104" s="10" t="str">
-        <x:v>林东恩</x:v>
+        <x:v>沈葵</x:v>
       </x:c>
       <x:c r="B104" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>多相催化与生物质转化</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>嘌呤与抗病毒药物骨架</x:v>
+        <x:v>加氢、氧化与生物质转化</x:v>
       </x:c>
       <x:c r="D104" s="10" t="str">
-        <x:v>嘌呤衍生物；核苷相关化合物</x:v>
+        <x:v>多相催化体系</x:v>
       </x:c>
       <x:c r="E104" s="10" t="str">
-        <x:v>骨架功能化如何服务于可用的药物中间体路线？</x:v>
+        <x:v>不同反应共享哪些可迁移的材料设计规律？</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2021/0301/c2421a420246/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="33" customHeight="1">
       <x:c r="A105" s="10" t="str">
-        <x:v>林东恩</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B105" s="10" t="str">
-        <x:v>有机合成与药物化学</x:v>
+        <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>可见光介导绿色氧化偶联</x:v>
+        <x:v>二维膜的精密构筑</x:v>
       </x:c>
       <x:c r="D105" s="10" t="str">
-        <x:v>核苷合成；嘌呤C-H功能化</x:v>
+        <x:v>MXene；二维材料膜</x:v>
       </x:c>
       <x:c r="E105" s="10" t="str">
-        <x:v>光反应在底物范围和放大时有哪些限制？</x:v>
+        <x:v>层间距、缺陷和堆叠方式如何决定实际通量与选择性？</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>官网项目线索</x:v>
+        <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="33" customHeight="1">
       <x:c r="A106" s="10" t="str">
-        <x:v>林东恩</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B106" s="10" t="str">
-        <x:v>高分子、配方与功能材料</x:v>
+        <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>环氧树脂、固化剂与光固化树脂</x:v>
+        <x:v>限域分子与离子传质</x:v>
       </x:c>
       <x:c r="D106" s="10" t="str">
-        <x:v>环氧树脂；固化体系</x:v>
+        <x:v>分子；离子；限域孔道</x:v>
       </x:c>
       <x:c r="E106" s="10" t="str">
-        <x:v>结构、固化条件与最终性能怎样关联？</x:v>
+        <x:v>尺寸、水合与电荷作用在何种条件下占主导？</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="33" customHeight="1">
       <x:c r="A107" s="10" t="str">
-        <x:v>林东恩</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B107" s="10" t="str">
-        <x:v>高分子、配方与功能材料</x:v>
+        <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>日化与陶瓷化学品配方</x:v>
+        <x:v>新型膜与气体分离</x:v>
       </x:c>
       <x:c r="D107" s="10" t="str">
-        <x:v>功能配方；功效成分相容性</x:v>
+        <x:v>MOF/COF膜；混合基质膜；纳滤膜</x:v>
       </x:c>
       <x:c r="E107" s="10" t="str">
-        <x:v>相容性、稳定性和功效评价是否使用可比条件？</x:v>
+        <x:v>材料性能如何保持到支撑膜与实际组件？</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="33" customHeight="1">
       <x:c r="A108" s="10" t="str">
-        <x:v>欧阳新平</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B108" s="10" t="str">
-        <x:v>高分子、配方与功能材料</x:v>
+        <x:v>环境治理与资源循环</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>木质素基精细化学品</x:v>
+        <x:v>盐湖提锂与退役电池回收</x:v>
       </x:c>
       <x:c r="D108" s="10" t="str">
-        <x:v>木质素；混凝土减水剂；分散剂</x:v>
+        <x:v>锂离子；盐湖；退役动力电池</x:v>
       </x:c>
       <x:c r="E108" s="10" t="str">
-        <x:v>分子量与官能团怎样影响吸附、分散和流变？</x:v>
+        <x:v>复杂离子共存下选择性、通量与回收率如何权衡？</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="33" customHeight="1">
       <x:c r="A109" s="10" t="str">
-        <x:v>欧阳新平</x:v>
+        <x:v>魏嫣莹</x:v>
       </x:c>
       <x:c r="B109" s="10" t="str">
-        <x:v>多相催化与生物质转化</x:v>
+        <x:v>环境治理与资源循环</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>木质素解聚与单酚分离</x:v>
+        <x:v>战略关键金属纯化</x:v>
       </x:c>
       <x:c r="D109" s="10" t="str">
-        <x:v>木质素；单酚；香兰素</x:v>
+        <x:v>关键金属；分离与高值利用</x:v>
       </x:c>
       <x:c r="E109" s="10" t="str">
-        <x:v>解聚选择性与后续分离难度怎样共同评价？</x:v>
+        <x:v>高纯要求与循环利用流程怎样衔接？</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0830/c2421a560609/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="33" customHeight="1">
       <x:c r="A110" s="10" t="str">
-        <x:v>欧阳新平</x:v>
+        <x:v>吴宏滨</x:v>
       </x:c>
       <x:c r="B110" s="10" t="str">
-        <x:v>高分子、配方与功能材料</x:v>
+        <x:v>半导体材料与光电器件</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>工业配方与材料应用</x:v>
+        <x:v>有机太阳电池界面与能量损失</x:v>
       </x:c>
       <x:c r="D110" s="10" t="str">
-        <x:v>砂浆；农药分散；陶瓷分散</x:v>
+        <x:v>电极缓冲层；给受体界面；非富勒烯体系</x:v>
       </x:c>
       <x:c r="E110" s="10" t="str">
-        <x:v>配方与使用工况改变后材料性能是否保持？</x:v>
+        <x:v>电压损失、辐射效率和能量偏移怎样联系到器件性能？</x:v>
       </x:c>
       <x:c r="F110" s="10" t="str">
+        <x:v>官网代表成果线索</x:v>
+      </x:c>
+      <x:c r="G110" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="33" customHeight="1">
+      <x:c r="A111" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B111" s="10" t="str">
+        <x:v>半导体材料与光电器件</x:v>
+      </x:c>
+      <x:c r="C111" s="10" t="str">
+        <x:v>有机发光与短波红外器件</x:v>
+      </x:c>
+      <x:c r="D111" s="10" t="str">
+        <x:v>白光聚合物LED；短波红外发光</x:v>
+      </x:c>
+      <x:c r="E111" s="10" t="str">
+        <x:v>发光效率、亮度、波长和工作寿命之间有什么代价？</x:v>
+      </x:c>
+      <x:c r="F111" s="10" t="str">
+        <x:v>官网代表成果线索</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="33" customHeight="1">
+      <x:c r="A112" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B112" s="10" t="str">
+        <x:v>半导体材料与光电器件</x:v>
+      </x:c>
+      <x:c r="C112" s="10" t="str">
+        <x:v>器件物理与光生电荷动力学</x:v>
+      </x:c>
+      <x:c r="D112" s="10" t="str">
+        <x:v>非辐射复合；无序；电荷生成与输运</x:v>
+      </x:c>
+      <x:c r="E112" s="10" t="str">
+        <x:v>材料光谱结果是否足以解释完整器件中的电荷生成及复合？</x:v>
+      </x:c>
+      <x:c r="F112" s="10" t="str">
+        <x:v>官网代表成果线索</x:v>
+      </x:c>
+      <x:c r="G112" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="33" customHeight="1">
+      <x:c r="A113" s="10" t="str">
+        <x:v>伍婉卿</x:v>
+      </x:c>
+      <x:c r="B113" s="10" t="str">
+        <x:v>有机合成与药物化学</x:v>
+      </x:c>
+      <x:c r="C113" s="10" t="str">
+        <x:v>催化有机合成方法学</x:v>
+      </x:c>
+      <x:c r="D113" s="10" t="str">
+        <x:v>过渡金属催化；成键反应</x:v>
+      </x:c>
+      <x:c r="E113" s="10" t="str">
+        <x:v>催化模式带来的新选择性如何证明？</x:v>
+      </x:c>
+      <x:c r="F113" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
-      <x:c r="G110" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="37.5" customHeight="1">
-      <x:c r="A111" s="10" t="str">
-        <x:v>王立世</x:v>
-      </x:c>
-      <x:c r="B111" s="10" t="str">
-        <x:v>分析化学与传感</x:v>
-      </x:c>
-      <x:c r="C111" s="10" t="str">
-        <x:v>纳米材料电分析应用</x:v>
-      </x:c>
-      <x:c r="D111" s="10" t="str">
-        <x:v>纳米材料；功能电极</x:v>
-      </x:c>
-      <x:c r="E111" s="10" t="str">
-        <x:v>响应提升与选择性改善是否可分别测量？</x:v>
-      </x:c>
-      <x:c r="F111" s="10" t="str">
-        <x:v>历史官方资料</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="37.5" customHeight="1">
-      <x:c r="A112" s="10" t="str">
-        <x:v>王立世</x:v>
-      </x:c>
-      <x:c r="B112" s="10" t="str">
-        <x:v>分析化学与传感</x:v>
-      </x:c>
-      <x:c r="C112" s="10" t="str">
-        <x:v>电分析理论与新方法</x:v>
-      </x:c>
-      <x:c r="D112" s="10" t="str">
-        <x:v>伏安方法；电极动力学</x:v>
-      </x:c>
-      <x:c r="E112" s="10" t="str">
-        <x:v>方法如何区分吸附、扩散与电荷转移控制？</x:v>
-      </x:c>
-      <x:c r="F112" s="10" t="str">
-        <x:v>历史官方资料</x:v>
-      </x:c>
-      <x:c r="G112" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="37.5" customHeight="1">
-      <x:c r="A113" s="10" t="str">
-        <x:v>王立世</x:v>
-      </x:c>
-      <x:c r="B113" s="10" t="str">
-        <x:v>分析化学与传感</x:v>
-      </x:c>
-      <x:c r="C113" s="10" t="str">
-        <x:v>分析仪器研制</x:v>
-      </x:c>
-      <x:c r="D113" s="10" t="str">
-        <x:v>电分析仪器</x:v>
-      </x:c>
-      <x:c r="E113" s="10" t="str">
-        <x:v>仪器指标、算法与分析方法的贡献怎样分开？</x:v>
-      </x:c>
-      <x:c r="F113" s="10" t="str">
-        <x:v>历史官方资料</x:v>
-      </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="33" customHeight="1">
       <x:c r="A114" s="10" t="str">
-        <x:v>奚红霞</x:v>
+        <x:v>伍婉卿</x:v>
       </x:c>
       <x:c r="B114" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C114" s="10" t="str">
-        <x:v>环境能源功能材料结构调控</x:v>
+        <x:v>不饱和键化合物高效转化</x:v>
       </x:c>
       <x:c r="D114" s="10" t="str">
-        <x:v>功能多孔材料</x:v>
+        <x:v>烯烃；炔烃</x:v>
       </x:c>
       <x:c r="E114" s="10" t="str">
-        <x:v>如何把可控结构变量映射到分离性能？</x:v>
+        <x:v>底物官能化怎样兼顾区域选择性与兼容性？</x:v>
       </x:c>
       <x:c r="F114" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G114" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="33" customHeight="1">
       <x:c r="A115" s="10" t="str">
-        <x:v>奚红霞</x:v>
+        <x:v>伍婉卿</x:v>
       </x:c>
       <x:c r="B115" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C115" s="10" t="str">
-        <x:v>结构建模与构效关系</x:v>
+        <x:v>功能分子及杂环构建</x:v>
       </x:c>
       <x:c r="D115" s="10" t="str">
-        <x:v>分子模拟；材料结构模型</x:v>
+        <x:v>含氮杂环；功能分子</x:v>
       </x:c>
       <x:c r="E115" s="10" t="str">
-        <x:v>模型能否预测独立实验而非只拟合已知结果？</x:v>
+        <x:v>产物价值来自骨架新颖性还是可验证的应用？</x:v>
       </x:c>
       <x:c r="F115" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G115" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="33" customHeight="1">
       <x:c r="A116" s="10" t="str">
-        <x:v>奚红霞</x:v>
+        <x:v>伍婉卿</x:v>
       </x:c>
       <x:c r="B116" s="10" t="str">
+        <x:v>有机合成与药物化学</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>烯烃氧化胺化</x:v>
+      </x:c>
+      <x:c r="D116" s="10" t="str">
+        <x:v>非活化烯烃；脂肪伯胺；钯催化</x:v>
+      </x:c>
+      <x:c r="E116" s="10" t="str">
+        <x:v>如何控制氧化条件下的竞争反应？</x:v>
+      </x:c>
+      <x:c r="F116" s="10" t="str">
+        <x:v>官网代表成果线索</x:v>
+      </x:c>
+      <x:c r="G116" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0321/c2421a539517/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="33" customHeight="1">
+      <x:c r="A117" s="10" t="str">
+        <x:v>夏启斌</x:v>
+      </x:c>
+      <x:c r="B117" s="10" t="str">
         <x:v>吸附、分离与高纯化</x:v>
       </x:c>
-      <x:c r="C116" s="10" t="str">
-        <x:v>传质与分离工程</x:v>
-      </x:c>
-      <x:c r="D116" s="10" t="str">
-        <x:v>多孔介质；分离过程</x:v>
-      </x:c>
-      <x:c r="E116" s="10" t="str">
-        <x:v>孔内扩散与宏观传质分别如何影响过程？</x:v>
-      </x:c>
-      <x:c r="F116" s="10" t="str">
-        <x:v>官网方向声明</x:v>
-      </x:c>
-      <x:c r="G116" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" ht="37.5" customHeight="1">
-      <x:c r="A117" s="10" t="str">
-        <x:v>肖静</x:v>
-      </x:c>
-      <x:c r="B117" s="10" t="str">
-        <x:v>环境治理与资源循环</x:v>
-      </x:c>
       <x:c r="C117" s="10" t="str">
-        <x:v>清洁燃料脱硫脱氮</x:v>
+        <x:v>轻烃与烷烃异构体分离</x:v>
       </x:c>
       <x:c r="D117" s="10" t="str">
-        <x:v>燃料；功能吸附剂</x:v>
+        <x:v>C2/C3/C4；C6异构体；MOF</x:v>
       </x:c>
       <x:c r="E117" s="10" t="str">
-        <x:v>复杂燃料组分如何竞争吸附并影响再生？</x:v>
+        <x:v>逆选择性、孔筛分和吸附热差异如何比较？</x:v>
       </x:c>
       <x:c r="F117" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网项目线索</x:v>
       </x:c>
       <x:c r="G117" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="33" customHeight="1">
       <x:c r="A118" s="10" t="str">
-        <x:v>肖静</x:v>
+        <x:v>夏启斌</x:v>
       </x:c>
       <x:c r="B118" s="10" t="str">
         <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C118" s="10" t="str">
-        <x:v>CO2等气体吸附分离</x:v>
+        <x:v>超纯气体与Ar/O2分离</x:v>
       </x:c>
       <x:c r="D118" s="10" t="str">
-        <x:v>高选择性吸附材料</x:v>
+        <x:v>铝基MOF；氩/氧</x:v>
       </x:c>
       <x:c r="E118" s="10" t="str">
-        <x:v>位点选择性与过程工作容量能否兼顾？</x:v>
+        <x:v>小尺寸差异下怎样形成有用的选择性和工作容量？</x:v>
       </x:c>
       <x:c r="F118" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网项目线索</x:v>
       </x:c>
       <x:c r="G118" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="33" customHeight="1">
       <x:c r="A119" s="10" t="str">
-        <x:v>肖静</x:v>
+        <x:v>夏启斌</x:v>
       </x:c>
       <x:c r="B119" s="10" t="str">
         <x:v>吸附、分离与高纯化</x:v>
       </x:c>
       <x:c r="C119" s="10" t="str">
-        <x:v>吸附分离过程设计</x:v>
+        <x:v>CO2捕获</x:v>
       </x:c>
       <x:c r="D119" s="10" t="str">
-        <x:v>液体燃料；气体净化过程</x:v>
+        <x:v>复合多孔材料；含水气体</x:v>
       </x:c>
       <x:c r="E119" s="10" t="str">
-        <x:v>材料筛选到连续过程之间需要补哪些数据？</x:v>
+        <x:v>湿度竞争与再生温度如何影响实际效果？</x:v>
       </x:c>
       <x:c r="F119" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G119" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" ht="37.5" customHeight="1">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="33" customHeight="1">
       <x:c r="A120" s="10" t="str">
-        <x:v>肖静</x:v>
+        <x:v>夏启斌</x:v>
       </x:c>
       <x:c r="B120" s="10" t="str">
         <x:v>环境治理与资源循环</x:v>
       </x:c>
       <x:c r="C120" s="10" t="str">
-        <x:v>水体有机微污染与环境催化</x:v>
+        <x:v>VOCs净化与低温脱硝</x:v>
       </x:c>
       <x:c r="D120" s="10" t="str">
-        <x:v>微污染物；环境催化材料</x:v>
+        <x:v>VOCs吸附剂；氧化催化剂；脱硝材料</x:v>
       </x:c>
       <x:c r="E120" s="10" t="str">
-        <x:v>去除、矿化和副产物怎样分别量化？</x:v>
+        <x:v>吸附容量、催化矿化与抗失活如何共同优化？</x:v>
       </x:c>
       <x:c r="F120" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G120" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="33" customHeight="1">
       <x:c r="A121" s="10" t="str">
-        <x:v>杨思宇</x:v>
+        <x:v>夏启斌</x:v>
       </x:c>
       <x:c r="B121" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>电化学能源与电合成</x:v>
       </x:c>
       <x:c r="C121" s="10" t="str">
-        <x:v>风光煤多能耦合化工转化</x:v>
+        <x:v>碳基储能材料</x:v>
       </x:c>
       <x:c r="D121" s="10" t="str">
-        <x:v>风能；太阳能；煤基化工；单元过程</x:v>
+        <x:v>多孔碳</x:v>
       </x:c>
       <x:c r="E121" s="10" t="str">
-        <x:v>波动电源怎样影响流程操作与系统最优解？</x:v>
+        <x:v>储能性能由孔结构还是表面化学主导？</x:v>
       </x:c>
       <x:c r="F121" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G121" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0325/c2421a539814/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="33" customHeight="1">
       <x:c r="A122" s="10" t="str">
-        <x:v>杨思宇</x:v>
+        <x:v>张煜然</x:v>
       </x:c>
       <x:c r="B122" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C122" s="10" t="str">
-        <x:v>AI辅助多物理场建模</x:v>
+        <x:v>量子计量与多参数估计</x:v>
       </x:c>
       <x:c r="D122" s="10" t="str">
-        <x:v>多物理场模型；数据驱动方法</x:v>
+        <x:v>量子Fisher信息；非高斯纠缠；固态自旋</x:v>
       </x:c>
       <x:c r="E122" s="10" t="str">
-        <x:v>训练范围外的物理一致性和预测误差如何验证？</x:v>
+        <x:v>计量优势使用什么资源基准，测量可达性与噪声约束是什么？</x:v>
       </x:c>
       <x:c r="F122" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G122" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="33" customHeight="1">
       <x:c r="A123" s="10" t="str">
-        <x:v>杨思宇</x:v>
+        <x:v>张煜然</x:v>
       </x:c>
       <x:c r="B123" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>低维凝聚态与表界面物理</x:v>
       </x:c>
       <x:c r="C123" s="10" t="str">
-        <x:v>微纳尺度传质传热建模</x:v>
+        <x:v>量子模拟、热化与信息传播</x:v>
       </x:c>
       <x:c r="D123" s="10" t="str">
-        <x:v>微纳结构；传质；传热</x:v>
+        <x:v>超导处理器；多体局域化；Floquet系统</x:v>
       </x:c>
       <x:c r="E123" s="10" t="str">
-        <x:v>哪些尺度效应不能直接由宏观关联式表示？</x:v>
+        <x:v>有限尺度、退相干和初态选择如何影响物相或动力学解释？</x:v>
       </x:c>
       <x:c r="F123" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G123" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="33" customHeight="1">
       <x:c r="A124" s="10" t="str">
-        <x:v>杨思宇</x:v>
+        <x:v>张煜然</x:v>
       </x:c>
       <x:c r="B124" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C124" s="10" t="str">
-        <x:v>绿电-氢能-工业耦合网络</x:v>
+        <x:v>非厄米拓扑与开放量子系统</x:v>
       </x:c>
       <x:c r="D124" s="10" t="str">
-        <x:v>绿电；氢能；工业网络</x:v>
+        <x:v>高阶拓扑；非马尔可夫通道</x:v>
       </x:c>
       <x:c r="E124" s="10" t="str">
-        <x:v>边界、储能与动态调度如何改变节能结论？</x:v>
+        <x:v>有效非厄米描述和真实开放系统之间需要哪些假设？</x:v>
       </x:c>
       <x:c r="F124" s="10" t="str">
-        <x:v>官网项目线索</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G124" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="33" customHeight="1">
       <x:c r="A125" s="10" t="str">
-        <x:v>张正国</x:v>
+        <x:v>张煜然</x:v>
       </x:c>
       <x:c r="B125" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>引力、宇宙学与量子信息</x:v>
       </x:c>
       <x:c r="C125" s="10" t="str">
-        <x:v>传热表界面与高效换热器</x:v>
+        <x:v>量子资源与拓扑纠缠</x:v>
       </x:c>
       <x:c r="D125" s="10" t="str">
-        <x:v>表界面功能结构；换热设备</x:v>
+        <x:v>相干性；多体纠缠；toric code</x:v>
       </x:c>
       <x:c r="E125" s="10" t="str">
-        <x:v>强化换热收益是否抵消压降和制造成本？</x:v>
+        <x:v>资源度量、可操作任务与拓扑表征的关系如何建立？</x:v>
       </x:c>
       <x:c r="F125" s="10" t="str">
-        <x:v>官网方向声明</x:v>
+        <x:v>官网代表成果线索</x:v>
       </x:c>
       <x:c r="G125" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="33" customHeight="1">
       <x:c r="A126" s="10" t="str">
-        <x:v>张正国</x:v>
+        <x:v>祝诗发</x:v>
       </x:c>
       <x:c r="B126" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C126" s="10" t="str">
-        <x:v>复合相变储热材料</x:v>
+        <x:v>炔烃化学与乙炔转化</x:v>
       </x:c>
       <x:c r="D126" s="10" t="str">
-        <x:v>有机/无机；无机/无机；多孔载体</x:v>
+        <x:v>炔烃；乙炔</x:v>
       </x:c>
       <x:c r="E126" s="10" t="str">
-        <x:v>潜热、导热、形稳和循环性能怎样权衡？</x:v>
+        <x:v>乙炔作为合成原料与待去除杂质时，研究问题有何不同？</x:v>
       </x:c>
       <x:c r="F126" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G126" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="33" customHeight="1">
       <x:c r="A127" s="10" t="str">
-        <x:v>张正国</x:v>
+        <x:v>祝诗发</x:v>
       </x:c>
       <x:c r="B127" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C127" s="10" t="str">
-        <x:v>电子器件与动力电池热管理</x:v>
+        <x:v>过渡金属催化新转化</x:v>
       </x:c>
       <x:c r="D127" s="10" t="str">
-        <x:v>电子器件；动力电池；热管理材料</x:v>
+        <x:v>过渡金属催化体系</x:v>
       </x:c>
       <x:c r="E127" s="10" t="str">
-        <x:v>测试热流和边界条件是否接近实际工况？</x:v>
+        <x:v>金属中心如何改变炔烃活化和成键选择性？</x:v>
       </x:c>
       <x:c r="F127" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G127" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+        <x:v>http://www2.scut.edu.cn/zhu/</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="33" customHeight="1">
       <x:c r="A128" s="10" t="str">
-        <x:v>张正国</x:v>
+        <x:v>祝诗发</x:v>
       </x:c>
       <x:c r="B128" s="10" t="str">
-        <x:v>化工过程、传热与系统</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C128" s="10" t="str">
-        <x:v>太阳能、建筑与热泵节能</x:v>
+        <x:v>可见光催化</x:v>
       </x:c>
       <x:c r="D128" s="10" t="str">
-        <x:v>太阳能热利用；建筑；热泵</x:v>
+        <x:v>光催化有机转化</x:v>
       </x:c>
       <x:c r="E128" s="10" t="str">
-        <x:v>实验材料的收益在系统中是否仍然成立？</x:v>
+        <x:v>如何区分能量转移、电子转移和热背景？</x:v>
       </x:c>
       <x:c r="F128" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G128" s="10" t="str">
-        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+        <x:v>https://www2.scut.edu.cn/zhu/research/list.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="33" customHeight="1">
       <x:c r="A129" s="10" t="str">
-        <x:v>邢华斌</x:v>
+        <x:v>祝诗发</x:v>
       </x:c>
       <x:c r="B129" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>有机合成与药物化学</x:v>
       </x:c>
       <x:c r="C129" s="10" t="str">
-        <x:v>高纯分离工程</x:v>
+        <x:v>不对称合成与天然产物全合成</x:v>
       </x:c>
       <x:c r="D129" s="10" t="str">
-        <x:v>高纯化学品；痕量杂质</x:v>
+        <x:v>手性分子；天然产物</x:v>
       </x:c>
       <x:c r="E129" s="10" t="str">
-        <x:v>高纯应用的杂质限值如何反推分离材料需求？</x:v>
+        <x:v>方法在复杂分子构建中是否保持选择性和步骤效率？</x:v>
       </x:c>
       <x:c r="F129" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G129" s="10" t="str">
-        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+        <x:v>https://www2.scut.edu.cn/zhu/research/list.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="33" customHeight="1">
       <x:c r="A130" s="10" t="str">
-        <x:v>邢华斌</x:v>
+        <x:v>樊栓狮</x:v>
       </x:c>
       <x:c r="B130" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>化工过程、传热与系统</x:v>
       </x:c>
       <x:c r="C130" s="10" t="str">
-        <x:v>电子化学材料与纯化</x:v>
+        <x:v>天然气水合物原理与应用</x:v>
       </x:c>
       <x:c r="D130" s="10" t="str">
-        <x:v>电子化学材料</x:v>
+        <x:v>天然气水合物；相平衡</x:v>
       </x:c>
       <x:c r="E130" s="10" t="str">
-        <x:v>材料结构研究怎样连接电子级纯度要求？</x:v>
+        <x:v>热力学平衡、成核与传热传质怎样共同控制形成过程？</x:v>
       </x:c>
       <x:c r="F130" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G130" s="10" t="str">
-        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="33" customHeight="1">
       <x:c r="A131" s="10" t="str">
-        <x:v>邢华斌</x:v>
+        <x:v>樊栓狮</x:v>
       </x:c>
       <x:c r="B131" s="10" t="str">
-        <x:v>吸附、分离与高纯化</x:v>
+        <x:v>化工过程、传热与系统</x:v>
       </x:c>
       <x:c r="C131" s="10" t="str">
-        <x:v>吸附分离材料设计</x:v>
+        <x:v>天然气及LNG储运</x:v>
       </x:c>
       <x:c r="D131" s="10" t="str">
-        <x:v>功能化多孔材料</x:v>
+        <x:v>天然气；LNG；流动安全</x:v>
       </x:c>
       <x:c r="E131" s="10" t="str">
-        <x:v>分子识别位点、孔口和孔腔的贡献怎样拆分？</x:v>
+        <x:v>气体储运的热力学条件与安全窗口怎样建立？</x:v>
       </x:c>
       <x:c r="F131" s="10" t="str">
         <x:v>官网方向声明</x:v>
       </x:c>
       <x:c r="G131" s="10" t="str">
-        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="33" customHeight="1">
       <x:c r="A132" s="10" t="str">
+        <x:v>樊栓狮</x:v>
+      </x:c>
+      <x:c r="B132" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C132" s="10" t="str">
+        <x:v>储能与节能空调</x:v>
+      </x:c>
+      <x:c r="D132" s="10" t="str">
+        <x:v>储能材料；冷量储存</x:v>
+      </x:c>
+      <x:c r="E132" s="10" t="str">
+        <x:v>材料循环性能如何影响设备层面节能？</x:v>
+      </x:c>
+      <x:c r="F132" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G132" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="33" customHeight="1">
+      <x:c r="A133" s="10" t="str">
+        <x:v>樊栓狮</x:v>
+      </x:c>
+      <x:c r="B133" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C133" s="10" t="str">
+        <x:v>可再生能源与新能源利用</x:v>
+      </x:c>
+      <x:c r="D133" s="10" t="str">
+        <x:v>能源利用系统</x:v>
+      </x:c>
+      <x:c r="E133" s="10" t="str">
+        <x:v>不同能源环节如何匹配供需并减少损耗？</x:v>
+      </x:c>
+      <x:c r="F133" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G133" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540046/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="33" customHeight="1">
+      <x:c r="A134" s="10" t="str">
+        <x:v>林东恩</x:v>
+      </x:c>
+      <x:c r="B134" s="10" t="str">
+        <x:v>有机合成与药物化学</x:v>
+      </x:c>
+      <x:c r="C134" s="10" t="str">
+        <x:v>嘌呤与抗病毒药物骨架</x:v>
+      </x:c>
+      <x:c r="D134" s="10" t="str">
+        <x:v>嘌呤衍生物；核苷相关化合物</x:v>
+      </x:c>
+      <x:c r="E134" s="10" t="str">
+        <x:v>骨架功能化如何服务于可用的药物中间体路线？</x:v>
+      </x:c>
+      <x:c r="F134" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G134" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="33" customHeight="1">
+      <x:c r="A135" s="10" t="str">
+        <x:v>林东恩</x:v>
+      </x:c>
+      <x:c r="B135" s="10" t="str">
+        <x:v>有机合成与药物化学</x:v>
+      </x:c>
+      <x:c r="C135" s="10" t="str">
+        <x:v>可见光介导绿色氧化偶联</x:v>
+      </x:c>
+      <x:c r="D135" s="10" t="str">
+        <x:v>核苷合成；嘌呤C-H功能化</x:v>
+      </x:c>
+      <x:c r="E135" s="10" t="str">
+        <x:v>光反应在底物范围和放大时有哪些限制？</x:v>
+      </x:c>
+      <x:c r="F135" s="10" t="str">
+        <x:v>官网项目线索</x:v>
+      </x:c>
+      <x:c r="G135" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="33" customHeight="1">
+      <x:c r="A136" s="10" t="str">
+        <x:v>林东恩</x:v>
+      </x:c>
+      <x:c r="B136" s="10" t="str">
+        <x:v>高分子、配方与功能材料</x:v>
+      </x:c>
+      <x:c r="C136" s="10" t="str">
+        <x:v>环氧树脂、固化剂与光固化树脂</x:v>
+      </x:c>
+      <x:c r="D136" s="10" t="str">
+        <x:v>环氧树脂；固化体系</x:v>
+      </x:c>
+      <x:c r="E136" s="10" t="str">
+        <x:v>结构、固化条件与最终性能怎样关联？</x:v>
+      </x:c>
+      <x:c r="F136" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G136" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="33" customHeight="1">
+      <x:c r="A137" s="10" t="str">
+        <x:v>林东恩</x:v>
+      </x:c>
+      <x:c r="B137" s="10" t="str">
+        <x:v>高分子、配方与功能材料</x:v>
+      </x:c>
+      <x:c r="C137" s="10" t="str">
+        <x:v>日化与陶瓷化学品配方</x:v>
+      </x:c>
+      <x:c r="D137" s="10" t="str">
+        <x:v>功能配方；功效成分相容性</x:v>
+      </x:c>
+      <x:c r="E137" s="10" t="str">
+        <x:v>相容性、稳定性和功效评价是否使用可比条件？</x:v>
+      </x:c>
+      <x:c r="F137" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G137" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0327/c2421a540067/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="37.5" customHeight="1">
+      <x:c r="A138" s="10" t="str">
+        <x:v>欧阳新平</x:v>
+      </x:c>
+      <x:c r="B138" s="10" t="str">
+        <x:v>高分子、配方与功能材料</x:v>
+      </x:c>
+      <x:c r="C138" s="10" t="str">
+        <x:v>木质素基精细化学品</x:v>
+      </x:c>
+      <x:c r="D138" s="10" t="str">
+        <x:v>木质素；混凝土减水剂；分散剂</x:v>
+      </x:c>
+      <x:c r="E138" s="10" t="str">
+        <x:v>分子量与官能团怎样影响吸附、分散和流变？</x:v>
+      </x:c>
+      <x:c r="F138" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G138" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="37.5" customHeight="1">
+      <x:c r="A139" s="10" t="str">
+        <x:v>欧阳新平</x:v>
+      </x:c>
+      <x:c r="B139" s="10" t="str">
+        <x:v>多相催化与生物质转化</x:v>
+      </x:c>
+      <x:c r="C139" s="10" t="str">
+        <x:v>木质素解聚与单酚分离</x:v>
+      </x:c>
+      <x:c r="D139" s="10" t="str">
+        <x:v>木质素；单酚；香兰素</x:v>
+      </x:c>
+      <x:c r="E139" s="10" t="str">
+        <x:v>解聚选择性与后续分离难度怎样共同评价？</x:v>
+      </x:c>
+      <x:c r="F139" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G139" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="37.5" customHeight="1">
+      <x:c r="A140" s="10" t="str">
+        <x:v>欧阳新平</x:v>
+      </x:c>
+      <x:c r="B140" s="10" t="str">
+        <x:v>高分子、配方与功能材料</x:v>
+      </x:c>
+      <x:c r="C140" s="10" t="str">
+        <x:v>工业配方与材料应用</x:v>
+      </x:c>
+      <x:c r="D140" s="10" t="str">
+        <x:v>砂浆；农药分散；陶瓷分散</x:v>
+      </x:c>
+      <x:c r="E140" s="10" t="str">
+        <x:v>配方与使用工况改变后材料性能是否保持？</x:v>
+      </x:c>
+      <x:c r="F140" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G140" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/ef/24/4731866942e591fe9db92e56ee2d/0728bb44-5652-4664-9d87-6bd3e079e61d.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="37.5" customHeight="1">
+      <x:c r="A141" s="10" t="str">
+        <x:v>王立世</x:v>
+      </x:c>
+      <x:c r="B141" s="10" t="str">
+        <x:v>分析化学与传感</x:v>
+      </x:c>
+      <x:c r="C141" s="10" t="str">
+        <x:v>纳米材料电分析应用</x:v>
+      </x:c>
+      <x:c r="D141" s="10" t="str">
+        <x:v>纳米材料；功能电极</x:v>
+      </x:c>
+      <x:c r="E141" s="10" t="str">
+        <x:v>响应提升与选择性改善是否可分别测量？</x:v>
+      </x:c>
+      <x:c r="F141" s="10" t="str">
+        <x:v>历史官方资料</x:v>
+      </x:c>
+      <x:c r="G141" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="37.5" customHeight="1">
+      <x:c r="A142" s="10" t="str">
+        <x:v>王立世</x:v>
+      </x:c>
+      <x:c r="B142" s="10" t="str">
+        <x:v>分析化学与传感</x:v>
+      </x:c>
+      <x:c r="C142" s="10" t="str">
+        <x:v>电分析理论与新方法</x:v>
+      </x:c>
+      <x:c r="D142" s="10" t="str">
+        <x:v>伏安方法；电极动力学</x:v>
+      </x:c>
+      <x:c r="E142" s="10" t="str">
+        <x:v>方法如何区分吸附、扩散与电荷转移控制？</x:v>
+      </x:c>
+      <x:c r="F142" s="10" t="str">
+        <x:v>历史官方资料</x:v>
+      </x:c>
+      <x:c r="G142" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="37.5" customHeight="1">
+      <x:c r="A143" s="10" t="str">
+        <x:v>王立世</x:v>
+      </x:c>
+      <x:c r="B143" s="10" t="str">
+        <x:v>分析化学与传感</x:v>
+      </x:c>
+      <x:c r="C143" s="10" t="str">
+        <x:v>分析仪器研制</x:v>
+      </x:c>
+      <x:c r="D143" s="10" t="str">
+        <x:v>电分析仪器</x:v>
+      </x:c>
+      <x:c r="E143" s="10" t="str">
+        <x:v>仪器指标、算法与分析方法的贡献怎样分开？</x:v>
+      </x:c>
+      <x:c r="F143" s="10" t="str">
+        <x:v>历史官方资料</x:v>
+      </x:c>
+      <x:c r="G143" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/30/80/44a17c69464b82dc1dfefbf4f8f4/750141ce-93da-4e06-bb65-6c1e9f5f7cc0.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="33" customHeight="1">
+      <x:c r="A144" s="10" t="str">
+        <x:v>奚红霞</x:v>
+      </x:c>
+      <x:c r="B144" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C144" s="10" t="str">
+        <x:v>环境能源功能材料结构调控</x:v>
+      </x:c>
+      <x:c r="D144" s="10" t="str">
+        <x:v>功能多孔材料</x:v>
+      </x:c>
+      <x:c r="E144" s="10" t="str">
+        <x:v>如何把可控结构变量映射到分离性能？</x:v>
+      </x:c>
+      <x:c r="F144" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G144" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="33" customHeight="1">
+      <x:c r="A145" s="10" t="str">
+        <x:v>奚红霞</x:v>
+      </x:c>
+      <x:c r="B145" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C145" s="10" t="str">
+        <x:v>结构建模与构效关系</x:v>
+      </x:c>
+      <x:c r="D145" s="10" t="str">
+        <x:v>分子模拟；材料结构模型</x:v>
+      </x:c>
+      <x:c r="E145" s="10" t="str">
+        <x:v>模型能否预测独立实验而非只拟合已知结果？</x:v>
+      </x:c>
+      <x:c r="F145" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G145" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="33" customHeight="1">
+      <x:c r="A146" s="10" t="str">
+        <x:v>奚红霞</x:v>
+      </x:c>
+      <x:c r="B146" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C146" s="10" t="str">
+        <x:v>传质与分离工程</x:v>
+      </x:c>
+      <x:c r="D146" s="10" t="str">
+        <x:v>多孔介质；分离过程</x:v>
+      </x:c>
+      <x:c r="E146" s="10" t="str">
+        <x:v>孔内扩散与宏观传质分别如何影响过程？</x:v>
+      </x:c>
+      <x:c r="F146" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G146" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2012/1221/c2421a54780/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="37.5" customHeight="1">
+      <x:c r="A147" s="10" t="str">
+        <x:v>肖静</x:v>
+      </x:c>
+      <x:c r="B147" s="10" t="str">
+        <x:v>环境治理与资源循环</x:v>
+      </x:c>
+      <x:c r="C147" s="10" t="str">
+        <x:v>清洁燃料脱硫脱氮</x:v>
+      </x:c>
+      <x:c r="D147" s="10" t="str">
+        <x:v>燃料；功能吸附剂</x:v>
+      </x:c>
+      <x:c r="E147" s="10" t="str">
+        <x:v>复杂燃料组分如何竞争吸附并影响再生？</x:v>
+      </x:c>
+      <x:c r="F147" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G147" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="37.5" customHeight="1">
+      <x:c r="A148" s="10" t="str">
+        <x:v>肖静</x:v>
+      </x:c>
+      <x:c r="B148" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C148" s="10" t="str">
+        <x:v>CO2等气体吸附分离</x:v>
+      </x:c>
+      <x:c r="D148" s="10" t="str">
+        <x:v>高选择性吸附材料</x:v>
+      </x:c>
+      <x:c r="E148" s="10" t="str">
+        <x:v>位点选择性与过程工作容量能否兼顾？</x:v>
+      </x:c>
+      <x:c r="F148" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G148" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="37.5" customHeight="1">
+      <x:c r="A149" s="10" t="str">
+        <x:v>肖静</x:v>
+      </x:c>
+      <x:c r="B149" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C149" s="10" t="str">
+        <x:v>吸附分离过程设计</x:v>
+      </x:c>
+      <x:c r="D149" s="10" t="str">
+        <x:v>液体燃料；气体净化过程</x:v>
+      </x:c>
+      <x:c r="E149" s="10" t="str">
+        <x:v>材料筛选到连续过程之间需要补哪些数据？</x:v>
+      </x:c>
+      <x:c r="F149" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G149" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="37.5" customHeight="1">
+      <x:c r="A150" s="10" t="str">
+        <x:v>肖静</x:v>
+      </x:c>
+      <x:c r="B150" s="10" t="str">
+        <x:v>环境治理与资源循环</x:v>
+      </x:c>
+      <x:c r="C150" s="10" t="str">
+        <x:v>水体有机微污染与环境催化</x:v>
+      </x:c>
+      <x:c r="D150" s="10" t="str">
+        <x:v>微污染物；环境催化材料</x:v>
+      </x:c>
+      <x:c r="E150" s="10" t="str">
+        <x:v>去除、矿化和副产物怎样分别量化？</x:v>
+      </x:c>
+      <x:c r="F150" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G150" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/_upload/article/files/19/68/9aa3d98940a6952a0f8be5fbd382/d83565f0-d17b-401b-a8b8-6d7ad1fd2d5c.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="33" customHeight="1">
+      <x:c r="A151" s="10" t="str">
+        <x:v>杨思宇</x:v>
+      </x:c>
+      <x:c r="B151" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C151" s="10" t="str">
+        <x:v>风光煤多能耦合化工转化</x:v>
+      </x:c>
+      <x:c r="D151" s="10" t="str">
+        <x:v>风能；太阳能；煤基化工；单元过程</x:v>
+      </x:c>
+      <x:c r="E151" s="10" t="str">
+        <x:v>波动电源怎样影响流程操作与系统最优解？</x:v>
+      </x:c>
+      <x:c r="F151" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G151" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="33" customHeight="1">
+      <x:c r="A152" s="10" t="str">
+        <x:v>杨思宇</x:v>
+      </x:c>
+      <x:c r="B152" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C152" s="10" t="str">
+        <x:v>AI辅助多物理场建模</x:v>
+      </x:c>
+      <x:c r="D152" s="10" t="str">
+        <x:v>多物理场模型；数据驱动方法</x:v>
+      </x:c>
+      <x:c r="E152" s="10" t="str">
+        <x:v>训练范围外的物理一致性和预测误差如何验证？</x:v>
+      </x:c>
+      <x:c r="F152" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G152" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="33" customHeight="1">
+      <x:c r="A153" s="10" t="str">
+        <x:v>杨思宇</x:v>
+      </x:c>
+      <x:c r="B153" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C153" s="10" t="str">
+        <x:v>微纳尺度传质传热建模</x:v>
+      </x:c>
+      <x:c r="D153" s="10" t="str">
+        <x:v>微纳结构；传质；传热</x:v>
+      </x:c>
+      <x:c r="E153" s="10" t="str">
+        <x:v>哪些尺度效应不能直接由宏观关联式表示？</x:v>
+      </x:c>
+      <x:c r="F153" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G153" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="33" customHeight="1">
+      <x:c r="A154" s="10" t="str">
+        <x:v>杨思宇</x:v>
+      </x:c>
+      <x:c r="B154" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C154" s="10" t="str">
+        <x:v>绿电-氢能-工业耦合网络</x:v>
+      </x:c>
+      <x:c r="D154" s="10" t="str">
+        <x:v>绿电；氢能；工业网络</x:v>
+      </x:c>
+      <x:c r="E154" s="10" t="str">
+        <x:v>边界、储能与动态调度如何改变节能结论？</x:v>
+      </x:c>
+      <x:c r="F154" s="10" t="str">
+        <x:v>官网项目线索</x:v>
+      </x:c>
+      <x:c r="G154" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2022/0328/c2421a465812/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="33" customHeight="1">
+      <x:c r="A155" s="10" t="str">
+        <x:v>张正国</x:v>
+      </x:c>
+      <x:c r="B155" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C155" s="10" t="str">
+        <x:v>传热表界面与高效换热器</x:v>
+      </x:c>
+      <x:c r="D155" s="10" t="str">
+        <x:v>表界面功能结构；换热设备</x:v>
+      </x:c>
+      <x:c r="E155" s="10" t="str">
+        <x:v>强化换热收益是否抵消压降和制造成本？</x:v>
+      </x:c>
+      <x:c r="F155" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G155" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="33" customHeight="1">
+      <x:c r="A156" s="10" t="str">
+        <x:v>张正国</x:v>
+      </x:c>
+      <x:c r="B156" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C156" s="10" t="str">
+        <x:v>复合相变储热材料</x:v>
+      </x:c>
+      <x:c r="D156" s="10" t="str">
+        <x:v>有机/无机；无机/无机；多孔载体</x:v>
+      </x:c>
+      <x:c r="E156" s="10" t="str">
+        <x:v>潜热、导热、形稳和循环性能怎样权衡？</x:v>
+      </x:c>
+      <x:c r="F156" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G156" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="33" customHeight="1">
+      <x:c r="A157" s="10" t="str">
+        <x:v>张正国</x:v>
+      </x:c>
+      <x:c r="B157" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C157" s="10" t="str">
+        <x:v>电子器件与动力电池热管理</x:v>
+      </x:c>
+      <x:c r="D157" s="10" t="str">
+        <x:v>电子器件；动力电池；热管理材料</x:v>
+      </x:c>
+      <x:c r="E157" s="10" t="str">
+        <x:v>测试热流和边界条件是否接近实际工况？</x:v>
+      </x:c>
+      <x:c r="F157" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G157" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="33" customHeight="1">
+      <x:c r="A158" s="10" t="str">
+        <x:v>张正国</x:v>
+      </x:c>
+      <x:c r="B158" s="10" t="str">
+        <x:v>化工过程、传热与系统</x:v>
+      </x:c>
+      <x:c r="C158" s="10" t="str">
+        <x:v>太阳能、建筑与热泵节能</x:v>
+      </x:c>
+      <x:c r="D158" s="10" t="str">
+        <x:v>太阳能热利用；建筑；热泵</x:v>
+      </x:c>
+      <x:c r="E158" s="10" t="str">
+        <x:v>实验材料的收益在系统中是否仍然成立？</x:v>
+      </x:c>
+      <x:c r="F158" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G158" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/ce/2024/0328/c2421a540124/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="33" customHeight="1">
+      <x:c r="A159" s="10" t="str">
         <x:v>邢华斌</x:v>
       </x:c>
-      <x:c r="B132" s="10" t="str">
+      <x:c r="B159" s="10" t="str">
         <x:v>吸附、分离与高纯化</x:v>
       </x:c>
-      <x:c r="C132" s="10" t="str">
+      <x:c r="C159" s="10" t="str">
+        <x:v>高纯分离工程</x:v>
+      </x:c>
+      <x:c r="D159" s="10" t="str">
+        <x:v>高纯化学品；痕量杂质</x:v>
+      </x:c>
+      <x:c r="E159" s="10" t="str">
+        <x:v>高纯应用的杂质限值如何反推分离材料需求？</x:v>
+      </x:c>
+      <x:c r="F159" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G159" s="10" t="str">
+        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="33" customHeight="1">
+      <x:c r="A160" s="10" t="str">
+        <x:v>邢华斌</x:v>
+      </x:c>
+      <x:c r="B160" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C160" s="10" t="str">
+        <x:v>电子化学材料与纯化</x:v>
+      </x:c>
+      <x:c r="D160" s="10" t="str">
+        <x:v>电子化学材料</x:v>
+      </x:c>
+      <x:c r="E160" s="10" t="str">
+        <x:v>材料结构研究怎样连接电子级纯度要求？</x:v>
+      </x:c>
+      <x:c r="F160" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G160" s="10" t="str">
+        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="33" customHeight="1">
+      <x:c r="A161" s="10" t="str">
+        <x:v>邢华斌</x:v>
+      </x:c>
+      <x:c r="B161" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C161" s="10" t="str">
+        <x:v>吸附分离材料设计</x:v>
+      </x:c>
+      <x:c r="D161" s="10" t="str">
+        <x:v>功能化多孔材料</x:v>
+      </x:c>
+      <x:c r="E161" s="10" t="str">
+        <x:v>分子识别位点、孔口和孔腔的贡献怎样拆分？</x:v>
+      </x:c>
+      <x:c r="F161" s="10" t="str">
+        <x:v>官网方向声明</x:v>
+      </x:c>
+      <x:c r="G161" s="10" t="str">
+        <x:v>https://person.zju.edu.cn/xinghb/747909.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="33" customHeight="1">
+      <x:c r="A162" s="10" t="str">
+        <x:v>邢华斌</x:v>
+      </x:c>
+      <x:c r="B162" s="10" t="str">
+        <x:v>吸附、分离与高纯化</x:v>
+      </x:c>
+      <x:c r="C162" s="10" t="str">
         <x:v>丙烯/丙烷精准筛分</x:v>
       </x:c>
-      <x:c r="D132" s="10" t="str">
+      <x:c r="D162" s="10" t="str">
         <x:v>阴离子功能化多孔材料ZU-609</x:v>
       </x:c>
-      <x:c r="E132" s="10" t="str">
+      <x:c r="E162" s="10" t="str">
         <x:v>筛分精度与扩散速度能否同时提升？</x:v>
       </x:c>
-      <x:c r="F132" s="10" t="str">
+      <x:c r="F162" s="10" t="str">
         <x:v>官网代表成果线索</x:v>
       </x:c>
-      <x:c r="G132" s="10" t="str">
+      <x:c r="G162" s="10" t="str">
         <x:v>https://www.zju.edu.cn/2023/1215/c41533a2838788/pagem.htm</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07b52f7ca9b4c04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d20035c4a24718"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF284C59"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="66.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="2" t="str">
+        <x:v>物理与应用物理论文清单</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>来源有界清单，非全集；日期保留已知精度，作者位置1仅表示第一署名。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="8" t="str">
+        <x:v>人物</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>发表日期与精度</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>论文题名</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>期刊</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>DOI</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>作者位置</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>归属证据</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>元数据状态</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>来源网址</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="33" customHeight="1">
+      <x:c r="A6" s="10" t="str">
+        <x:v>江风益</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>2005-12 (month)</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>Growth and characterization of InGaN blue LED structure on Si(111) by MOCVD</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>Journal of Crystal Growth</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="str">
+        <x:v>10.1016/j.jcrysgro.2005.08.046</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/022015/lwcg/list.html
+https://doi.org/10.1016/j.jcrysgro.2005.08.046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="37.5" customHeight="1">
+      <x:c r="A7" s="10" t="str">
+        <x:v>江风益</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>2015-05-19 (day)</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>High optical efficiency GaN based blue LED on silicon substrate</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>SCIENTIA SINICA Physica, Mechanica &amp; Astronomica</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str">
+        <x:v>10.1360/sspma2015-00027</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/022015/lwcg/list.html
+https://doi.org/10.1360/sspma2015-00027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="33" customHeight="1">
+      <x:c r="A8" s="10" t="str">
+        <x:v>江风益</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>2019 (year)</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>Semiconductor yellow light-emitting diodes</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>Acta Physica Sinica</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="str">
+        <x:v>10.7498/aps.68.20191044</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/022015/lwcg/list.html
+https://doi.org/10.7498/aps.68.20191044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="33" customHeight="1">
+      <x:c r="A9" s="10" t="str">
+        <x:v>江风益</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>2019-01-14 (day)</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>Efficient InGaN-based yellow-light-emitting diodes</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>Photonics Research</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="str">
+        <x:v>10.1364/prj.7.000144</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/022015/lwcg/list.html
+https://doi.org/10.1364/prj.7.000144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="33" customHeight="1">
+      <x:c r="A10" s="10" t="str">
+        <x:v>江风益</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>2020-10-09 (day)</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Efficient emission of InGaN-based light-emitting diodes: toward orange and red</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>Photonics Research</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str">
+        <x:v>10.1364/prj.402555</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/022015/lwcg/list.html
+https://doi.org/10.1364/prj.402555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="33" customHeight="1">
+      <x:c r="A11" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>2020-07-01 (day)</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>Quantum bit threads of MERA tensor network in large c limit *</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>Chinese Physics C</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str">
+        <x:v>10.1088/1674-1137/44/7/075102</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1088/1674-1137/44/7/075102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="33" customHeight="1">
+      <x:c r="A12" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>2020-08-05 (day)</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>Inequalities of holographic entanglement of purification from bit threads</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>The European Physical Journal C</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str">
+        <x:v>10.1140/epjc/s10052-020-8283-1</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1140/epjc/s10052-020-8283-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="33" customHeight="1">
+      <x:c r="A13" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>2020-09-10 (day)</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>Holographic complexity for nonlinearly charged Lifshitz black holes</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>Classical and Quantum Gravity</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="str">
+        <x:v>10.1088/1361-6382/aba843</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1088/1361-6382/aba843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="37.5" customHeight="1">
+      <x:c r="A14" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>2020-09-24 (day)</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>Information loss paradox revisited: Farewell firewall?</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>International Journal of Modern Physics D</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="str">
+        <x:v>10.1142/s0218271820430191</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1142/s0218271820430191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="33" customHeight="1">
+      <x:c r="A15" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>2020-11-18 (day)</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>Constraints on Hořava–Lifshitz gravity from GRB 170817A</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>The European Physical Journal C</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="str">
+        <x:v>10.1140/epjc/s10052-020-08626-z</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1140/epjc/s10052-020-08626-z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="33" customHeight="1">
+      <x:c r="A16" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>2020-12 (month)</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>Vacua in novel 4D Einstein-Gauss-Bonnet gravity: Pathology and instability?</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Physics Letters B</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="str">
+        <x:v>10.1016/j.physletb.2020.135907</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1016/j.physletb.2020.135907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="37.5" customHeight="1">
+      <x:c r="A17" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>2021-03-01 (day)</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>Theoretical and observational constraints on regularized 4D Einstein-Gauss-Bonnet gravity</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>Physical Review D</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="str">
+        <x:v>10.1103/physrevd.103.064002</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1103/physrevd.103.064002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="37.5" customHeight="1">
+      <x:c r="A18" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>2021-11-03 (day)</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>Extended geometry of Gambini-Olmedo-Pullin polymer black hole and its quasinormal spectrum</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>Physical Review D</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="str">
+        <x:v>10.1103/physrevd.104.106001</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1103/physrevd.104.106001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="33" customHeight="1">
+      <x:c r="A19" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>2021-12 (month)</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>Rotations of the polarization of a gravitational wave propagating in universe</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>Nuclear Physics B</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="str">
+        <x:v>10.1016/j.nuclphysb.2021.115578</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1016/j.nuclphysb.2021.115578</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="33" customHeight="1">
+      <x:c r="A20" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>2022-06-27 (day)</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>Improved proof-by-contraction method and relative homologous entropy inequalities</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Journal of High Energy Physics</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="str">
+        <x:v>10.1007/jhep06(2022)153</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1007/jhep06(2022)153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="33" customHeight="1">
+      <x:c r="A21" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>2022-07-04 (day)</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>Island and Page curve for one-sided asymptotically flat black hole</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>Journal of High Energy Physics</x:v>
+      </x:c>
+      <x:c r="E21" s="10" t="str">
+        <x:v>10.1007/jhep07(2022)020</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1007/jhep07(2022)020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="37.5" customHeight="1">
+      <x:c r="A22" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>2023-01-05 (day)</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>Unitary constraints on semiclassical Schwarzschild black holes in the presence of island</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>Physical Review D</x:v>
+      </x:c>
+      <x:c r="E22" s="10" t="str">
+        <x:v>10.1103/physrevd.107.026005</x:v>
+      </x:c>
+      <x:c r="F22" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G22" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1103/physrevd.107.026005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="33" customHeight="1">
+      <x:c r="A23" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>2023-04-11 (day)</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>Detecting sublunar-mass primordial black holes with the Earth-Moon binary system</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="str">
+        <x:v>Physical Review D</x:v>
+      </x:c>
+      <x:c r="E23" s="10" t="str">
+        <x:v>10.1103/physrevd.107.084019</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G23" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H23" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1103/physrevd.107.084019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="37.5" customHeight="1">
+      <x:c r="A24" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>2023-05-05 (day)</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>Page curves and entanglement islands for the step-function Vaidya model of evaporating black holes</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="str">
+        <x:v>Journal of High Energy Physics</x:v>
+      </x:c>
+      <x:c r="E24" s="10" t="str">
+        <x:v>10.1007/jhep05(2023)042</x:v>
+      </x:c>
+      <x:c r="F24" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G24" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H24" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I24" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1007/jhep05(2023)042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="33" customHeight="1">
+      <x:c r="A25" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="str">
+        <x:v>2023-08-01 (day)</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>A note on the entanglement entropy of primary fermion fields in JT gravity*</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="str">
+        <x:v>Chinese Physics C</x:v>
+      </x:c>
+      <x:c r="E25" s="10" t="str">
+        <x:v>10.1088/1674-1137/acdd60</x:v>
+      </x:c>
+      <x:c r="F25" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G25" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H25" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1088/1674-1137/acdd60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="33" customHeight="1">
+      <x:c r="A26" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>2024-01-20 (day)</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>Quantum gravity induced entanglement of masses with extra dimensions</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="str">
+        <x:v>The European Physical Journal C</x:v>
+      </x:c>
+      <x:c r="E26" s="10" t="str">
+        <x:v>10.1140/epjc/s10052-024-12413-5</x:v>
+      </x:c>
+      <x:c r="F26" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G26" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H26" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I26" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1140/epjc/s10052-024-12413-5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="37.5" customHeight="1">
+      <x:c r="A27" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>2024-03-11 (day)</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>Gravity-induced entanglement between two massive microscopic particles in curved spacetime: I. The Schwarzschild background</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="str">
+        <x:v>The European Physical Journal C</x:v>
+      </x:c>
+      <x:c r="E27" s="10" t="str">
+        <x:v>10.1140/epjc/s10052-024-12632-w</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G27" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H27" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I27" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1140/epjc/s10052-024-12632-w</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="37.5" customHeight="1">
+      <x:c r="A28" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>2024-05-14 (day)</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>Gravity-induced entanglement between two massive microscopic particles in curved spacetime: II. Friedmann–Lemaître–Robertson–Walker universe</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="str">
+        <x:v>The European Physical Journal C</x:v>
+      </x:c>
+      <x:c r="E28" s="10" t="str">
+        <x:v>10.1140/epjc/s10052-024-12831-5</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G28" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H28" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1140/epjc/s10052-024-12831-5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="37.5" customHeight="1">
+      <x:c r="A29" s="10" t="str">
+        <x:v>舒富文</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>2024-08-16 (day)</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>Testing the first law of black hole mechanics with gravitational waves</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="str">
+        <x:v>Science China Physics, Mechanics &amp; Astronomy</x:v>
+      </x:c>
+      <x:c r="E29" s="10" t="str">
+        <x:v>10.1007/s11433-024-2442-3</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G29" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H29" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I29" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/091956/
+https://doi.org/10.1007/s11433-024-2442-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="37.5" customHeight="1">
+      <x:c r="A30" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>2020-05-19 (day)</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>Synthesis of Two-Dimensional Metal–Organic Frameworks via Dehydrogenation Reactions on a Cu(111) Surface</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E30" s="10" t="str">
+        <x:v>10.1021/acs.jpcc.0c00931</x:v>
+      </x:c>
+      <x:c r="F30" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G30" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H30" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpcc.0c00931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="37.5" customHeight="1">
+      <x:c r="A31" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>2021-02-15 (day)</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>A Fundamental Role of the Molecular Length in Forming Metal–Organic Hybrids of Phenol Derivatives on Silver Surfaces</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E31" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.1c00005</x:v>
+      </x:c>
+      <x:c r="F31" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G31" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H31" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I31" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.1c00005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="37.5" customHeight="1">
+      <x:c r="A32" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="str">
+        <x:v>2021-08-19 (day)</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>Constructing and Transferring Two-Dimensional Tessellation Kagome Lattices via Chemical Reactions on Cu(111) Surface</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E32" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.1c02345</x:v>
+      </x:c>
+      <x:c r="F32" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H32" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I32" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.1c02345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="33" customHeight="1">
+      <x:c r="A33" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="str">
+        <x:v>2022-02-28 (day)</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>From n-alkane to polyacetylene on Cu (110): Linkage modulation in chain growth</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="str">
+        <x:v>Science China Chemistry</x:v>
+      </x:c>
+      <x:c r="E33" s="10" t="str">
+        <x:v>10.1007/s11426-021-1213-2</x:v>
+      </x:c>
+      <x:c r="F33" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G33" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H33" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I33" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1007/s11426-021-1213-2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="37.5" customHeight="1">
+      <x:c r="A34" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B34" s="10" t="str">
+        <x:v>2022-07-13 (day)</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>Synthesis of the Two-Dimensional Robust Kagome Lattice on Au(111) via the Introduction of Fe Atoms</x:v>
+      </x:c>
+      <x:c r="D34" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E34" s="10" t="str">
+        <x:v>10.1021/acs.jpcc.2c03361</x:v>
+      </x:c>
+      <x:c r="F34" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G34" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H34" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I34" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpcc.2c03361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="37.5" customHeight="1">
+      <x:c r="A35" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B35" s="10" t="str">
+        <x:v>2022-09-20 (day)</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>Intra- and Inter-Self-Assembly of Identical Supramolecules on Silver Surfaces</x:v>
+      </x:c>
+      <x:c r="D35" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E35" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.2c02501</x:v>
+      </x:c>
+      <x:c r="F35" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G35" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H35" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I35" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.2c02501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="37.5" customHeight="1">
+      <x:c r="A36" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B36" s="10" t="str">
+        <x:v>2022-11-16 (day)</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
+        <x:v>Influence of Molecular Configurations on the Desulfonylation Reactions on Metal Surfaces</x:v>
+      </x:c>
+      <x:c r="D36" s="10" t="str">
+        <x:v>Journal of the American Chemical Society</x:v>
+      </x:c>
+      <x:c r="E36" s="10" t="str">
+        <x:v>10.1021/jacs.2c08736</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H36" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I36" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/jacs.2c08736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="37.5" customHeight="1">
+      <x:c r="A37" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B37" s="10" t="str">
+        <x:v>2023-02-07 (day)</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>Highly Selective On-Surface [2 + 2] Cycloaddition Induced by Hierarchical Metal–Organic Hybrids</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E37" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.2c03913</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G37" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H37" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I37" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.2c03913</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="37.5" customHeight="1">
+      <x:c r="A38" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B38" s="10" t="str">
+        <x:v>2023-10-20 (day)</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>Constructing Two-Dimensional Distorted Kagome Lattices on Ag(111)</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E38" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.3c02620</x:v>
+      </x:c>
+      <x:c r="F38" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G38" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H38" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I38" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.3c02620</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="33" customHeight="1">
+      <x:c r="A39" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B39" s="10" t="str">
+        <x:v>2023-11-10 (day)</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>Controlled Hierarchical Dehydrogenation Reactions on Au(111)</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E39" s="10" t="str">
+        <x:v>10.1021/acs.jpcc.3c05180</x:v>
+      </x:c>
+      <x:c r="F39" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G39" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H39" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I39" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpcc.3c05180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="37.5" customHeight="1">
+      <x:c r="A40" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B40" s="10" t="str">
+        <x:v>2023-12-08 (day)</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>Synthesis of Large-Scale High-Quality Metal–Organic Frameworks on Cu(100) via Hierarchical Dehydrogenation Reactions</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry Letters</x:v>
+      </x:c>
+      <x:c r="E40" s="10" t="str">
+        <x:v>10.1021/acs.jpclett.3c02878</x:v>
+      </x:c>
+      <x:c r="F40" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G40" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H40" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/acs.jpclett.3c02878</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="33" customHeight="1">
+      <x:c r="A41" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B41" s="10" t="str">
+        <x:v>2024-04-08 (day)</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>Universal inter-molecular radical transfer reactions on metal surfaces</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="str">
+        <x:v>Nature Communications</x:v>
+      </x:c>
+      <x:c r="E41" s="10" t="str">
+        <x:v>10.1038/s41467-024-47252-1</x:v>
+      </x:c>
+      <x:c r="F41" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I41" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1038/s41467-024-47252-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="37.5" customHeight="1">
+      <x:c r="A42" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B42" s="10" t="str">
+        <x:v>2024-12-10 (day)</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>Mechanistical Study on Substrate‐Controlled Highly Selective [2+2] and [2+3] Cycloaddition Reactions</x:v>
+      </x:c>
+      <x:c r="D42" s="10" t="str">
+        <x:v>Chemistry – A European Journal</x:v>
+      </x:c>
+      <x:c r="E42" s="10" t="str">
+        <x:v>10.1002/chem.202404074</x:v>
+      </x:c>
+      <x:c r="F42" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I42" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1002/chem.202404074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="37.5" customHeight="1">
+      <x:c r="A43" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B43" s="10" t="str">
+        <x:v>2025-05-30 (day)</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>Real-space investigations of on-surface intermolecular radical transfer reactions assisted by persistent radicals</x:v>
+      </x:c>
+      <x:c r="D43" s="10" t="str">
+        <x:v>Science Advances</x:v>
+      </x:c>
+      <x:c r="E43" s="10" t="str">
+        <x:v>10.1126/sciadv.adu9436</x:v>
+      </x:c>
+      <x:c r="F43" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I43" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1126/sciadv.adu9436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="37.5" customHeight="1">
+      <x:c r="A44" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B44" s="10" t="str">
+        <x:v>2025-07-23 (day)</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>On-surface visualization of the influence of the chemical environment on halogen–hydrogen bonds at submolecular scale</x:v>
+      </x:c>
+      <x:c r="D44" s="10" t="str">
+        <x:v>The Journal of Chemical Physics</x:v>
+      </x:c>
+      <x:c r="E44" s="10" t="str">
+        <x:v>10.1063/5.0276082</x:v>
+      </x:c>
+      <x:c r="F44" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I44" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1063/5.0276082</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="37.5" customHeight="1">
+      <x:c r="A45" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B45" s="10" t="str">
+        <x:v>2025-10-16 (day)</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>Successive chiral transfer from molecular to mesoscopic scale in a controlled 2D hierarchical nanostructure on Ag(111)</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="str">
+        <x:v>The Journal of Chemical Physics</x:v>
+      </x:c>
+      <x:c r="E45" s="10" t="str">
+        <x:v>10.1063/5.0296770</x:v>
+      </x:c>
+      <x:c r="F45" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I45" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1063/5.0296770</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="37.5" customHeight="1">
+      <x:c r="A46" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>2025-10-25 (day)</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>Highly Selective Intermolecular Cross-Coupling Reactions via a Persistent Radical Effect on Ag(111)</x:v>
+      </x:c>
+      <x:c r="D46" s="10" t="str">
+        <x:v>Journal of the American Chemical Society</x:v>
+      </x:c>
+      <x:c r="E46" s="10" t="str">
+        <x:v>10.1021/jacs.5c13021</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I46" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.1021/jacs.5c13021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="37.5" customHeight="1">
+      <x:c r="A47" s="10" t="str">
+        <x:v>王俊波</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>2026-07-01 (day)</x:v>
+      </x:c>
+      <x:c r="C47" s="10" t="str">
+        <x:v>Switching Mono- and Diselective
+                    Ortho
+                    Aromatic C–H Bond Activations via Extrinsic Fe Atoms on Metal Surfaces</x:v>
+      </x:c>
+      <x:c r="D47" s="10" t="str">
+        <x:v>CCS Chemistry</x:v>
+      </x:c>
+      <x:c r="E47" s="10" t="str">
+        <x:v>10.31635/ccschem.025.202506040</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/093634/
+https://doi.org/10.31635/ccschem.025.202506040</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="33" customHeight="1">
+      <x:c r="A48" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B48" s="10" t="str">
+        <x:v>2013-05-27 (day)</x:v>
+      </x:c>
+      <x:c r="C48" s="10" t="str">
+        <x:v>Low‐Dimensional Te‐Based Nanostructures</x:v>
+      </x:c>
+      <x:c r="D48" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E48" s="10" t="str">
+        <x:v>10.1002/adma.201301128</x:v>
+      </x:c>
+      <x:c r="F48" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H48" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I48" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/adma.201301128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="33" customHeight="1">
+      <x:c r="A49" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B49" s="10" t="str">
+        <x:v>2013-11-04 (day)</x:v>
+      </x:c>
+      <x:c r="C49" s="10" t="str">
+        <x:v>Topological Surface Transport Properties of Single-Crystalline SnTe Nanowire</x:v>
+      </x:c>
+      <x:c r="D49" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E49" s="10" t="str">
+        <x:v>10.1021/nl402841x</x:v>
+      </x:c>
+      <x:c r="F49" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I49" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/nl402841x</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="37.5" customHeight="1">
+      <x:c r="A50" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B50" s="10" t="str">
+        <x:v>2014-07-02 (day)</x:v>
+      </x:c>
+      <x:c r="C50" s="10" t="str">
+        <x:v>Van der Waals Epitaxy and Photoresponse of Hexagonal Tellurium Nanoplates on Flexible Mica Sheets</x:v>
+      </x:c>
+      <x:c r="D50" s="10" t="str">
+        <x:v>ACS Nano</x:v>
+      </x:c>
+      <x:c r="E50" s="10" t="str">
+        <x:v>10.1021/nn5028104</x:v>
+      </x:c>
+      <x:c r="F50" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H50" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I50" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/nn5028104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="33" customHeight="1">
+      <x:c r="A51" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B51" s="10" t="str">
+        <x:v>2014-12-17 (day)</x:v>
+      </x:c>
+      <x:c r="C51" s="10" t="str">
+        <x:v>Topological Crystalline Insulator Pb1-xSnxSe Nanowires with {100} Facets</x:v>
+      </x:c>
+      <x:c r="D51" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E51" s="10" t="str">
+        <x:v>10.1002/smll.201403159</x:v>
+      </x:c>
+      <x:c r="F51" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H51" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I51" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/smll.201403159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="37.5" customHeight="1">
+      <x:c r="A52" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B52" s="10" t="str">
+        <x:v>2015-01-23 (day)</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="str">
+        <x:v>van der Waals Epitaxial Ultrathin Two-Dimensional Nonlayered Semiconductor for Highly Efficient Flexible Optoelectronic Devices</x:v>
+      </x:c>
+      <x:c r="D52" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E52" s="10" t="str">
+        <x:v>10.1021/nl504258m</x:v>
+      </x:c>
+      <x:c r="F52" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H52" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I52" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/nl504258m</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="37.5" customHeight="1">
+      <x:c r="A53" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B53" s="10" t="str">
+        <x:v>2015-03-03 (day)</x:v>
+      </x:c>
+      <x:c r="C53" s="10" t="str">
+        <x:v>Weak Antilocalization Effect of Topological Crystalline Insulator Pb1–xSnxTe Nanowires with Tunable Composition and Distinct {100} Facets</x:v>
+      </x:c>
+      <x:c r="D53" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E53" s="10" t="str">
+        <x:v>10.1021/nl504976g</x:v>
+      </x:c>
+      <x:c r="F53" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G53" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H53" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I53" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/nl504976g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="33" customHeight="1">
+      <x:c r="A54" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B54" s="10" t="str">
+        <x:v>2015-07-14 (day)</x:v>
+      </x:c>
+      <x:c r="C54" s="10" t="str">
+        <x:v>Low-Dimensional Topological Crystalline Insulators</x:v>
+      </x:c>
+      <x:c r="D54" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E54" s="10" t="str">
+        <x:v>10.1002/smll.201501381</x:v>
+      </x:c>
+      <x:c r="F54" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H54" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I54" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/smll.201501381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="33" customHeight="1">
+      <x:c r="A55" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B55" s="10" t="str">
+        <x:v>2015-08-25 (day)</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="str">
+        <x:v>BN‐Enabled Epitaxy of Pb
+                      1–
+                      x
+                    Sn
+                      x
+                    Se Nanoplates on SiO
+                    2
+                    /Si for High‐Performance Mid‐Infrared Detection</x:v>
+      </x:c>
+      <x:c r="D55" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E55" s="10" t="str">
+        <x:v>10.1002/smll.201502049</x:v>
+      </x:c>
+      <x:c r="F55" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H55" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I55" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/smll.201502049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="37.5" customHeight="1">
+      <x:c r="A56" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B56" s="10" t="str">
+        <x:v>2015-11-30 (day)</x:v>
+      </x:c>
+      <x:c r="C56" s="10" t="str">
+        <x:v>Rational Design of Ultralarge Pb1−xSnxTe Nanoplates for Exploring Crystalline Symmetry‐Protected Topological Transport</x:v>
+      </x:c>
+      <x:c r="D56" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E56" s="10" t="str">
+        <x:v>10.1002/adma.201504630</x:v>
+      </x:c>
+      <x:c r="F56" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H56" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I56" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/adma.201504630</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="37.5" customHeight="1">
+      <x:c r="A57" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B57" s="10" t="str">
+        <x:v>2016-03-15 (day)</x:v>
+      </x:c>
+      <x:c r="C57" s="10" t="str">
+        <x:v>Oriented Growth of Pb1−xSnxTe Nanowire Arrays for Integration of Flexible Infrared Detectors</x:v>
+      </x:c>
+      <x:c r="D57" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E57" s="10" t="str">
+        <x:v>10.1002/adma.201506338</x:v>
+      </x:c>
+      <x:c r="F57" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H57" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I57" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/adma.201506338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="37.5" customHeight="1">
+      <x:c r="A58" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B58" s="10" t="str">
+        <x:v>2016-05-11 (day)</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>High‐Performance Phototransistor of Epitaxial PbS Nanoplate‐Graphene Heterostructure with Edge Contact</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E58" s="10" t="str">
+        <x:v>10.1002/adma.201601071</x:v>
+      </x:c>
+      <x:c r="F58" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H58" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I58" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/adma.201601071</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="33" customHeight="1">
+      <x:c r="A59" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B59" s="10" t="str">
+        <x:v>2016-07-04 (day)</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>Epitaxial 2D PbS Nanoplates Arrays with Highly Efficient Infrared Response</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E59" s="10" t="str">
+        <x:v>10.1002/adma.201602481</x:v>
+      </x:c>
+      <x:c r="F59" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G59" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H59" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/adma.201602481</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="33" customHeight="1">
+      <x:c r="A60" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B60" s="10" t="str">
+        <x:v>2018-04-06 (day)</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>Nonvolatile infrared memory in MoS
+            2
+            /PbS van der Waals heterostructures</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>Science Advances</x:v>
+      </x:c>
+      <x:c r="E60" s="10" t="str">
+        <x:v>10.1126/sciadv.aap7916</x:v>
+      </x:c>
+      <x:c r="F60" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H60" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I60" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1126/sciadv.aap7916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="33" customHeight="1">
+      <x:c r="A61" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B61" s="10" t="str">
+        <x:v>2018-04-14 (day)</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>Room‐Temperature Nanoseconds Spin Relaxation in WTe2 and MoTe2 Thin Films</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>Advanced Science</x:v>
+      </x:c>
+      <x:c r="E61" s="10" t="str">
+        <x:v>10.1002/advs.201700912</x:v>
+      </x:c>
+      <x:c r="F61" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H61" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I61" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/advs.201700912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="37.5" customHeight="1">
+      <x:c r="A62" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B62" s="10" t="str">
+        <x:v>2019-03-12 (day)</x:v>
+      </x:c>
+      <x:c r="C62" s="10" t="str">
+        <x:v>Anomalous Photothermoelectric Transport Due to Anisotropic Energy Dispersion in WTe2</x:v>
+      </x:c>
+      <x:c r="D62" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E62" s="10" t="str">
+        <x:v>10.1021/acs.nanolett.9b00513</x:v>
+      </x:c>
+      <x:c r="F62" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G62" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H62" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I62" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acs.nanolett.9b00513</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="33" customHeight="1">
+      <x:c r="A63" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B63" s="10" t="str">
+        <x:v>2019-12-03 (day)</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="str">
+        <x:v>Gapless van der
+Waals Heterostructures for Infrared
+Optoelectronic Devices</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="str">
+        <x:v>ACS Nano</x:v>
+      </x:c>
+      <x:c r="E63" s="10" t="str">
+        <x:v>10.1021/acsnano.9b08375</x:v>
+      </x:c>
+      <x:c r="F63" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G63" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H63" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I63" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsnano.9b08375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="33" customHeight="1">
+      <x:c r="A64" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B64" s="10" t="str">
+        <x:v>2019-12-12 (day)</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="str">
+        <x:v>Direct imaging of carrier diffusion length in organic-inorganic perovskites</x:v>
+      </x:c>
+      <x:c r="D64" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E64" s="10" t="str">
+        <x:v>10.1063/1.5133979</x:v>
+      </x:c>
+      <x:c r="F64" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G64" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H64" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I64" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/1.5133979</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="37.5" customHeight="1">
+      <x:c r="A65" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B65" s="10" t="str">
+        <x:v>2019-12-12 (day)</x:v>
+      </x:c>
+      <x:c r="C65" s="10" t="str">
+        <x:v>Nonvolatile charge memory with optical controllability in two-terminal pristine
+                    α
+                    -In
+                    2
+                    Se
+                    3
+                    nanosheets</x:v>
+      </x:c>
+      <x:c r="D65" s="10" t="str">
+        <x:v>Journal of Physics D: Applied Physics</x:v>
+      </x:c>
+      <x:c r="E65" s="10" t="str">
+        <x:v>10.1088/1361-6463/ab5737</x:v>
+      </x:c>
+      <x:c r="F65" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G65" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H65" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I65" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1088/1361-6463/ab5737</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="33" customHeight="1">
+      <x:c r="A66" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B66" s="10" t="str">
+        <x:v>2020-10-21 (day)</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="str">
+        <x:v>Manipulating Photon Propagation via a Perovskite Microwire Array</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E66" s="10" t="str">
+        <x:v>10.1021/acs.jpcc.0c07712</x:v>
+      </x:c>
+      <x:c r="F66" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G66" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H66" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I66" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acs.jpcc.0c07712</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="37.5" customHeight="1">
+      <x:c r="A67" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B67" s="10" t="str">
+        <x:v>2022-01-24 (day)</x:v>
+      </x:c>
+      <x:c r="C67" s="10" t="str">
+        <x:v>Hot-carrier infrared detection in PbS with ultrafast and highly sensitive responses</x:v>
+      </x:c>
+      <x:c r="D67" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E67" s="10" t="str">
+        <x:v>10.1063/5.0078394</x:v>
+      </x:c>
+      <x:c r="F67" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G67" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H67" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I67" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0078394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="37.5" customHeight="1">
+      <x:c r="A68" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B68" s="10" t="str">
+        <x:v>2022-03 (month)</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="str">
+        <x:v>Enhancement of infrared response speed via modulating crystallinity of highly-oriented PbS polycrystalline thin films</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="str">
+        <x:v>Infrared Physics &amp; Technology</x:v>
+      </x:c>
+      <x:c r="E68" s="10" t="str">
+        <x:v>10.1016/j.infrared.2022.104033</x:v>
+      </x:c>
+      <x:c r="F68" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G68" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H68" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I68" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1016/j.infrared.2022.104033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="37.5" customHeight="1">
+      <x:c r="A69" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B69" s="10" t="str">
+        <x:v>2023-06-13 (day)</x:v>
+      </x:c>
+      <x:c r="C69" s="10" t="str">
+        <x:v>Long-distance transport of hot carriers due to acoustic phonon bottleneck in PbSe with room-temperature sensitive mid-infrared sensing</x:v>
+      </x:c>
+      <x:c r="D69" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E69" s="10" t="str">
+        <x:v>10.1063/5.0155528</x:v>
+      </x:c>
+      <x:c r="F69" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G69" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H69" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I69" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0155528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="37.5" customHeight="1">
+      <x:c r="A70" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B70" s="10" t="str">
+        <x:v>2023-09-12 (day)</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="str">
+        <x:v>Short-wave infrared position-sensitive detector enabled by lateral diffusion of thermalized carriers in lead salts</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E70" s="10" t="str">
+        <x:v>10.1063/5.0164229</x:v>
+      </x:c>
+      <x:c r="F70" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G70" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H70" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I70" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0164229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="33" customHeight="1">
+      <x:c r="A71" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B71" s="10" t="str">
+        <x:v>2023-09-20 (day)</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>Ferroelectric-programmed photonic computing in monolayer WS2</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E71" s="10" t="str">
+        <x:v>10.1063/5.0165109</x:v>
+      </x:c>
+      <x:c r="F71" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H71" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I71" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0165109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="33" customHeight="1">
+      <x:c r="A72" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B72" s="10" t="str">
+        <x:v>2024-02-01 (day)</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="str">
+        <x:v>PbS/CsPbBr
+                    3
+                    Heterojunction for Broadband Neuromorphic Vision Sensing</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="str">
+        <x:v>ACS Applied Materials &amp; Interfaces</x:v>
+      </x:c>
+      <x:c r="E72" s="10" t="str">
+        <x:v>10.1021/acsami.3c17935</x:v>
+      </x:c>
+      <x:c r="F72" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G72" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H72" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I72" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsami.3c17935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="37.5" customHeight="1">
+      <x:c r="A73" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B73" s="10" t="str">
+        <x:v>2024-02-24 (day)</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
+        <x:v>Si/CuO Heterojunction‐Based Photomemristor for Reconfigurable, Non‐Volatile, and Self‐Powered In‐Sensor Computing</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E73" s="10" t="str">
+        <x:v>10.1002/smll.202309945</x:v>
+      </x:c>
+      <x:c r="F73" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G73" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H73" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I73" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/smll.202309945</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="37.5" customHeight="1">
+      <x:c r="A74" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="str">
+        <x:v>2024-05-09 (day)</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>Dimension-Confined Growth of a Crack-Free PbS Microplate Array for Infrared Image Sensing</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>ACS Applied Materials &amp; Interfaces</x:v>
+      </x:c>
+      <x:c r="E74" s="10" t="str">
+        <x:v>10.1021/acsami.4c01807</x:v>
+      </x:c>
+      <x:c r="F74" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H74" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I74" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsami.4c01807</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="37.5" customHeight="1">
+      <x:c r="A75" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="str">
+        <x:v>2024-06-27 (day)</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>Highly precise optical positioning through deep learning-assisted photo-thermoelectric detection</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E75" s="10" t="str">
+        <x:v>10.1063/5.0207986</x:v>
+      </x:c>
+      <x:c r="F75" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H75" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I75" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0207986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="37.5" customHeight="1">
+      <x:c r="A76" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B76" s="10" t="str">
+        <x:v>2024-12-03 (day)</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>Ultra-broadband detection by photovoltaic and thermoelectric coupling based on large-scale single-crystalline SnSe thin film</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E76" s="10" t="str">
+        <x:v>10.1063/5.0238951</x:v>
+      </x:c>
+      <x:c r="F76" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G76" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H76" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I76" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0238951</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="37.5" customHeight="1">
+      <x:c r="A77" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B77" s="10" t="str">
+        <x:v>2024-12-29 (day)</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>Ion Intercalation‐Enabled Reconfigurable Photodetector with Low Programming Voltage and Broadband Response Based on Van Der Waals Tin Disulfide</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E77" s="10" t="str">
+        <x:v>10.1002/smll.202408545</x:v>
+      </x:c>
+      <x:c r="F77" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G77" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H77" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I77" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1002/smll.202408545</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="33" customHeight="1">
+      <x:c r="A78" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B78" s="10" t="str">
+        <x:v>2025-07-07 (day)</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>Optical image encryption with photo-thermoelectric device</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>Optics Express</x:v>
+      </x:c>
+      <x:c r="E78" s="10" t="str">
+        <x:v>10.1364/oe.563795</x:v>
+      </x:c>
+      <x:c r="F78" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G78" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H78" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I78" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1364/oe.563795</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="37.5" customHeight="1">
+      <x:c r="A79" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B79" s="10" t="str">
+        <x:v>2025-07-14 (day)</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="str">
+        <x:v>Interface phonon coupling-boosted photo-thermoelectric response in a SrTiO3/PbSe heterostructure</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E79" s="10" t="str">
+        <x:v>10.1063/5.0283129</x:v>
+      </x:c>
+      <x:c r="F79" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H79" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I79" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1063/5.0283129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="37.5" customHeight="1">
+      <x:c r="A80" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B80" s="10" t="str">
+        <x:v>2025-08-20 (day)</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>Spatial confined hot carrier dynamics for beyond unity quantum efficiency detection</x:v>
+      </x:c>
+      <x:c r="D80" s="10" t="str">
+        <x:v>Nature Communications</x:v>
+      </x:c>
+      <x:c r="E80" s="10" t="str">
+        <x:v>10.1038/s41467-025-62548-6</x:v>
+      </x:c>
+      <x:c r="F80" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G80" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H80" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I80" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1038/s41467-025-62548-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="37.5" customHeight="1">
+      <x:c r="A81" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B81" s="10" t="str">
+        <x:v>2025-10-18 (day)</x:v>
+      </x:c>
+      <x:c r="C81" s="10" t="str">
+        <x:v>Multitask Multiplexed Switchable Infrared Optoelectronic Detection Based on Band Switch</x:v>
+      </x:c>
+      <x:c r="D81" s="10" t="str">
+        <x:v>ACS Photonics</x:v>
+      </x:c>
+      <x:c r="E81" s="10" t="str">
+        <x:v>10.1021/acsphotonics.5c01554</x:v>
+      </x:c>
+      <x:c r="F81" s="10" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G81" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H81" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I81" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsphotonics.5c01554</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="33" customHeight="1">
+      <x:c r="A82" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B82" s="10" t="str">
+        <x:v>2026-05-30 (day)</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="str">
+        <x:v>PbSe/WTe
+                    2
+                    Schottky Heterojunction for Low-Noise Mid-Infrared Detection</x:v>
+      </x:c>
+      <x:c r="D82" s="10" t="str">
+        <x:v>ACS Applied Materials &amp; Interfaces</x:v>
+      </x:c>
+      <x:c r="E82" s="10" t="str">
+        <x:v>10.1021/acsami.6c06229</x:v>
+      </x:c>
+      <x:c r="F82" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G82" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H82" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I82" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsami.6c06229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="33" customHeight="1">
+      <x:c r="A83" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B83" s="10" t="str">
+        <x:v>2026-06-01 (day)</x:v>
+      </x:c>
+      <x:c r="C83" s="10" t="str">
+        <x:v>Solar-Blind
+UV and NIR Bipolar Photodiode for 1069 Key Space Optical
+Encryption</x:v>
+      </x:c>
+      <x:c r="D83" s="10" t="str">
+        <x:v>ACS Photonics</x:v>
+      </x:c>
+      <x:c r="E83" s="10" t="str">
+        <x:v>10.1021/acsphotonics.6c00576</x:v>
+      </x:c>
+      <x:c r="F83" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G83" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H83" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I83" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsphotonics.6c00576</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="33" customHeight="1">
+      <x:c r="A84" s="10" t="str">
+        <x:v>王启胜</x:v>
+      </x:c>
+      <x:c r="B84" s="10" t="str">
+        <x:v>2026-07-28 (day)</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="str">
+        <x:v>Intrinsic Photovoltaic
+Effect-Enhanced Polarimetric
+Detection in Chiral Tellurium Nanowires Thin Film</x:v>
+      </x:c>
+      <x:c r="D84" s="10" t="str">
+        <x:v>ACS Photonics</x:v>
+      </x:c>
+      <x:c r="E84" s="10" t="str">
+        <x:v>10.1021/acsphotonics.6c00776</x:v>
+      </x:c>
+      <x:c r="F84" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G84" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H84" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I84" s="10" t="str">
+        <x:v>https://www.x-mol.com/groups/wang_qisheng/publications
+https://doi.org/10.1021/acsphotonics.6c00776</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="33" customHeight="1">
+      <x:c r="A85" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B85" s="10" t="str">
+        <x:v>2021-12-21 (day)</x:v>
+      </x:c>
+      <x:c r="C85" s="10" t="str">
+        <x:v>Dirac cones with zero refractive indices in phoxonic crystals</x:v>
+      </x:c>
+      <x:c r="D85" s="10" t="str">
+        <x:v>Optics Express</x:v>
+      </x:c>
+      <x:c r="E85" s="10" t="str">
+        <x:v>10.1364/oe.446356</x:v>
+      </x:c>
+      <x:c r="F85" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G85" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H85" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I85" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/oe.446356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="37.5" customHeight="1">
+      <x:c r="A86" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B86" s="10" t="str">
+        <x:v>2022-05-20 (day)</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="str">
+        <x:v>Manipulating strong coupling between exciton and quasibound states in the continuum resonance</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E86" s="10" t="str">
+        <x:v>10.1103/physrevb.105.195425</x:v>
+      </x:c>
+      <x:c r="F86" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G86" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H86" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I86" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1103/physrevb.105.195425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="37.5" customHeight="1">
+      <x:c r="A87" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B87" s="10" t="str">
+        <x:v>2022-10-11 (day)</x:v>
+      </x:c>
+      <x:c r="C87" s="10" t="str">
+        <x:v>Manipulating the optical beam width in topological pseudospin-dependent waveguides using all-dielectric photonic crystals</x:v>
+      </x:c>
+      <x:c r="D87" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E87" s="10" t="str">
+        <x:v>10.1364/ol.474271</x:v>
+      </x:c>
+      <x:c r="F87" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G87" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H87" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I87" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/ol.474271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="37.5" customHeight="1">
+      <x:c r="A88" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B88" s="10" t="str">
+        <x:v>2022-11-09 (day)</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="str">
+        <x:v>Coexistence of photonic and phononic corner states in a second-order topological phoxonic crystal</x:v>
+      </x:c>
+      <x:c r="D88" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E88" s="10" t="str">
+        <x:v>10.1063/5.0127301</x:v>
+      </x:c>
+      <x:c r="F88" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G88" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H88" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I88" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1063/5.0127301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="37.5" customHeight="1">
+      <x:c r="A89" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B89" s="10" t="str">
+        <x:v>2022-12 (month)</x:v>
+      </x:c>
+      <x:c r="C89" s="10" t="str">
+        <x:v>Topological coupling and decoupling of photonic crystal waveguides: Application to topological wavelength demultiplexing</x:v>
+      </x:c>
+      <x:c r="D89" s="10" t="str">
+        <x:v>Optics &amp; Laser Technology</x:v>
+      </x:c>
+      <x:c r="E89" s="10" t="str">
+        <x:v>10.1016/j.optlastec.2022.108476</x:v>
+      </x:c>
+      <x:c r="F89" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G89" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H89" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I89" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1016/j.optlastec.2022.108476</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="37.5" customHeight="1">
+      <x:c r="A90" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B90" s="10" t="str">
+        <x:v>2023-01-17 (day)</x:v>
+      </x:c>
+      <x:c r="C90" s="10" t="str">
+        <x:v>Strong coupling between excitons and quasibound states in the continuum in bulk transition metal dichalcogenides</x:v>
+      </x:c>
+      <x:c r="D90" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E90" s="10" t="str">
+        <x:v>10.1103/physrevb.107.045417</x:v>
+      </x:c>
+      <x:c r="F90" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G90" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H90" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I90" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1103/physrevb.107.045417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="37.5" customHeight="1">
+      <x:c r="A91" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B91" s="10" t="str">
+        <x:v>2023-06-05 (day)</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="str">
+        <x:v>Optical resonance with subwavelength spectral coherence switch in open-end cavity</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="str">
+        <x:v>Science China Physics, Mechanics &amp; Astronomy</x:v>
+      </x:c>
+      <x:c r="E91" s="10" t="str">
+        <x:v>10.1007/s11433-023-2097-9</x:v>
+      </x:c>
+      <x:c r="F91" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G91" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H91" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I91" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1007/s11433-023-2097-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="37.5" customHeight="1">
+      <x:c r="A92" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B92" s="10" t="str">
+        <x:v>2023-06-07 (day)</x:v>
+      </x:c>
+      <x:c r="C92" s="10" t="str">
+        <x:v>Compact topological polarization beam splitter based on all-dielectric fishnet photonic crystals</x:v>
+      </x:c>
+      <x:c r="D92" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E92" s="10" t="str">
+        <x:v>10.1364/ol.492427</x:v>
+      </x:c>
+      <x:c r="F92" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G92" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H92" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I92" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/ol.492427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="37.5" customHeight="1">
+      <x:c r="A93" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B93" s="10" t="str">
+        <x:v>2023-06-21 (day)</x:v>
+      </x:c>
+      <x:c r="C93" s="10" t="str">
+        <x:v>Enhancing Faraday and Kerr rotations based on the toroidal dipole mode in an all-dielectric magneto-optical metasurface</x:v>
+      </x:c>
+      <x:c r="D93" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E93" s="10" t="str">
+        <x:v>10.1364/ol.492913</x:v>
+      </x:c>
+      <x:c r="F93" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G93" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H93" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I93" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/ol.492913</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="33" customHeight="1">
+      <x:c r="A94" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B94" s="10" t="str">
+        <x:v>2023-08-01 (day)</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="str">
+        <x:v>Non-line-of-sight imaging with absorption backprojection</x:v>
+      </x:c>
+      <x:c r="D94" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E94" s="10" t="str">
+        <x:v>10.1063/5.0156149</x:v>
+      </x:c>
+      <x:c r="F94" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G94" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H94" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I94" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1063/5.0156149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="33" customHeight="1">
+      <x:c r="A95" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B95" s="10" t="str">
+        <x:v>2023-08-04 (day)</x:v>
+      </x:c>
+      <x:c r="C95" s="10" t="str">
+        <x:v>Polarization-Independent Second-Order Photonic Topological Corner States</x:v>
+      </x:c>
+      <x:c r="D95" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E95" s="10" t="str">
+        <x:v>10.1103/physrevapplied.20.024014</x:v>
+      </x:c>
+      <x:c r="F95" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H95" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I95" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1103/physrevapplied.20.024014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="37.5" customHeight="1">
+      <x:c r="A96" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B96" s="10" t="str">
+        <x:v>2024-05-02 (day)</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="str">
+        <x:v>Tailoring intrinsic chirality in a two-dimensional planar waveguide grating via quasibound states in the continuum</x:v>
+      </x:c>
+      <x:c r="D96" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E96" s="10" t="str">
+        <x:v>10.1103/physrevb.109.205403</x:v>
+      </x:c>
+      <x:c r="F96" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G96" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H96" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I96" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1103/physrevb.109.205403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="33" customHeight="1">
+      <x:c r="A97" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B97" s="10" t="str">
+        <x:v>2024-05-30 (day)</x:v>
+      </x:c>
+      <x:c r="C97" s="10" t="str">
+        <x:v>Decision-making and control with diffractive optical networks</x:v>
+      </x:c>
+      <x:c r="D97" s="10" t="str">
+        <x:v>Advanced Photonics Nexus</x:v>
+      </x:c>
+      <x:c r="E97" s="10" t="str">
+        <x:v>10.1117/1.apn.3.4.046003</x:v>
+      </x:c>
+      <x:c r="F97" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G97" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H97" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I97" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1117/1.apn.3.4.046003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="37.5" customHeight="1">
+      <x:c r="A98" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B98" s="10" t="str">
+        <x:v>2024-10-15 (day)</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="str">
+        <x:v>Metasurface-Based Diffractive Optical Networks With Dual-Channel Complex Amplitude Modulation</x:v>
+      </x:c>
+      <x:c r="D98" s="10" t="str">
+        <x:v>Journal of Lightwave Technology</x:v>
+      </x:c>
+      <x:c r="E98" s="10" t="str">
+        <x:v>10.1109/jlt.2024.3420794</x:v>
+      </x:c>
+      <x:c r="F98" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G98" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H98" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I98" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1109/jlt.2024.3420794</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="37.5" customHeight="1">
+      <x:c r="A99" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B99" s="10" t="str">
+        <x:v>2024-11-19 (day)</x:v>
+      </x:c>
+      <x:c r="C99" s="10" t="str">
+        <x:v>Polarization-independent topological corner states based on all-dielectric valley photonic crystals</x:v>
+      </x:c>
+      <x:c r="D99" s="10" t="str">
+        <x:v>Optics Express</x:v>
+      </x:c>
+      <x:c r="E99" s="10" t="str">
+        <x:v>10.1364/oe.542654</x:v>
+      </x:c>
+      <x:c r="F99" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G99" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H99" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I99" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/oe.542654</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="33" customHeight="1">
+      <x:c r="A100" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B100" s="10" t="str">
+        <x:v>2025-03-14 (day)</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="str">
+        <x:v>High-efficiency broadband achromatic metalens in the visible</x:v>
+      </x:c>
+      <x:c r="D100" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E100" s="10" t="str">
+        <x:v>10.1063/5.0240728</x:v>
+      </x:c>
+      <x:c r="F100" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G100" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H100" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I100" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1063/5.0240728</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="33" customHeight="1">
+      <x:c r="A101" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B101" s="10" t="str">
+        <x:v>2025-04-15 (day)</x:v>
+      </x:c>
+      <x:c r="C101" s="10" t="str">
+        <x:v>Optoelectronic generative adversarial networks</x:v>
+      </x:c>
+      <x:c r="D101" s="10" t="str">
+        <x:v>Communications Physics</x:v>
+      </x:c>
+      <x:c r="E101" s="10" t="str">
+        <x:v>10.1038/s42005-025-02081-6</x:v>
+      </x:c>
+      <x:c r="F101" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G101" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H101" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I101" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1038/s42005-025-02081-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="37.5" customHeight="1">
+      <x:c r="A102" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B102" s="10" t="str">
+        <x:v>2025-04-28 (day)</x:v>
+      </x:c>
+      <x:c r="C102" s="10" t="str">
+        <x:v>Giant enhancement of the transverse magneto-optical Kerr effect in etchless bismuth iron garnet empowered by quasi-bound states in the continuum</x:v>
+      </x:c>
+      <x:c r="D102" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E102" s="10" t="str">
+        <x:v>10.1063/5.0260200</x:v>
+      </x:c>
+      <x:c r="F102" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G102" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H102" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I102" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1063/5.0260200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="33" customHeight="1">
+      <x:c r="A103" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B103" s="10" t="str">
+        <x:v>2025-05-27 (day)</x:v>
+      </x:c>
+      <x:c r="C103" s="10" t="str">
+        <x:v>Dual-band dislocation modes in a topological photonic crystal</x:v>
+      </x:c>
+      <x:c r="D103" s="10" t="str">
+        <x:v>Photonics Research</x:v>
+      </x:c>
+      <x:c r="E103" s="10" t="str">
+        <x:v>10.1364/prj.555997</x:v>
+      </x:c>
+      <x:c r="F103" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G103" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H103" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I103" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/prj.555997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="37.5" customHeight="1">
+      <x:c r="A104" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B104" s="10" t="str">
+        <x:v>2025-07-11 (day)</x:v>
+      </x:c>
+      <x:c r="C104" s="10" t="str">
+        <x:v>Enhancing Chemical Bonding at Buried Interface Enables Improved Performance of Perovskite Solar Cell</x:v>
+      </x:c>
+      <x:c r="D104" s="10" t="str">
+        <x:v>Small</x:v>
+      </x:c>
+      <x:c r="E104" s="10" t="str">
+        <x:v>10.1002/smll.202504930</x:v>
+      </x:c>
+      <x:c r="F104" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G104" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H104" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I104" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1002/smll.202504930</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="33" customHeight="1">
+      <x:c r="A105" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B105" s="10" t="str">
+        <x:v>2025-12-19 (day)</x:v>
+      </x:c>
+      <x:c r="C105" s="10" t="str">
+        <x:v>Observation of moiré plasmonic skyrmion clusters</x:v>
+      </x:c>
+      <x:c r="D105" s="10" t="str">
+        <x:v>Science Advances</x:v>
+      </x:c>
+      <x:c r="E105" s="10" t="str">
+        <x:v>10.1126/sciadv.adx0478</x:v>
+      </x:c>
+      <x:c r="F105" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G105" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H105" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I105" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1126/sciadv.adx0478</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="33" customHeight="1">
+      <x:c r="A106" s="10" t="str">
+        <x:v>于天宝</x:v>
+      </x:c>
+      <x:c r="B106" s="10" t="str">
+        <x:v>2026-04-09 (day)</x:v>
+      </x:c>
+      <x:c r="C106" s="10" t="str">
+        <x:v>Integrated spectropolarimeter by metasurface-based diffractive optical networks</x:v>
+      </x:c>
+      <x:c r="D106" s="10" t="str">
+        <x:v>Optica</x:v>
+      </x:c>
+      <x:c r="E106" s="10" t="str">
+        <x:v>10.1364/optica.583686</x:v>
+      </x:c>
+      <x:c r="F106" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G106" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H106" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I106" s="10" t="str">
+        <x:v>https://teacher.ncu.edu.cn/publish/090023/
+https://doi.org/10.1364/optica.583686</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="33" customHeight="1">
+      <x:c r="A107" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B107" s="10" t="str">
+        <x:v>1998-08-15 (day)</x:v>
+      </x:c>
+      <x:c r="C107" s="10" t="str">
+        <x:v>Creation of partial band gaps in anisotropic photonic-band-gap structures</x:v>
+      </x:c>
+      <x:c r="D107" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E107" s="10" t="str">
+        <x:v>10.1103/physrevb.58.3721</x:v>
+      </x:c>
+      <x:c r="F107" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H107" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I107" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevb.58.3721</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="33" customHeight="1">
+      <x:c r="A108" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B108" s="10" t="str">
+        <x:v>1998-09-21 (day)</x:v>
+      </x:c>
+      <x:c r="C108" s="10" t="str">
+        <x:v>Large Absolute Band Gap in 2D Anisotropic Photonic Crystals</x:v>
+      </x:c>
+      <x:c r="D108" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E108" s="10" t="str">
+        <x:v>10.1103/physrevlett.81.2574</x:v>
+      </x:c>
+      <x:c r="F108" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H108" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I108" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevlett.81.2574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="33" customHeight="1">
+      <x:c r="A109" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B109" s="10" t="str">
+        <x:v>2000-05-08 (day)</x:v>
+      </x:c>
+      <x:c r="C109" s="10" t="str">
+        <x:v>Spontaneous Emission from Photonic Crystals: Full Vectorial Calculations</x:v>
+      </x:c>
+      <x:c r="D109" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E109" s="10" t="str">
+        <x:v>10.1103/physrevlett.84.4341</x:v>
+      </x:c>
+      <x:c r="F109" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H109" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I109" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevlett.84.4341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="33" customHeight="1">
+      <x:c r="A110" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B110" s="10" t="str">
+        <x:v>2000-07-15 (day)</x:v>
+      </x:c>
+      <x:c r="C110" s="10" t="str">
+        <x:v>Fragility of photonic band gaps in inverse-opal photonic crystals</x:v>
+      </x:c>
+      <x:c r="D110" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E110" s="10" t="str">
+        <x:v>10.1103/physrevb.62.1516</x:v>
+      </x:c>
+      <x:c r="F110" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H110" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I110" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevb.62.1516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="33" customHeight="1">
+      <x:c r="A111" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B111" s="10" t="str">
+        <x:v>2002-06-20 (day)</x:v>
+      </x:c>
+      <x:c r="C111" s="10" t="str">
+        <x:v>Synthesis and Self-Assembly of Au@SiO2 Core−Shell Colloids</x:v>
+      </x:c>
+      <x:c r="D111" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E111" s="10" t="str">
+        <x:v>10.1021/nl025598i</x:v>
+      </x:c>
+      <x:c r="F111" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H111" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I111" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl025598i</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="33" customHeight="1">
+      <x:c r="A112" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B112" s="10" t="str">
+        <x:v>2003-04-15 (day)</x:v>
+      </x:c>
+      <x:c r="C112" s="10" t="str">
+        <x:v>Photonic band structures solved by a plane-wave-based transfer-matrix method</x:v>
+      </x:c>
+      <x:c r="D112" s="10" t="str">
+        <x:v>Physical Review E</x:v>
+      </x:c>
+      <x:c r="E112" s="10" t="str">
+        <x:v>10.1103/physreve.67.046607</x:v>
+      </x:c>
+      <x:c r="F112" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H112" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I112" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physreve.67.046607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="37.5" customHeight="1">
+      <x:c r="A113" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B113" s="10" t="str">
+        <x:v>2003-10-02 (day)</x:v>
+      </x:c>
+      <x:c r="C113" s="10" t="str">
+        <x:v>Light propagation in semi-infinite photonic crystals and related waveguide structures</x:v>
+      </x:c>
+      <x:c r="D113" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E113" s="10" t="str">
+        <x:v>10.1103/physrevb.68.155101</x:v>
+      </x:c>
+      <x:c r="F113" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevb.68.155101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="33" customHeight="1">
+      <x:c r="A114" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B114" s="10" t="str">
+        <x:v>2003-12-12 (day)</x:v>
+      </x:c>
+      <x:c r="C114" s="10" t="str">
+        <x:v>Evaluation of lensing in photonic crystal slabs exhibiting negative refraction</x:v>
+      </x:c>
+      <x:c r="D114" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E114" s="10" t="str">
+        <x:v>10.1103/physrevb.68.245110</x:v>
+      </x:c>
+      <x:c r="F114" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H114" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I114" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevb.68.245110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="33" customHeight="1">
+      <x:c r="A115" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B115" s="10" t="str">
+        <x:v>2004-02-12 (day)</x:v>
+      </x:c>
+      <x:c r="C115" s="10" t="str">
+        <x:v>Anomalous Propagation Loss in Photonic Crystal Waveguides</x:v>
+      </x:c>
+      <x:c r="D115" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E115" s="10" t="str">
+        <x:v>10.1103/physrevlett.92.063904</x:v>
+      </x:c>
+      <x:c r="F115" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H115" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I115" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevlett.92.063904</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="37.5" customHeight="1">
+      <x:c r="A116" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B116" s="10" t="str">
+        <x:v>2005-02-08 (day)</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>Gold Nanocages:  Bioconjugation and Their Potential Use as Optical Imaging Contrast Agents</x:v>
+      </x:c>
+      <x:c r="D116" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E116" s="10" t="str">
+        <x:v>10.1021/nl047950t</x:v>
+      </x:c>
+      <x:c r="F116" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G116" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H116" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl047950t</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="33" customHeight="1">
+      <x:c r="A117" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B117" s="10" t="str">
+        <x:v>2005-06-23 (day)</x:v>
+      </x:c>
+      <x:c r="C117" s="10" t="str">
+        <x:v>Negative Refraction and Imaging Using 12-fold-Symmetry Quasicrystals</x:v>
+      </x:c>
+      <x:c r="D117" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E117" s="10" t="str">
+        <x:v>10.1103/physrevlett.94.247402</x:v>
+      </x:c>
+      <x:c r="F117" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G117" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H117" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I117" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevlett.94.247402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="37.5" customHeight="1">
+      <x:c r="A118" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B118" s="10" t="str">
+        <x:v>2006 (year)</x:v>
+      </x:c>
+      <x:c r="C118" s="10" t="str">
+        <x:v>Gold nanostructures: engineering their plasmonic properties for biomedical applications</x:v>
+      </x:c>
+      <x:c r="D118" s="10" t="str">
+        <x:v>Chemical Society Reviews</x:v>
+      </x:c>
+      <x:c r="E118" s="10" t="str">
+        <x:v>10.1039/b517615h</x:v>
+      </x:c>
+      <x:c r="F118" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G118" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H118" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1039/b517615h</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="37.5" customHeight="1">
+      <x:c r="A119" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B119" s="10" t="str">
+        <x:v>2006-06-30 (day)</x:v>
+      </x:c>
+      <x:c r="C119" s="10" t="str">
+        <x:v>Maneuvering the Surface Plasmon Resonance of Silver Nanostructures through Shape-Controlled Synthesis</x:v>
+      </x:c>
+      <x:c r="D119" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry B</x:v>
+      </x:c>
+      <x:c r="E119" s="10" t="str">
+        <x:v>10.1021/jp0608628</x:v>
+      </x:c>
+      <x:c r="F119" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G119" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H119" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I119" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/jp0608628</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="37.5" customHeight="1">
+      <x:c r="A120" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B120" s="10" t="str">
+        <x:v>2007-03-22 (day)</x:v>
+      </x:c>
+      <x:c r="C120" s="10" t="str">
+        <x:v>The SERS Activity of a Supported Ag Nanocube Strongly Depends on Its Orientation Relative to Laser Polarization</x:v>
+      </x:c>
+      <x:c r="D120" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E120" s="10" t="str">
+        <x:v>10.1021/nl070157q</x:v>
+      </x:c>
+      <x:c r="F120" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G120" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H120" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I120" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl070157q</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="37.5" customHeight="1">
+      <x:c r="A121" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B121" s="10" t="str">
+        <x:v>2007-04-13 (day)</x:v>
+      </x:c>
+      <x:c r="C121" s="10" t="str">
+        <x:v>Immuno Gold Nanocages with Tailored Optical Properties for Targeted Photothermal Destruction of Cancer Cells</x:v>
+      </x:c>
+      <x:c r="D121" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E121" s="10" t="str">
+        <x:v>10.1021/nl070345g</x:v>
+      </x:c>
+      <x:c r="F121" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G121" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H121" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I121" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl070345g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="37.5" customHeight="1">
+      <x:c r="A122" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B122" s="10" t="str">
+        <x:v>2007-05-09 (day)</x:v>
+      </x:c>
+      <x:c r="C122" s="10" t="str">
+        <x:v>Second harmonic generation in one-dimensional nonlinear photonic crystals solved by the transfer matrix method</x:v>
+      </x:c>
+      <x:c r="D122" s="10" t="str">
+        <x:v>Physical Review E</x:v>
+      </x:c>
+      <x:c r="E122" s="10" t="str">
+        <x:v>10.1103/physreve.75.056606</x:v>
+      </x:c>
+      <x:c r="F122" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G122" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H122" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I122" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physreve.75.056606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="37.5" customHeight="1">
+      <x:c r="A123" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B123" s="10" t="str">
+        <x:v>2007-11-20 (day)</x:v>
+      </x:c>
+      <x:c r="C123" s="10" t="str">
+        <x:v>Photoacoustic Tomography of a Rat Cerebral Cortex in vivo with Au Nanocages as an Optical Contrast Agent</x:v>
+      </x:c>
+      <x:c r="D123" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E123" s="10" t="str">
+        <x:v>10.1021/nl072349r</x:v>
+      </x:c>
+      <x:c r="F123" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G123" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H123" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I123" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl072349r</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="37.5" customHeight="1">
+      <x:c r="A124" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B124" s="10" t="str">
+        <x:v>2008-11-26 (day)</x:v>
+      </x:c>
+      <x:c r="C124" s="10" t="str">
+        <x:v>Quantitative Analysis of Dipole and Quadrupole Excitation in the Surface Plasmon Resonance of Metal Nanoparticles</x:v>
+      </x:c>
+      <x:c r="D124" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E124" s="10" t="str">
+        <x:v>10.1021/jp807075f</x:v>
+      </x:c>
+      <x:c r="F124" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G124" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H124" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I124" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/jp807075f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="33" customHeight="1">
+      <x:c r="A125" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B125" s="10" t="str">
+        <x:v>2009-10-02 (day)</x:v>
+      </x:c>
+      <x:c r="C125" s="10" t="str">
+        <x:v>10 fs ultrafast all-optical switching in polystyrene nonlinear photonic crystals</x:v>
+      </x:c>
+      <x:c r="D125" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E125" s="10" t="str">
+        <x:v>10.1063/1.3242025</x:v>
+      </x:c>
+      <x:c r="F125" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G125" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H125" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I125" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1063/1.3242025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="37.5" customHeight="1">
+      <x:c r="A126" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B126" s="10" t="str">
+        <x:v>2009-12-03 (day)</x:v>
+      </x:c>
+      <x:c r="C126" s="10" t="str">
+        <x:v>Metal Nanoparticles with Gain toward Single-Molecule Detection by Surface-Enhanced Raman Scattering</x:v>
+      </x:c>
+      <x:c r="D126" s="10" t="str">
+        <x:v>Nano Letters</x:v>
+      </x:c>
+      <x:c r="E126" s="10" t="str">
+        <x:v>10.1021/nl903409x</x:v>
+      </x:c>
+      <x:c r="F126" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H126" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I126" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nl903409x</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="37.5" customHeight="1">
+      <x:c r="A127" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B127" s="10" t="str">
+        <x:v>2010-06-04 (day)</x:v>
+      </x:c>
+      <x:c r="C127" s="10" t="str">
+        <x:v>The Growth Mechanism of Copper Nanowires and Their Properties in Flexible, Transparent Conducting Films</x:v>
+      </x:c>
+      <x:c r="D127" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E127" s="10" t="str">
+        <x:v>10.1002/adma.201000775</x:v>
+      </x:c>
+      <x:c r="F127" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G127" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H127" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I127" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1002/adma.201000775</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="37.5" customHeight="1">
+      <x:c r="A128" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B128" s="10" t="str">
+        <x:v>2010-07-27 (day)</x:v>
+      </x:c>
+      <x:c r="C128" s="10" t="str">
+        <x:v>Robust one-way modes in gyromagnetic photonic crystal waveguides with different interfaces</x:v>
+      </x:c>
+      <x:c r="D128" s="10" t="str">
+        <x:v>Applied Physics Letters</x:v>
+      </x:c>
+      <x:c r="E128" s="10" t="str">
+        <x:v>10.1063/1.3470873</x:v>
+      </x:c>
+      <x:c r="F128" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G128" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H128" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I128" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1063/1.3470873</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="37.5" customHeight="1">
+      <x:c r="A129" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B129" s="10" t="str">
+        <x:v>2011-01-18 (day)</x:v>
+      </x:c>
+      <x:c r="C129" s="10" t="str">
+        <x:v>All-optical logic gates based on two-dimensional low-refractive-index nonlinear photonic crystal slabs</x:v>
+      </x:c>
+      <x:c r="D129" s="10" t="str">
+        <x:v>Optics Express</x:v>
+      </x:c>
+      <x:c r="E129" s="10" t="str">
+        <x:v>10.1364/oe.19.001945</x:v>
+      </x:c>
+      <x:c r="F129" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G129" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H129" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I129" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/oe.19.001945</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="33" customHeight="1">
+      <x:c r="A130" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B130" s="10" t="str">
+        <x:v>2011-04-01 (day)</x:v>
+      </x:c>
+      <x:c r="C130" s="10" t="str">
+        <x:v>Efficient surface plasmon amplification from gain-assisted gold nanorods</x:v>
+      </x:c>
+      <x:c r="D130" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E130" s="10" t="str">
+        <x:v>10.1364/ol.36.001296</x:v>
+      </x:c>
+      <x:c r="F130" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G130" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H130" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I130" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/ol.36.001296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="37.5" customHeight="1">
+      <x:c r="A131" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B131" s="10" t="str">
+        <x:v>2011-11-11 (day)</x:v>
+      </x:c>
+      <x:c r="C131" s="10" t="str">
+        <x:v>Recent progress in engineering and application of surface plasmon resonance in metal nanostructures</x:v>
+      </x:c>
+      <x:c r="D131" s="10" t="str">
+        <x:v>Chinese Science Bulletin</x:v>
+      </x:c>
+      <x:c r="E131" s="10" t="str">
+        <x:v>10.1360/972011-1500</x:v>
+      </x:c>
+      <x:c r="F131" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G131" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H131" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I131" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1360/972011-1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="33" customHeight="1">
+      <x:c r="A132" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B132" s="10" t="str">
+        <x:v>2011-12-16 (day)</x:v>
+      </x:c>
+      <x:c r="C132" s="10" t="str">
+        <x:v>On-chip optical diode based on silicon photonic crystal heterojunctions</x:v>
+      </x:c>
+      <x:c r="D132" s="10" t="str">
+        <x:v>Optics Express</x:v>
+      </x:c>
+      <x:c r="E132" s="10" t="str">
+        <x:v>10.1364/oe.19.026948</x:v>
+      </x:c>
+      <x:c r="F132" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G132" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H132" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I132" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/oe.19.026948</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="37.5" customHeight="1">
+      <x:c r="A133" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B133" s="10" t="str">
+        <x:v>2012-05-03 (day)</x:v>
+      </x:c>
+      <x:c r="C133" s="10" t="str">
+        <x:v>Manipulation of gold nanorods with dual-optical tweezers for surface plasmon resonance control</x:v>
+      </x:c>
+      <x:c r="D133" s="10" t="str">
+        <x:v>Nanotechnology</x:v>
+      </x:c>
+      <x:c r="E133" s="10" t="str">
+        <x:v>10.1088/0957-4484/23/21/215302</x:v>
+      </x:c>
+      <x:c r="F133" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G133" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H133" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I133" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1088/0957-4484/23/21/215302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="33" customHeight="1">
+      <x:c r="A134" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B134" s="10" t="str">
+        <x:v>2012-05-14 (day)</x:v>
+      </x:c>
+      <x:c r="C134" s="10" t="str">
+        <x:v>Optical trapping of gold nanoparticles by cylindrical vector beam</x:v>
+      </x:c>
+      <x:c r="D134" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E134" s="10" t="str">
+        <x:v>10.1364/ol.37.001694</x:v>
+      </x:c>
+      <x:c r="F134" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G134" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H134" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I134" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/ol.37.001694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="33" customHeight="1">
+      <x:c r="A135" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B135" s="10" t="str">
+        <x:v>2012-08-17 (day)</x:v>
+      </x:c>
+      <x:c r="C135" s="10" t="str">
+        <x:v>Wavefront shaping of infrared light through a subwavelength hole</x:v>
+      </x:c>
+      <x:c r="D135" s="10" t="str">
+        <x:v>Light: Science &amp; Applications</x:v>
+      </x:c>
+      <x:c r="E135" s="10" t="str">
+        <x:v>10.1038/lsa.2012.26</x:v>
+      </x:c>
+      <x:c r="F135" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G135" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H135" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I135" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1038/lsa.2012.26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="33" customHeight="1">
+      <x:c r="A136" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B136" s="10" t="str">
+        <x:v>2012-09-19 (day)</x:v>
+      </x:c>
+      <x:c r="C136" s="10" t="str">
+        <x:v>Linear and passive silicon optical isolator</x:v>
+      </x:c>
+      <x:c r="D136" s="10" t="str">
+        <x:v>Scientific Reports</x:v>
+      </x:c>
+      <x:c r="E136" s="10" t="str">
+        <x:v>10.1038/srep00674</x:v>
+      </x:c>
+      <x:c r="F136" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G136" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H136" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I136" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1038/srep00674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="37.5" customHeight="1">
+      <x:c r="A137" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B137" s="10" t="str">
+        <x:v>2013-02-12 (day)</x:v>
+      </x:c>
+      <x:c r="C137" s="10" t="str">
+        <x:v>Comparison Study of Gold Nanohexapods, Nanorods, and Nanocages for Photothermal Cancer Treatment</x:v>
+      </x:c>
+      <x:c r="D137" s="10" t="str">
+        <x:v>ACS Nano</x:v>
+      </x:c>
+      <x:c r="E137" s="10" t="str">
+        <x:v>10.1021/nn304332s</x:v>
+      </x:c>
+      <x:c r="F137" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G137" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H137" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I137" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/nn304332s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="37.5" customHeight="1">
+      <x:c r="A138" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B138" s="10" t="str">
+        <x:v>2013-05-13 (day)</x:v>
+      </x:c>
+      <x:c r="C138" s="10" t="str">
+        <x:v>Simultaneous Excitation and Emission Enhancement of Fluorescence Assisted by Double Plasmon Modes of Gold Nanorods</x:v>
+      </x:c>
+      <x:c r="D138" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E138" s="10" t="str">
+        <x:v>10.1021/jp4001626</x:v>
+      </x:c>
+      <x:c r="F138" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G138" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H138" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I138" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/jp4001626</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="37.5" customHeight="1">
+      <x:c r="A139" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B139" s="10" t="str">
+        <x:v>2013-06-11 (day)</x:v>
+      </x:c>
+      <x:c r="C139" s="10" t="str">
+        <x:v>Microscopic and macroscopic manipulation of gold nanorod and its hybrid nanostructures [Invited]</x:v>
+      </x:c>
+      <x:c r="D139" s="10" t="str">
+        <x:v>Photonics Research</x:v>
+      </x:c>
+      <x:c r="E139" s="10" t="str">
+        <x:v>10.1364/prj.1.000028</x:v>
+      </x:c>
+      <x:c r="F139" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G139" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H139" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I139" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/prj.1.000028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="37.5" customHeight="1">
+      <x:c r="A140" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B140" s="10" t="str">
+        <x:v>2013-08-05 (day)</x:v>
+      </x:c>
+      <x:c r="C140" s="10" t="str">
+        <x:v>Origin of Shape Resonance in Second-Harmonic Generation from Metallic Nanohole Arrays</x:v>
+      </x:c>
+      <x:c r="D140" s="10" t="str">
+        <x:v>Scientific Reports</x:v>
+      </x:c>
+      <x:c r="E140" s="10" t="str">
+        <x:v>10.1038/srep02358</x:v>
+      </x:c>
+      <x:c r="F140" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G140" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H140" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I140" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1038/srep02358</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="37.5" customHeight="1">
+      <x:c r="A141" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B141" s="10" t="str">
+        <x:v>2014 (year)</x:v>
+      </x:c>
+      <x:c r="C141" s="10" t="str">
+        <x:v>Polystyrene Kerr nonlinear photonic crystals for building ultrafast optical switching and logic devices</x:v>
+      </x:c>
+      <x:c r="D141" s="10" t="str">
+        <x:v>J. Mater. Chem. C</x:v>
+      </x:c>
+      <x:c r="E141" s="10" t="str">
+        <x:v>10.1039/c3tc31914h</x:v>
+      </x:c>
+      <x:c r="F141" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G141" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H141" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I141" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1039/c3tc31914h</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="33" customHeight="1">
+      <x:c r="A142" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B142" s="10" t="str">
+        <x:v>2014-01-13 (day)</x:v>
+      </x:c>
+      <x:c r="C142" s="10" t="str">
+        <x:v>Direct method to control surface plasmon polaritons on metal surfaces</x:v>
+      </x:c>
+      <x:c r="D142" s="10" t="str">
+        <x:v>Optics Letters</x:v>
+      </x:c>
+      <x:c r="E142" s="10" t="str">
+        <x:v>10.1364/ol.39.000339</x:v>
+      </x:c>
+      <x:c r="F142" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G142" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H142" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I142" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1364/ol.39.000339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="37.5" customHeight="1">
+      <x:c r="A143" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B143" s="10" t="str">
+        <x:v>2014-01-21 (day)</x:v>
+      </x:c>
+      <x:c r="C143" s="10" t="str">
+        <x:v>Highly Sensitive, Uniform, and Reproducible Surface‐Enhanced Raman Spectroscopy from Hollow Au‐Ag Alloy Nanourchins</x:v>
+      </x:c>
+      <x:c r="D143" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E143" s="10" t="str">
+        <x:v>10.1002/adma.201305106</x:v>
+      </x:c>
+      <x:c r="F143" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G143" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H143" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I143" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1002/adma.201305106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="37.5" customHeight="1">
+      <x:c r="A144" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B144" s="10" t="str">
+        <x:v>2014-04-02 (day)</x:v>
+      </x:c>
+      <x:c r="C144" s="10" t="str">
+        <x:v>Direct laser writing of symmetry‐broken spiral tapers for polarization‐insensitive three‐dimensional plasmonic focusing</x:v>
+      </x:c>
+      <x:c r="D144" s="10" t="str">
+        <x:v>Laser &amp; Photonics Reviews</x:v>
+      </x:c>
+      <x:c r="E144" s="10" t="str">
+        <x:v>10.1002/lpor.201300206</x:v>
+      </x:c>
+      <x:c r="F144" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G144" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H144" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I144" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1002/lpor.201300206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="37.5" customHeight="1">
+      <x:c r="A145" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B145" s="10" t="str">
+        <x:v>2014-07-18 (day)</x:v>
+      </x:c>
+      <x:c r="C145" s="10" t="str">
+        <x:v>Simultaneous broadband generation of second and third harmonics from chirped nonlinear photonic crystals</x:v>
+      </x:c>
+      <x:c r="D145" s="10" t="str">
+        <x:v>Light: Science &amp; Applications</x:v>
+      </x:c>
+      <x:c r="E145" s="10" t="str">
+        <x:v>10.1038/lsa.2014.70</x:v>
+      </x:c>
+      <x:c r="F145" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G145" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H145" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I145" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1038/lsa.2014.70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="37.5" customHeight="1">
+      <x:c r="A146" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B146" s="10" t="str">
+        <x:v>2014-10-19 (day)</x:v>
+      </x:c>
+      <x:c r="C146" s="10" t="str">
+        <x:v>Efficient Coupling of Solar Energy to Catalytic Hydrogenation by Using Well‐Designed Palladium Nanostructures</x:v>
+      </x:c>
+      <x:c r="D146" s="10" t="str">
+        <x:v>Angewandte Chemie International Edition</x:v>
+      </x:c>
+      <x:c r="E146" s="10" t="str">
+        <x:v>10.1002/anie.201407785</x:v>
+      </x:c>
+      <x:c r="F146" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G146" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H146" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I146" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1002/anie.201407785</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="37.5" customHeight="1">
+      <x:c r="A147" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B147" s="10" t="str">
+        <x:v>2014-11-13 (day)</x:v>
+      </x:c>
+      <x:c r="C147" s="10" t="str">
+        <x:v>Elementary analysis of interferometers for wave—particle duality test and the prospect of going beyond the complementarity principle</x:v>
+      </x:c>
+      <x:c r="D147" s="10" t="str">
+        <x:v>Chinese Physics B</x:v>
+      </x:c>
+      <x:c r="E147" s="10" t="str">
+        <x:v>10.1088/1674-1056/23/11/110309</x:v>
+      </x:c>
+      <x:c r="F147" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H147" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I147" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1088/1674-1056/23/11/110309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="33" customHeight="1">
+      <x:c r="A148" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B148" s="10" t="str">
+        <x:v>2015-03-31 (day)</x:v>
+      </x:c>
+      <x:c r="C148" s="10" t="str">
+        <x:v>Optics and photonics at nanoscale: Principles and perspectives</x:v>
+      </x:c>
+      <x:c r="D148" s="10" t="str">
+        <x:v>EPL (Europhysics Letters)</x:v>
+      </x:c>
+      <x:c r="E148" s="10" t="str">
+        <x:v>10.1209/0295-5075/110/14001</x:v>
+      </x:c>
+      <x:c r="F148" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H148" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I148" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1209/0295-5075/110/14001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="33" customHeight="1">
+      <x:c r="A149" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B149" s="10" t="str">
+        <x:v>2015-05-11 (day)</x:v>
+      </x:c>
+      <x:c r="C149" s="10" t="str">
+        <x:v>Optical Origin of Subnanometer Resolution in Tip-Enhanced Raman Mapping</x:v>
+      </x:c>
+      <x:c r="D149" s="10" t="str">
+        <x:v>The Journal of Physical Chemistry C</x:v>
+      </x:c>
+      <x:c r="E149" s="10" t="str">
+        <x:v>10.1021/acs.jpcc.5b02653</x:v>
+      </x:c>
+      <x:c r="F149" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G149" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H149" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I149" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/acs.jpcc.5b02653</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="37.5" customHeight="1">
+      <x:c r="A150" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B150" s="10" t="str">
+        <x:v>2015-08-20 (day)</x:v>
+      </x:c>
+      <x:c r="C150" s="10" t="str">
+        <x:v>High-Efficiency Broadband High-Harmonic Generation from a Single Quasi-Phase-Matching Nonlinear Crystal</x:v>
+      </x:c>
+      <x:c r="D150" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E150" s="10" t="str">
+        <x:v>10.1103/physrevlett.115.083902</x:v>
+      </x:c>
+      <x:c r="F150" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G150" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H150" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I150" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1103/physrevlett.115.083902</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="33" customHeight="1">
+      <x:c r="A151" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B151" s="10" t="str">
+        <x:v>2015-11-04 (day)</x:v>
+      </x:c>
+      <x:c r="C151" s="10" t="str">
+        <x:v>All-Optical Modulation of a Graphene-Cladded Silicon Photonic Crystal Cavity</x:v>
+      </x:c>
+      <x:c r="D151" s="10" t="str">
+        <x:v>ACS Photonics</x:v>
+      </x:c>
+      <x:c r="E151" s="10" t="str">
+        <x:v>10.1021/acsphotonics.5b00469</x:v>
+      </x:c>
+      <x:c r="F151" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G151" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H151" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I151" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1021/acsphotonics.5b00469</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="37.5" customHeight="1">
+      <x:c r="A152" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B152" s="10" t="str">
+        <x:v>2016 (year)</x:v>
+      </x:c>
+      <x:c r="C152" s="10" t="str">
+        <x:v>On the critical role of Rayleigh scattering in single-molecule surface-enhanced Raman scattering via a plasmonic nanogap</x:v>
+      </x:c>
+      <x:c r="D152" s="10" t="str">
+        <x:v>Nanoscale</x:v>
+      </x:c>
+      <x:c r="E152" s="10" t="str">
+        <x:v>10.1039/c6nr04574j</x:v>
+      </x:c>
+      <x:c r="F152" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G152" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H152" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I152" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1039/c6nr04574j</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="37.5" customHeight="1">
+      <x:c r="A153" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B153" s="10" t="str">
+        <x:v>2016 (year)</x:v>
+      </x:c>
+      <x:c r="C153" s="10" t="str">
+        <x:v>Self-propelled round-trip motion of Janus particles in static line optical tweezers</x:v>
+      </x:c>
+      <x:c r="D153" s="10" t="str">
+        <x:v>Nanoscale</x:v>
+      </x:c>
+      <x:c r="E153" s="10" t="str">
+        <x:v>10.1039/c6nr07470g</x:v>
+      </x:c>
+      <x:c r="F153" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G153" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H153" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I153" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1039/c6nr07470g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="37.5" customHeight="1">
+      <x:c r="A154" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B154" s="10" t="str">
+        <x:v>2016-08-11 (day)</x:v>
+      </x:c>
+      <x:c r="C154" s="10" t="str">
+        <x:v>Time-Modulated Hamiltonian for Interpreting Delayed-Choice Experiments via Mach–Zehnder Interferometers</x:v>
+      </x:c>
+      <x:c r="D154" s="10" t="str">
+        <x:v>Chinese Physics Letters</x:v>
+      </x:c>
+      <x:c r="E154" s="10" t="str">
+        <x:v>10.1088/0256-307x/33/8/080302</x:v>
+      </x:c>
+      <x:c r="F154" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H154" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I154" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1088/0256-307x/33/8/080302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="37.5" customHeight="1">
+      <x:c r="A155" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B155" s="10" t="str">
+        <x:v>2017-02-21 (day)</x:v>
+      </x:c>
+      <x:c r="C155" s="10" t="str">
+        <x:v>Plasmonic Particles with Unique Optical Interaction and Mechanical Motion Properties</x:v>
+      </x:c>
+      <x:c r="D155" s="10" t="str">
+        <x:v>Particle &amp; Particle Systems Characterization</x:v>
+      </x:c>
+      <x:c r="E155" s="10" t="str">
+        <x:v>10.1002/ppsc.201600380</x:v>
+      </x:c>
+      <x:c r="F155" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G155" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H155" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I155" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a233587/page.htm
+https://doi.org/10.1002/ppsc.201600380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="37.5" customHeight="1">
+      <x:c r="A156" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B156" s="10" t="str">
+        <x:v>2022-06-21 (day)</x:v>
+      </x:c>
+      <x:c r="C156" s="10" t="str">
+        <x:v>Prediction and Observation of Robust One-Way Bulk States in a Gyromagnetic Photonic Crystal</x:v>
+      </x:c>
+      <x:c r="D156" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E156" s="10" t="str">
+        <x:v>10.1103/physrevlett.128.257401</x:v>
+      </x:c>
+      <x:c r="F156" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G156" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H156" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I156" s="10" t="str">
+        <x:v>https://news.scut.edu.cn/2023/0423/c160a46712/page.htm
+https://doi.org/10.1103/physrevlett.128.257401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="33" customHeight="1">
+      <x:c r="A157" s="10" t="str">
+        <x:v>李志远</x:v>
+      </x:c>
+      <x:c r="B157" s="10" t="str">
+        <x:v>2026-01-20 (day)</x:v>
+      </x:c>
+      <x:c r="C157" s="10" t="str">
+        <x:v>mJ-level 7-octave ultraflat white laser encompassing 200–25,000 nm</x:v>
+      </x:c>
+      <x:c r="D157" s="10" t="str">
+        <x:v>Light: Science &amp; Applications</x:v>
+      </x:c>
+      <x:c r="E157" s="10" t="str">
+        <x:v>10.1038/s41377-025-02142-z</x:v>
+      </x:c>
+      <x:c r="F157" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G157" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H157" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I157" s="10" t="str">
+        <x:v>https://www.scut.edu.cn/new/2026/0123/c443a59361/page.htm
+https://doi.org/10.1038/s41377-025-02142-z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="33" customHeight="1">
+      <x:c r="A158" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B158" s="10" t="str">
+        <x:v>2012-03-27 (day)</x:v>
+      </x:c>
+      <x:c r="C158" s="10" t="str">
+        <x:v>Dark acoustic metamaterials as super absorbers for low-frequency sound</x:v>
+      </x:c>
+      <x:c r="D158" s="10" t="str">
+        <x:v>Nature Communications</x:v>
+      </x:c>
+      <x:c r="E158" s="10" t="str">
+        <x:v>10.1038/ncomms1758</x:v>
+      </x:c>
+      <x:c r="F158" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G158" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H158" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I158" s="10" t="str">
+        <x:v>https://www.nature.com/articles/ncomms1758
+https://doi.org/10.1038/ncomms1758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="37.5" customHeight="1">
+      <x:c r="A159" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B159" s="10" t="str">
+        <x:v>2012-07-24 (day)</x:v>
+      </x:c>
+      <x:c r="C159" s="10" t="str">
+        <x:v>First-principles study of Dirac and Dirac-like cones in phononic and photonic crystals</x:v>
+      </x:c>
+      <x:c r="D159" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E159" s="10" t="str">
+        <x:v>10.1103/physrevb.86.035141</x:v>
+      </x:c>
+      <x:c r="F159" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G159" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H159" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I159" s="10" t="str">
+        <x:v>https://journals.aps.org/prb/abstract/10.1103/PhysRevB.86.035141
+https://doi.org/10.1103/physrevb.86.035141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="33" customHeight="1">
+      <x:c r="A160" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B160" s="10" t="str">
+        <x:v>2017-11-08 (day)</x:v>
+      </x:c>
+      <x:c r="C160" s="10" t="str">
+        <x:v>Acoustic frequency filter based on anisotropic topological phononic crystals</x:v>
+      </x:c>
+      <x:c r="D160" s="10" t="str">
+        <x:v>Scientific Reports</x:v>
+      </x:c>
+      <x:c r="E160" s="10" t="str">
+        <x:v>10.1038/s41598-017-15409-2</x:v>
+      </x:c>
+      <x:c r="F160" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G160" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H160" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I160" s="10" t="str">
+        <x:v>https://www.nature.com/articles/s41598-017-15409-2
+https://doi.org/10.1038/s41598-017-15409-2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="37.5" customHeight="1">
+      <x:c r="A161" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B161" s="10" t="str">
+        <x:v>2020-10-02 (day)</x:v>
+      </x:c>
+      <x:c r="C161" s="10" t="str">
+        <x:v>Metagratings for Waterborne Sound: Various Functionalities Enabled by an Efficient Inverse-Design Approach</x:v>
+      </x:c>
+      <x:c r="D161" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E161" s="10" t="str">
+        <x:v>10.1103/physrevapplied.14.044003</x:v>
+      </x:c>
+      <x:c r="F161" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G161" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H161" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I161" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.14.044003
+https://doi.org/10.1103/physrevapplied.14.044003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="37.5" customHeight="1">
+      <x:c r="A162" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B162" s="10" t="str">
+        <x:v>2021-06-01 (day)</x:v>
+      </x:c>
+      <x:c r="C162" s="10" t="str">
+        <x:v>Acoustic Metagrating Circulators: Nonreciprocal, Robust, and Tunable Manipulation with Unitary Efficiency</x:v>
+      </x:c>
+      <x:c r="D162" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E162" s="10" t="str">
+        <x:v>10.1103/physrevapplied.15.064002</x:v>
+      </x:c>
+      <x:c r="F162" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G162" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H162" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I162" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.15.064002
+https://doi.org/10.1103/physrevapplied.15.064002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="37.5" customHeight="1">
+      <x:c r="A163" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B163" s="10" t="str">
+        <x:v>2021-10-18 (day)</x:v>
+      </x:c>
+      <x:c r="C163" s="10" t="str">
+        <x:v>Multifunctional Waterborne Acoustic Metagratings: From Extraordinary Transmission to Total and Abnormal Reflection</x:v>
+      </x:c>
+      <x:c r="D163" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E163" s="10" t="str">
+        <x:v>10.1103/physrevapplied.16.044029</x:v>
+      </x:c>
+      <x:c r="F163" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G163" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H163" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I163" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.16.044029
+https://doi.org/10.1103/physrevapplied.16.044029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="37.5" customHeight="1">
+      <x:c r="A164" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B164" s="10" t="str">
+        <x:v>2022-08-29 (day)</x:v>
+      </x:c>
+      <x:c r="C164" s="10" t="str">
+        <x:v>Metagrating-based acoustic wavelength division multiplexing enabled by deterministic and probabilistic deep learning models</x:v>
+      </x:c>
+      <x:c r="D164" s="10" t="str">
+        <x:v>Physical Review Research</x:v>
+      </x:c>
+      <x:c r="E164" s="10" t="str">
+        <x:v>10.1103/physrevresearch.4.033165</x:v>
+      </x:c>
+      <x:c r="F164" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G164" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H164" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I164" s="10" t="str">
+        <x:v>https://journals.aps.org/prresearch/abstract/10.1103/PhysRevResearch.4.033165
+https://doi.org/10.1103/physrevresearch.4.033165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="33" customHeight="1">
+      <x:c r="A165" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B165" s="10" t="str">
+        <x:v>2023-02-09 (day)</x:v>
+      </x:c>
+      <x:c r="C165" s="10" t="str">
+        <x:v>Flow-Permeable and Tunable Metalens for Subdiffraction Waterborne-Sound Focusing</x:v>
+      </x:c>
+      <x:c r="D165" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E165" s="10" t="str">
+        <x:v>10.1103/physrevapplied.19.024026</x:v>
+      </x:c>
+      <x:c r="F165" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G165" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H165" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I165" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.19.024026
+https://doi.org/10.1103/physrevapplied.19.024026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="37.5" customHeight="1">
+      <x:c r="A166" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B166" s="10" t="str">
+        <x:v>2023-11-03 (day)</x:v>
+      </x:c>
+      <x:c r="C166" s="10" t="str">
+        <x:v>Wide-angle and high-efficiency acoustic retroreflectors enabled by many-objective optimization algorithm and deep learning models</x:v>
+      </x:c>
+      <x:c r="D166" s="10" t="str">
+        <x:v>Physical Review Materials</x:v>
+      </x:c>
+      <x:c r="E166" s="10" t="str">
+        <x:v>10.1103/physrevmaterials.7.115201</x:v>
+      </x:c>
+      <x:c r="F166" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G166" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H166" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I166" s="10" t="str">
+        <x:v>https://journals.aps.org/prmaterials/abstract/10.1103/PhysRevMaterials.7.115201
+https://doi.org/10.1103/physrevmaterials.7.115201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="37.5" customHeight="1">
+      <x:c r="A167" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B167" s="10" t="str">
+        <x:v>2023-11-27 (day)</x:v>
+      </x:c>
+      <x:c r="C167" s="10" t="str">
+        <x:v>Achromatic Needle Focusing with Superresolution Enabled by a Ring-Shaped Acoustic Metalens</x:v>
+      </x:c>
+      <x:c r="D167" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E167" s="10" t="str">
+        <x:v>10.1103/physrevapplied.20.054053</x:v>
+      </x:c>
+      <x:c r="F167" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G167" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H167" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I167" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.20.054053
+https://doi.org/10.1103/physrevapplied.20.054053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="37.5" customHeight="1">
+      <x:c r="A168" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B168" s="10" t="str">
+        <x:v>2024-03-05 (day)</x:v>
+      </x:c>
+      <x:c r="C168" s="10" t="str">
+        <x:v>High-efficiency and large-numerical-aperture focusing with subdiffraction resolution using a hybrid elastic metalens</x:v>
+      </x:c>
+      <x:c r="D168" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E168" s="10" t="str">
+        <x:v>10.1103/physrevapplied.21.034007</x:v>
+      </x:c>
+      <x:c r="F168" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G168" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H168" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I168" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.21.034007
+https://doi.org/10.1103/physrevapplied.21.034007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="37.5" customHeight="1">
+      <x:c r="A169" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B169" s="10" t="str">
+        <x:v>2024-12-30 (day)</x:v>
+      </x:c>
+      <x:c r="C169" s="10" t="str">
+        <x:v>Ultrahigh-efficiency and superresolution focusing of the flexural wave enabled by a hybrid metalens with a large numerical aperture</x:v>
+      </x:c>
+      <x:c r="D169" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E169" s="10" t="str">
+        <x:v>10.1103/physrevapplied.22.064094</x:v>
+      </x:c>
+      <x:c r="F169" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G169" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H169" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I169" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/PhysRevApplied.22.064094
+https://doi.org/10.1103/physrevapplied.22.064094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="37.5" customHeight="1">
+      <x:c r="A170" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B170" s="10" t="str">
+        <x:v>2025-12-19 (day)</x:v>
+      </x:c>
+      <x:c r="C170" s="10" t="str">
+        <x:v>Hybrid metalens for ultrawide-angle and high-efficiency focusing of waterborne sound</x:v>
+      </x:c>
+      <x:c r="D170" s="10" t="str">
+        <x:v>Physical Review Applied</x:v>
+      </x:c>
+      <x:c r="E170" s="10" t="str">
+        <x:v>10.1103/d7kq-cl68</x:v>
+      </x:c>
+      <x:c r="F170" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G170" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H170" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I170" s="10" t="str">
+        <x:v>https://journals.aps.org/prapplied/abstract/10.1103/d7kq-cl68
+https://doi.org/10.1103/d7kq-cl68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="37.5" customHeight="1">
+      <x:c r="A171" s="10" t="str">
+        <x:v>梅军</x:v>
+      </x:c>
+      <x:c r="B171" s="10" t="str">
+        <x:v>2026-08-03 (day)</x:v>
+      </x:c>
+      <x:c r="C171" s="10" t="str">
+        <x:v>Continuous far-field zone focusing of flexural waves through phase engineering of metagratings</x:v>
+      </x:c>
+      <x:c r="D171" s="10" t="str">
+        <x:v>APS Open Science</x:v>
+      </x:c>
+      <x:c r="E171" s="10" t="str">
+        <x:v>10.1103/k8wt-lybx</x:v>
+      </x:c>
+      <x:c r="F171" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G171" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H171" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I171" s="10" t="str">
+        <x:v>https://journals.aps.org/apsos/abstract/10.1103/k8wt-lybx
+https://doi.org/10.1103/k8wt-lybx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="37.5" customHeight="1">
+      <x:c r="A172" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B172" s="10" t="str">
+        <x:v>2011-09-09 (day)</x:v>
+      </x:c>
+      <x:c r="C172" s="10" t="str">
+        <x:v>Simultaneous Enhancement of Open‐Circuit Voltage, Short‐Circuit Current Density, and Fill Factor in Polymer Solar Cells</x:v>
+      </x:c>
+      <x:c r="D172" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E172" s="10" t="str">
+        <x:v>10.1002/adma.201103006</x:v>
+      </x:c>
+      <x:c r="F172" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G172" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H172" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I172" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1002/adma.201103006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="37.5" customHeight="1">
+      <x:c r="A173" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B173" s="10" t="str">
+        <x:v>2012-08-19 (day)</x:v>
+      </x:c>
+      <x:c r="C173" s="10" t="str">
+        <x:v>Enhanced power-conversion efficiency in polymer solar cells using an inverted device structure</x:v>
+      </x:c>
+      <x:c r="D173" s="10" t="str">
+        <x:v>Nature Photonics</x:v>
+      </x:c>
+      <x:c r="E173" s="10" t="str">
+        <x:v>10.1038/nphoton.2012.190</x:v>
+      </x:c>
+      <x:c r="F173" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G173" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H173" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I173" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1038/nphoton.2012.190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="37.5" customHeight="1">
+      <x:c r="A174" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B174" s="10" t="str">
+        <x:v>2013-12-16 (day)</x:v>
+      </x:c>
+      <x:c r="C174" s="10" t="str">
+        <x:v>Recent Advances in Polymer Solar Cells: Realization of High Device Performance by Incorporating Water/Alcohol‐Soluble Conjugated Polymers as Electrode Buffer Layer</x:v>
+      </x:c>
+      <x:c r="D174" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E174" s="10" t="str">
+        <x:v>10.1002/adma.201303391</x:v>
+      </x:c>
+      <x:c r="F174" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G174" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H174" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I174" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1002/adma.201303391</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="37.5" customHeight="1">
+      <x:c r="A175" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B175" s="10" t="str">
+        <x:v>2014-03-14 (day)</x:v>
+      </x:c>
+      <x:c r="C175" s="10" t="str">
+        <x:v>White Polymer Light‐Emitting Devices for Solid‐State Lighting: Materials, Devices, and Recent Progress</x:v>
+      </x:c>
+      <x:c r="D175" s="10" t="str">
+        <x:v>Advanced Materials</x:v>
+      </x:c>
+      <x:c r="E175" s="10" t="str">
+        <x:v>10.1002/adma.201304784</x:v>
+      </x:c>
+      <x:c r="F175" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G175" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H175" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I175" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1002/adma.201304784</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="33" customHeight="1">
+      <x:c r="A176" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B176" s="10" t="str">
+        <x:v>2015-02-09 (day)</x:v>
+      </x:c>
+      <x:c r="C176" s="10" t="str">
+        <x:v>Single-junction polymer solar cells with high efficiency and photovoltage</x:v>
+      </x:c>
+      <x:c r="D176" s="10" t="str">
+        <x:v>Nature Photonics</x:v>
+      </x:c>
+      <x:c r="E176" s="10" t="str">
+        <x:v>10.1038/nphoton.2015.6</x:v>
+      </x:c>
+      <x:c r="F176" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G176" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H176" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I176" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1038/nphoton.2015.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="37.5" customHeight="1">
+      <x:c r="A177" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B177" s="10" t="str">
+        <x:v>2018-11-12 (day)</x:v>
+      </x:c>
+      <x:c r="C177" s="10" t="str">
+        <x:v>High-Performance Fullerene-Free Polymer Solar Cells Featuring Efficient Photocurrent Generation from Dual Pathways and Low Nonradiative Recombination Loss</x:v>
+      </x:c>
+      <x:c r="D177" s="10" t="str">
+        <x:v>ACS Energy Letters</x:v>
+      </x:c>
+      <x:c r="E177" s="10" t="str">
+        <x:v>10.1021/acsenergylett.8b01824</x:v>
+      </x:c>
+      <x:c r="F177" s="10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G177" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H177" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I177" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1021/acsenergylett.8b01824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="37.5" customHeight="1">
+      <x:c r="A178" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B178" s="10" t="str">
+        <x:v>2019 (year)</x:v>
+      </x:c>
+      <x:c r="C178" s="10" t="str">
+        <x:v>Assessing the energy offset at the electron donor/acceptor interface in organic solar cells through radiative efficiency measurements</x:v>
+      </x:c>
+      <x:c r="D178" s="10" t="str">
+        <x:v>Energy &amp; Environmental Science</x:v>
+      </x:c>
+      <x:c r="E178" s="10" t="str">
+        <x:v>10.1039/c9ee02939g</x:v>
+      </x:c>
+      <x:c r="F178" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G178" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H178" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I178" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1039/c9ee02939g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="37.5" customHeight="1">
+      <x:c r="A179" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B179" s="10" t="str">
+        <x:v>2020-01-20 (day)</x:v>
+      </x:c>
+      <x:c r="C179" s="10" t="str">
+        <x:v>High-efficiency organic solar cells with low non-radiative recombination loss and low energetic disorder</x:v>
+      </x:c>
+      <x:c r="D179" s="10" t="str">
+        <x:v>Nature Photonics</x:v>
+      </x:c>
+      <x:c r="E179" s="10" t="str">
+        <x:v>10.1038/s41566-019-0573-5</x:v>
+      </x:c>
+      <x:c r="F179" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G179" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H179" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I179" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1038/s41566-019-0573-5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="33" customHeight="1">
+      <x:c r="A180" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B180" s="10" t="str">
+        <x:v>2022-09-29 (day)</x:v>
+      </x:c>
+      <x:c r="C180" s="10" t="str">
+        <x:v>Bright short-wavelength infrared organic light-emitting devices</x:v>
+      </x:c>
+      <x:c r="D180" s="10" t="str">
+        <x:v>Nature Photonics</x:v>
+      </x:c>
+      <x:c r="E180" s="10" t="str">
+        <x:v>10.1038/s41566-022-01069-w</x:v>
+      </x:c>
+      <x:c r="F180" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G180" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H180" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I180" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1038/s41566-022-01069-w</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="33" customHeight="1">
+      <x:c r="A181" s="10" t="str">
+        <x:v>吴宏滨</x:v>
+      </x:c>
+      <x:c r="B181" s="10" t="str">
+        <x:v>2024-04-15 (day)</x:v>
+      </x:c>
+      <x:c r="C181" s="10" t="str">
+        <x:v>Physical insights into non-fullerene organic photovoltaics</x:v>
+      </x:c>
+      <x:c r="D181" s="10" t="str">
+        <x:v>Nature Reviews Physics</x:v>
+      </x:c>
+      <x:c r="E181" s="10" t="str">
+        <x:v>10.1038/s42254-024-00719-y</x:v>
+      </x:c>
+      <x:c r="F181" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G181" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H181" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I181" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2017/1206/c13953a574503/page.htm
+https://doi.org/10.1038/s42254-024-00719-y</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="33" customHeight="1">
+      <x:c r="A182" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B182" s="10" t="str">
+        <x:v>2014-10-13 (day)</x:v>
+      </x:c>
+      <x:c r="C182" s="10" t="str">
+        <x:v>Quantum metrological bounds for vector parameters</x:v>
+      </x:c>
+      <x:c r="D182" s="10" t="str">
+        <x:v>Physical Review A</x:v>
+      </x:c>
+      <x:c r="E182" s="10" t="str">
+        <x:v>10.1103/physreva.90.043818</x:v>
+      </x:c>
+      <x:c r="F182" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G182" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H182" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I182" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physreva.90.043818</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="33" customHeight="1">
+      <x:c r="A183" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B183" s="10" t="str">
+        <x:v>2015-02-04 (day)</x:v>
+      </x:c>
+      <x:c r="C183" s="10" t="str">
+        <x:v>Quantum metrology via repeated quantum nondemolition measurements in a photon box</x:v>
+      </x:c>
+      <x:c r="D183" s="10" t="str">
+        <x:v>Physical Review A</x:v>
+      </x:c>
+      <x:c r="E183" s="10" t="str">
+        <x:v>10.1103/physreva.91.022104</x:v>
+      </x:c>
+      <x:c r="F183" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G183" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H183" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I183" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physreva.91.022104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="33" customHeight="1">
+      <x:c r="A184" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B184" s="10" t="str">
+        <x:v>2015-04-02 (day)</x:v>
+      </x:c>
+      <x:c r="C184" s="10" t="str">
+        <x:v>Demonstration of entanglement-enhanced phase estimation in solid</x:v>
+      </x:c>
+      <x:c r="D184" s="10" t="str">
+        <x:v>Nature Communications</x:v>
+      </x:c>
+      <x:c r="E184" s="10" t="str">
+        <x:v>10.1038/ncomms7726</x:v>
+      </x:c>
+      <x:c r="F184" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G184" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H184" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I184" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1038/ncomms7726</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="33" customHeight="1">
+      <x:c r="A185" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B185" s="10" t="str">
+        <x:v>2016-01-20 (day)</x:v>
+      </x:c>
+      <x:c r="C185" s="10" t="str">
+        <x:v>Quantifying coherence in infinite-dimensional systems</x:v>
+      </x:c>
+      <x:c r="D185" s="10" t="str">
+        <x:v>Physical Review A</x:v>
+      </x:c>
+      <x:c r="E185" s="10" t="str">
+        <x:v>10.1103/physreva.93.012334</x:v>
+      </x:c>
+      <x:c r="F185" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G185" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H185" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I185" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physreva.93.012334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="37.5" customHeight="1">
+      <x:c r="A186" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B186" s="10" t="str">
+        <x:v>2017-04-12 (day)</x:v>
+      </x:c>
+      <x:c r="C186" s="10" t="str">
+        <x:v>Single-Shot Readout of a Nuclear Spin Weakly Coupled to a Nitrogen-Vacancy Center at Room Temperature</x:v>
+      </x:c>
+      <x:c r="D186" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E186" s="10" t="str">
+        <x:v>10.1103/physrevlett.118.150504</x:v>
+      </x:c>
+      <x:c r="F186" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G186" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H186" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I186" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.118.150504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="33" customHeight="1">
+      <x:c r="A187" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B187" s="10" t="str">
+        <x:v>2018-02-02 (day)</x:v>
+      </x:c>
+      <x:c r="C187" s="10" t="str">
+        <x:v>Emulating Many-Body Localization with a Superconducting Quantum Processor</x:v>
+      </x:c>
+      <x:c r="D187" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E187" s="10" t="str">
+        <x:v>10.1103/physrevlett.120.050507</x:v>
+      </x:c>
+      <x:c r="F187" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G187" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H187" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I187" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.120.050507</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="33" customHeight="1">
+      <x:c r="A188" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B188" s="10" t="str">
+        <x:v>2018-06-18 (day)</x:v>
+      </x:c>
+      <x:c r="C188" s="10" t="str">
+        <x:v>Characterization of Topological States via Dual Multipartite Entanglement</x:v>
+      </x:c>
+      <x:c r="D188" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E188" s="10" t="str">
+        <x:v>10.1103/physrevlett.120.250501</x:v>
+      </x:c>
+      <x:c r="F188" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G188" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H188" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I188" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.120.250501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="33" customHeight="1">
+      <x:c r="A189" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B189" s="10" t="str">
+        <x:v>2019-02-20 (day)</x:v>
+      </x:c>
+      <x:c r="C189" s="10" t="str">
+        <x:v>Second-Order Topological Phases in Non-Hermitian Systems</x:v>
+      </x:c>
+      <x:c r="D189" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E189" s="10" t="str">
+        <x:v>10.1103/physrevlett.122.076801</x:v>
+      </x:c>
+      <x:c r="F189" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G189" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H189" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I189" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.122.076801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="33" customHeight="1">
+      <x:c r="A190" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B190" s="10" t="str">
+        <x:v>2019-05-24 (day)</x:v>
+      </x:c>
+      <x:c r="C190" s="10" t="str">
+        <x:v>Strongly correlated quantum walks with a 12-qubit superconducting processor</x:v>
+      </x:c>
+      <x:c r="D190" s="10" t="str">
+        <x:v>Science</x:v>
+      </x:c>
+      <x:c r="E190" s="10" t="str">
+        <x:v>10.1126/science.aaw1611</x:v>
+      </x:c>
+      <x:c r="F190" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G190" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H190" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I190" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1126/science.aaw1611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="37.5" customHeight="1">
+      <x:c r="A191" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B191" s="10" t="str">
+        <x:v>2019-07-30 (day)</x:v>
+      </x:c>
+      <x:c r="C191" s="10" t="str">
+        <x:v>Propagation and Localization of Collective Excitations on a 24-Qubit Superconducting Processor</x:v>
+      </x:c>
+      <x:c r="D191" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E191" s="10" t="str">
+        <x:v>10.1103/physrevlett.123.050502</x:v>
+      </x:c>
+      <x:c r="F191" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G191" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H191" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I191" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.123.050502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="33" customHeight="1">
+      <x:c r="A192" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B192" s="10" t="str">
+        <x:v>2019-08-09 (day)</x:v>
+      </x:c>
+      <x:c r="C192" s="10" t="str">
+        <x:v>Generation of multicomponent atomic Schrödinger cat states of up to 20 qubits</x:v>
+      </x:c>
+      <x:c r="D192" s="10" t="str">
+        <x:v>Science</x:v>
+      </x:c>
+      <x:c r="E192" s="10" t="str">
+        <x:v>10.1126/science.aay0600</x:v>
+      </x:c>
+      <x:c r="F192" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G192" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H192" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I192" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1126/science.aay0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="33" customHeight="1">
+      <x:c r="A193" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B193" s="10" t="str">
+        <x:v>2019-08-15 (day)</x:v>
+      </x:c>
+      <x:c r="C193" s="10" t="str">
+        <x:v>Topological band theory for non-Hermitian systems from the Dirac equation</x:v>
+      </x:c>
+      <x:c r="D193" s="10" t="str">
+        <x:v>Physical Review B</x:v>
+      </x:c>
+      <x:c r="E193" s="10" t="str">
+        <x:v>10.1103/physrevb.100.054105</x:v>
+      </x:c>
+      <x:c r="F193" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G193" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H193" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I193" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevb.100.054105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="37.5" customHeight="1">
+      <x:c r="A194" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B194" s="10" t="str">
+        <x:v>2020-05-27 (day)</x:v>
+      </x:c>
+      <x:c r="C194" s="10" t="str">
+        <x:v>Observing Information Backflow from Controllable Non-Markovian Multichannels in Diamond</x:v>
+      </x:c>
+      <x:c r="D194" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E194" s="10" t="str">
+        <x:v>10.1103/physrevlett.124.210502</x:v>
+      </x:c>
+      <x:c r="F194" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G194" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H194" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I194" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.124.210502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="33" customHeight="1">
+      <x:c r="A195" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B195" s="10" t="str">
+        <x:v>2020-06-17 (day)</x:v>
+      </x:c>
+      <x:c r="C195" s="10" t="str">
+        <x:v>Probing dynamical phase transitions with a superconducting quantum simulator</x:v>
+      </x:c>
+      <x:c r="D195" s="10" t="str">
+        <x:v>Science Advances</x:v>
+      </x:c>
+      <x:c r="E195" s="10" t="str">
+        <x:v>10.1126/sciadv.aba4935</x:v>
+      </x:c>
+      <x:c r="F195" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G195" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H195" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I195" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1126/sciadv.aba4935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="33" customHeight="1">
+      <x:c r="A196" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B196" s="10" t="str">
+        <x:v>2020-09-21 (day)</x:v>
+      </x:c>
+      <x:c r="C196" s="10" t="str">
+        <x:v>Observation of energy-resolved many-body localization</x:v>
+      </x:c>
+      <x:c r="D196" s="10" t="str">
+        <x:v>Nature Physics</x:v>
+      </x:c>
+      <x:c r="E196" s="10" t="str">
+        <x:v>10.1038/s41567-020-1035-1</x:v>
+      </x:c>
+      <x:c r="F196" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G196" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H196" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I196" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1038/s41567-020-1035-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="37.5" customHeight="1">
+      <x:c r="A197" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B197" s="10" t="str">
+        <x:v>2021-07-09 (day)</x:v>
+      </x:c>
+      <x:c r="C197" s="10" t="str">
+        <x:v>Observation of Strong and Weak Thermalization in a Superconducting Quantum Processor</x:v>
+      </x:c>
+      <x:c r="D197" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E197" s="10" t="str">
+        <x:v>10.1103/physrevlett.127.020602</x:v>
+      </x:c>
+      <x:c r="F197" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G197" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H197" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I197" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.127.020602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="37.5" customHeight="1">
+      <x:c r="A198" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B198" s="10" t="str">
+        <x:v>2022-04-12 (day)</x:v>
+      </x:c>
+      <x:c r="C198" s="10" t="str">
+        <x:v>Metrological Characterization of Non-Gaussian Entangled States of Superconducting Qubits</x:v>
+      </x:c>
+      <x:c r="D198" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E198" s="10" t="str">
+        <x:v>10.1103/physrevlett.128.150501</x:v>
+      </x:c>
+      <x:c r="F198" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G198" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H198" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I198" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.128.150501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="37.5" customHeight="1">
+      <x:c r="A199" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B199" s="10" t="str">
+        <x:v>2022-04-19 (day)</x:v>
+      </x:c>
+      <x:c r="C199" s="10" t="str">
+        <x:v>Observation of Thermalization and Information Scrambling in a Superconducting Quantum Processor</x:v>
+      </x:c>
+      <x:c r="D199" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E199" s="10" t="str">
+        <x:v>10.1103/physrevlett.128.160502</x:v>
+      </x:c>
+      <x:c r="F199" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G199" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H199" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I199" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.128.160502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="37.5" customHeight="1">
+      <x:c r="A200" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B200" s="10" t="str">
+        <x:v>2022-05-24 (day)</x:v>
+      </x:c>
+      <x:c r="C200" s="10" t="str">
+        <x:v>Multipartite entanglement of the topologically ordered state in a perturbed toric code</x:v>
+      </x:c>
+      <x:c r="D200" s="10" t="str">
+        <x:v>Physical Review Research</x:v>
+      </x:c>
+      <x:c r="E200" s="10" t="str">
+        <x:v>10.1103/physrevresearch.4.023144</x:v>
+      </x:c>
+      <x:c r="F200" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G200" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H200" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I200" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevresearch.4.023144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="33" customHeight="1">
+      <x:c r="A201" s="10" t="str">
+        <x:v>张煜然</x:v>
+      </x:c>
+      <x:c r="B201" s="10" t="str">
+        <x:v>2022-10-13 (day)</x:v>
+      </x:c>
+      <x:c r="C201" s="10" t="str">
+        <x:v>Probing Operator Spreading via Floquet Engineering in a Superconducting Circuit</x:v>
+      </x:c>
+      <x:c r="D201" s="10" t="str">
+        <x:v>Physical Review Letters</x:v>
+      </x:c>
+      <x:c r="E201" s="10" t="str">
+        <x:v>10.1103/physrevlett.129.160602</x:v>
+      </x:c>
+      <x:c r="F201" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G201" s="10" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H201" s="10" t="str">
+        <x:v>crossref_verified</x:v>
+      </x:c>
+      <x:c r="I201" s="10" t="str">
+        <x:v>https://www2.scut.edu.cn/physics/2023/0529/c13954a504136/page.htm
+https://doi.org/10.1103/physrevlett.129.160602</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19677bfc77834a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>